--- a/data/sxbet/ligas/La Liga/trades.xlsx
+++ b/data/sxbet/ligas/La Liga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V9"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xb7f333fbe5a18daf831395020096fbb62febd43977f5f81366c99339b63d902d</t>
+          <t>0x20fcd5dbfafe538f08c15c6b35af5d546fa35aa588ef9811c9696ac39843c736</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,52 +546,52 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>63.86</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves -0.5</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>La Liga</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Racing Santander</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>La Liga</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x1518c9a8caca0376f881601c848e03d81cd65f5d32c2b63a51625351cc193e86</t>
+          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786621976</t>
+          <t>1786640471</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>152.501493</t>
+          <t>12.195122</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,7 +643,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x79454b5fc310a342a5ad62ccf677e7ea1c42b0e701cd313d0019ee8ec1faf7a2</t>
+          <t>0x48d06bf1eb103be3b93f605ad7b9ed301f228fa4dfae557dca83434f1d5e0c1a</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -658,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>97.87</t>
+          <t>26.96</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportivo Alaves -0.5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -683,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xf9063ec13eee8f96a20b89bd687d0a5f1a3197a4408eb58240f63d72be7c644f</t>
+          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786621975</t>
+          <t>1786640450</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>320.885246</t>
+          <t>65.957187</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,12 +755,12 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x6df789a868c08b6d011dc9dc3fe38cf8be42973ee6e2b3513f1ae98f3a70e174</t>
+          <t>0xe750c1fb5c3ef7edfc166b18659be46b00e3cc96d5ae299b162166175d07245f</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -770,22 +770,22 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>82.86999</t>
+          <t>20.06</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Racing Santander +1</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -810,7 +810,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xeffd773f9a996fcdab4f40cb833c6db488621204b6af7959d07794c43de040c4</t>
+          <t>0x0a08c3d7f08812839b48fc67d5842cc07f2a5e67ce2a26c46d0210680fda2f99</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -840,7 +840,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786621975</t>
+          <t>1786639065</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>112.556862</t>
+          <t>36.891954</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,12 +867,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x4061873586e14d63aeb0e4cdf23afafe5cd7b3c74fe59157daf06c85b8fd8796</t>
+          <t>0xdc16a40eba6eeb7462531fd3b01240a8f58f0ea20568efbaba25b17131094f2e</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -882,22 +882,22 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>1.4213</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Racing Santander -0.5</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xb811d0e9d1802cd3762a57ca8fc3a5399392dd37dec4f8d9fd37f0170ece0f50</t>
+          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -952,17 +952,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786621975</t>
+          <t>1786633518</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>146.95082</t>
+          <t>11.869436</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,7 +979,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x8dda40aa7d3c4140b3e5ab6ab62f3db4f5a3730a15ebff80f0bda9807c704ca2</t>
+          <t>0x1b67e861f8e383798d979684797f608bfad6122cc87844f2a37a8cf06e019030</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -987,15 +987,19 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>27.87224</t>
+          <t>53.83</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5325</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1003,7 +1007,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -1011,27 +1019,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Celta de Vigo vs Osasuna</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x0f075dae0a586d46b2073e126cbc52393dc2ff99a26953308f94b3b2751764b7</t>
+          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19370496</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1056,17 +1064,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786619056</t>
+          <t>1786633487</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786908600</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>52.342235</t>
+          <t>128.166667</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,39 +1091,31 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x4565877a70aabfac9d4d4a2afcda9ace6e304d9bd921ce69a2149c76528e271a</t>
+          <t>0x909a230aebd5eb00de6012a0eb69301784b515acf69e93ee497d243bd3ce212f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xb363112BA7ed93A221Efb405496e4Fa3BE119D81</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xbcD65d7e2D58b95Cf434eB65a82b9FD5b682D144</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>72.15999</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Rayo Vallecano</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -1123,27 +1123,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x2b9c4f75049808a8d2b353d1c6e902da151d2fea092e70f08cdd4ac2ffbfd8a6</t>
+          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1168,17 +1168,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786614389</t>
+          <t>1786632901</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>175.438596</t>
+          <t>120.26665</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,39 +1195,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x562837a4689bf537ab0502cfe5d722bafc1833bc972e329ba5399cd7649a219c</t>
+          <t>0x081a76991e0701cf3dbcaa6ccbdd7d9dd69242e812c8b7e977517fe836423751</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.1038</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -1235,27 +1227,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Espanyol vs Levante</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xda132f38d7cbcb404e0db6126292d55c3614e3311c2670ac15890a14a94cdaea</t>
+          <t>0xd36fc2a623f22222f73350186e7d08c0d31b2d895ac24a68dc8408d4e98bf55a</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370489</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1280,17 +1272,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786586644</t>
+          <t>1786631513</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>7.769231</t>
+          <t>76.240964</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1307,28 +1299,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x27be56be09649bd460766fe27df249788cf4d7ad87d19f5f9a8bfba225e519b9</t>
+          <t>0x6f1c770a5b9534dbfff85f398a28d171effe0e02699c6558a37a881468f3090e</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.52676</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.7512</t>
+          <t>1.1013</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1339,70 +1331,1782 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
+          <t>Sevilla vs Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>L19370582</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>1786631323</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>1786822200</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>78.123457</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>0xffde28cdfe7ae2b6324278e8117e605bc5c2ecb236877e683d06b5cbe620b2b1</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>1.165</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J10" t="inlineStr">
         <is>
           <t>Deportivo Alaves</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="K10" t="inlineStr">
         <is>
           <t>Getafe</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>1786631207</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>67.333333</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>0x1542e94d97dca7a28f2bf2b946f64e1fefc9fc04f50a7622a8a2791d01c58796</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>11.85998</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>1.7113</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>1786630102</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>16.67484</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>0x9ff18d48c5ac1507ef9b6a3dfaf34f20966e85ee30cbd99e0df47a940abf1d32</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>1.4412</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0x776caca6c8b9cb32d9a7b2ec2b4f40bbb630001b4db7c24175062af09044b7dd</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>1786626342</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>11.331445</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>0x50f0b3572b92fd4a3268a217b75ca6b4a52b72077d0276df9d0d123d8b3ebc60</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>16.18903</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>1.4412</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0x776caca6c8b9cb32d9a7b2ec2b4f40bbb630001b4db7c24175062af09044b7dd</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>1786626327</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>36.68902</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>0x2d1550913dec85439afda8d85c6033895212998f22943ab968dee5cbd7d7e7a2</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>35.45869</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>1.2537</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0x0596e7ef887839f51f014583ff32fca0dbfab0916b17c3d05d740985b59eabc3</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>1786624561</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>139.73868</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>0x6f809dd95ba0a7f41584a66e0979cb2c04ebaeefb6e5d949b0bfd9c53278c063</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>1.7163</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>1786623012</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>6.980803</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>0xddff1b4ca7359c6045ede1bd2995e1e57620811dc33cc7338113c5449dccd695</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>28.91904</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>1.6038</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>0xf684bc2655869d0024c7de5a1f2b51fb35813185b075bf3cc8d5f2fe8ce176b5</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>1786622982</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>47.899031</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>0xb02e365f47ba9eaba62de63e4b14c94bf1b59d60c56188857359df36e7b10ef0</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>30.81465</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>1.7113</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>1786622982</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>43.32464</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0xb7f333fbe5a18daf831395020096fbb62febd43977f5f81366c99339b63d902d</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>63.86</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>1.4187</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>Racing Santander vs Villarreal</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>0x1518c9a8caca0376f881601c848e03d81cd65f5d32c2b63a51625351cc193e86</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>L19370490</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>1786621976</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>1786892400</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>152.501493</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>0x79454b5fc310a342a5ad62ccf677e7ea1c42b0e701cd313d0019ee8ec1faf7a2</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>97.87</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>1.305</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>Racing Santander vs Villarreal</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>0xf9063ec13eee8f96a20b89bd687d0a5f1a3197a4408eb58240f63d72be7c644f</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>L19370490</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>1786621975</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>1786892400</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>320.885246</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>0x6df789a868c08b6d011dc9dc3fe38cf8be42973ee6e2b3513f1ae98f3a70e174</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>82.86999</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>1.7363</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Racing Santander +1</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>Racing Santander vs Villarreal</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>0xeffd773f9a996fcdab4f40cb833c6db488621204b6af7959d07794c43de040c4</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>L19370490</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>1786621975</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>1786892400</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>112.556862</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>0x4061873586e14d63aeb0e4cdf23afafe5cd7b3c74fe59157daf06c85b8fd8796</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>44.82</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>1.305</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Racing Santander -0.5</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>Racing Santander vs Villarreal</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>0xb811d0e9d1802cd3762a57ca8fc3a5399392dd37dec4f8d9fd37f0170ece0f50</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>L19370490</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>1786621975</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>1786892400</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>146.95082</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>0x8dda40aa7d3c4140b3e5ab6ab62f3db4f5a3730a15ebff80f0bda9807c704ca2</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>27.87224</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>1.5325</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>Celta de Vigo vs Osasuna</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Celta de Vigo</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>0x0f075dae0a586d46b2073e126cbc52393dc2ff99a26953308f94b3b2751764b7</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>L19370496</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>1786619056</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>1786908600</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>52.342235</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>0x4565877a70aabfac9d4d4a2afcda9ace6e304d9bd921ce69a2149c76528e271a</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>0xb363112BA7ed93A221Efb405496e4Fa3BE119D81</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>1.285</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Sevilla vs Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>0x2b9c4f75049808a8d2b353d1c6e902da151d2fea092e70f08cdd4ac2ffbfd8a6</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>L19370582</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>1786614389</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>1786822200</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>175.438596</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>0x562837a4689bf537ab0502cfe5d722bafc1833bc972e329ba5399cd7649a219c</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>0xda132f38d7cbcb404e0db6126292d55c3614e3311c2670ac15890a14a94cdaea</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>1786586644</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>7.769231</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>0x27be56be09649bd460766fe27df249788cf4d7ad87d19f5f9a8bfba225e519b9</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>1.52676</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>1.7512</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
         <is>
           <t>0x32766ed977cae312bdb45c44b07e70207b356db986ef0293796496f193e13d1e</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>L19370598</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
         <is>
           <t>1786578252</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S25" t="inlineStr">
         <is>
           <t>1786815000</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="T25" t="inlineStr">
         <is>
           <t>2.032293</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="U25" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/La Liga/trades.xlsx
+++ b/data/sxbet/ligas/La Liga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V25"/>
+  <dimension ref="A1:V43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,39 +531,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x20fcd5dbfafe538f08c15c6b35af5d546fa35aa588ef9811c9696ac39843c736</t>
+          <t>0x11476693f9b725995aedcf0e75acf05d19a0f1647da3059f334da311f0f1e922</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1.19253</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.5713</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Deportivo Alaves -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -571,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Racing Santander vs Villarreal</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
+          <t>0x10c92f089fb69109ac5beea7c82a0e1cd2f23257cd842348710e2598be68bc48</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370490</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786640471</t>
+          <t>1786664168</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>12.195122</t>
+          <t>2.08758</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,39 +635,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x48d06bf1eb103be3b93f605ad7b9ed301f228fa4dfae557dca83434f1d5e0c1a</t>
+          <t>0x046492cfcbf4e5a3ced4caa85326fa8b44dbff1fb248a61a7fa6c8a8d2d9c1f8</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>26.96</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.5962</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Deportivo Alaves -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -698,7 +682,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
+          <t>0xfcdcf41a0510583d5bb65df7215b5101ff435808043952db2a0364f1424743db</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -728,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786640450</t>
+          <t>1786663762</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -738,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>65.957187</t>
+          <t>8.385744</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,39 +739,31 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xe750c1fb5c3ef7edfc166b18659be46b00e3cc96d5ae299b162166175d07245f</t>
+          <t>0xe376b22b83ba1a0d5c58e6763337d61f4445c85bfdc77949472d41c7c47e42b6</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -795,27 +771,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Celta de Vigo vs Osasuna</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x0a08c3d7f08812839b48fc67d5842cc07f2a5e67ce2a26c46d0210680fda2f99</t>
+          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370496</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -840,17 +816,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786639065</t>
+          <t>1786657450</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786908600</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>36.891954</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -867,12 +843,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xdc16a40eba6eeb7462531fd3b01240a8f58f0ea20568efbaba25b17131094f2e</t>
+          <t>0x4e949c2076e8faf4dcc272acfa8d69c62442324aca8ceeb5820b8348c74f13f6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -882,12 +858,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4213</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -897,7 +873,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Tie</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -907,27 +883,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Celta de Vigo vs Osasuna</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
+          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370496</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -952,17 +928,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786633518</t>
+          <t>1786657449</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786908600</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>11.869436</t>
+          <t>52.967742</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -979,27 +955,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x1b67e861f8e383798d979684797f608bfad6122cc87844f2a37a8cf06e019030</t>
+          <t>0xd54151c9cd066d8a5e7714f77ebc5e24ee2aac3e2c8a52a50b3a6becd0bac875</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>53.83</t>
+          <t>112.94</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.6625</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1007,11 +979,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -1019,27 +987,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
+          <t>0x78a4cf6b02d047f006e2c80b80d1bba724ebd9a508d0cce70fc13d1dcc698bd3</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1064,17 +1032,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786633487</t>
+          <t>1786656774</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>128.166667</t>
+          <t>170.475472</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1091,28 +1059,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x909a230aebd5eb00de6012a0eb69301784b515acf69e93ee497d243bd3ce212f</t>
+          <t>0x835c08ffc86c9c616d8c107e844ff9658b10b62372398122a4f7ded5bb28a516</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xbcD65d7e2D58b95Cf434eB65a82b9FD5b682D144</t>
+          <t>0x8e9bE2B8b636Cc98b01957cE9D4E3B62cF579080</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>72.15999</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1123,27 +1091,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1168,17 +1136,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786632901</t>
+          <t>1786651844</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>120.26665</t>
+          <t>8.492552</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1195,28 +1163,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x081a76991e0701cf3dbcaa6ccbdd7d9dd69242e812c8b7e977517fe836423751</t>
+          <t>0x45cc84f2dd4c1b45226a895eead76c109d5af22eac83562ab8aa23758f8a6b5e</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xa3786b93377213A42Bf1d3261d373cE67Cf2AA67</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.1038</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1227,27 +1195,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Espanyol vs Levante</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xd36fc2a623f22222f73350186e7d08c0d31b2d895ac24a68dc8408d4e98bf55a</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19370489</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1272,17 +1240,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786631513</t>
+          <t>1786651814</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>76.240964</t>
+          <t>42.735043</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1299,28 +1267,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x6f1c770a5b9534dbfff85f398a28d171effe0e02699c6558a37a881468f3090e</t>
+          <t>0x213398a7cadc42743f3aee31a89c45cc1f9c78136646bd816983864c34b13f79</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x4feB57379592eb94c51c014553de6EEbD4d42577</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.1013</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1331,27 +1299,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Celta de Vigo vs Osasuna</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
+          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370496</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1376,17 +1344,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786631323</t>
+          <t>1786651743</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786908600</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>78.123457</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1403,28 +1371,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xffde28cdfe7ae2b6324278e8117e605bc5c2ecb236877e683d06b5cbe620b2b1</t>
+          <t>0x0adf7a0f94fb74bebb4e5acb49582e1f91e3ae462b204becaedfbe0f50714ede</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x06a603b688E676702ec63D735CAe4A57ff71B3e1</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1435,27 +1403,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1480,17 +1448,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786631207</t>
+          <t>1786651718</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>67.333333</t>
+          <t>8.546991</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1507,23 +1475,23 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x1542e94d97dca7a28f2bf2b946f64e1fefc9fc04f50a7622a8a2791d01c58796</t>
+          <t>0xc33e951dfa8d84c01759f86fe63dfc68ddc2b547988e3a32445d72b681f7f7a5</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11.85998</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.7113</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1539,27 +1507,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1584,17 +1552,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786630102</t>
+          <t>1786651637</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>16.67484</t>
+          <t>8.546991</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1611,28 +1579,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x9ff18d48c5ac1507ef9b6a3dfaf34f20966e85ee30cbd99e0df47a940abf1d32</t>
+          <t>0x948b3c3ece530e62252af65b92bdd73725833fe7355d5496ab1d4f6d84e43cc4</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.4412</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1643,27 +1611,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x776caca6c8b9cb32d9a7b2ec2b4f40bbb630001b4db7c24175062af09044b7dd</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1688,17 +1656,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786626342</t>
+          <t>1786651588</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>11.331445</t>
+          <t>1.709402</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1715,28 +1683,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x50f0b3572b92fd4a3268a217b75ca6b4a52b72077d0276df9d0d123d8b3ebc60</t>
+          <t>0x7578c65431424d3ae35de659ad6d246a7814cbb553d85319bf0968700f7bca4a</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>16.18903</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.4412</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1747,27 +1715,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x776caca6c8b9cb32d9a7b2ec2b4f40bbb630001b4db7c24175062af09044b7dd</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1792,17 +1760,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786626327</t>
+          <t>1786651585</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>36.68902</t>
+          <t>17.094</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1819,28 +1787,28 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x2d1550913dec85439afda8d85c6033895212998f22943ab968dee5cbd7d7e7a2</t>
+          <t>0x28bc2779df67c8165804579669b7a40ef9e3a34f89e4d9d4c81a44f6c49d8be2</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x2F9aCBd9B89C6eF3bc3Dc2B0F0cCD0E0936BF912</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>35.45869</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.2537</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -1851,27 +1819,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x0596e7ef887839f51f014583ff32fca0dbfab0916b17c3d05d740985b59eabc3</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1896,17 +1864,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786624561</t>
+          <t>1786651567</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>139.73868</t>
+          <t>17.094</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1923,23 +1891,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x6f809dd95ba0a7f41584a66e0979cb2c04ebaeefb6e5d949b0bfd9c53278c063</t>
+          <t>0x0eaa76f318c30c9b01a36fedfdc1b48daafadd063ed5c90a74fd0908bdecfce3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x6203b6338991Ec84C8A8f5ef06bC17ceB1395Ddb</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.7163</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1955,27 +1923,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2000,17 +1968,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786623012</t>
+          <t>1786651567</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>6.980803</t>
+          <t>11.965812</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2027,28 +1995,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xddff1b4ca7359c6045ede1bd2995e1e57620811dc33cc7338113c5449dccd695</t>
+          <t>0xcc54eb94d459bc0b9a34beb78c07fafbc7c1f3e7c6d43846f17fb20856c43d24</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>28.91904</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2059,27 +2027,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xf684bc2655869d0024c7de5a1f2b51fb35813185b075bf3cc8d5f2fe8ce176b5</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2104,17 +2072,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786622982</t>
+          <t>1786651559</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>47.899031</t>
+          <t>42.735043</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2131,23 +2099,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0xb02e365f47ba9eaba62de63e4b14c94bf1b59d60c56188857359df36e7b10ef0</t>
+          <t>0x1b14ab3ce842bb0ded035add24fcdd28a77380141c189ae36b1f623e70dff465</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>30.81465</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.7113</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2163,27 +2131,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2208,17 +2176,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786622982</t>
+          <t>1786651559</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>43.32464</t>
+          <t>17.094</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2235,67 +2203,59 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xb7f333fbe5a18daf831395020096fbb62febd43977f5f81366c99339b63d902d</t>
+          <t>0x31a8e64cfb4307b5b608318a4e037810f68fe9bef13258aa7d3c45dd664c0ad3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x03d4fFC791EE4A80194C9d9782E7D56407b242Ed</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>63.86</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr">
+        <is>
           <t>La Liga</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Racing Santander</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>La Liga</t>
-        </is>
-      </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0x1518c9a8caca0376f881601c848e03d81cd65f5d32c2b63a51625351cc193e86</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2320,17 +2280,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786621976</t>
+          <t>1786651558</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>152.501493</t>
+          <t>25.641026</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2347,39 +2307,31 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x79454b5fc310a342a5ad62ccf677e7ea1c42b0e701cd313d0019ee8ec1faf7a2</t>
+          <t>0x1c244dc1d052ae42a83bf5640bcba1b28bb9c28853e7f42713fa4fddcb66b677</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>97.87</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Racing Santander</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -2387,27 +2339,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xf9063ec13eee8f96a20b89bd687d0a5f1a3197a4408eb58240f63d72be7c644f</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2432,17 +2384,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786621975</t>
+          <t>1786651550</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>320.885246</t>
+          <t>8.546991</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2459,12 +2411,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x6df789a868c08b6d011dc9dc3fe38cf8be42973ee6e2b3513f1ae98f3a70e174</t>
+          <t>0x20fcd5dbfafe538f08c15c6b35af5d546fa35aa588ef9811c9696ac39843c736</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2474,22 +2426,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>82.86999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Racing Santander +1</t>
+          <t>Deportivo Alaves -0.5</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2499,27 +2451,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xeffd773f9a996fcdab4f40cb833c6db488621204b6af7959d07794c43de040c4</t>
+          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2544,17 +2496,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786621975</t>
+          <t>1786640471</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>112.556862</t>
+          <t>12.195122</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2571,7 +2523,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x4061873586e14d63aeb0e4cdf23afafe5cd7b3c74fe59157daf06c85b8fd8796</t>
+          <t>0x48d06bf1eb103be3b93f605ad7b9ed301f228fa4dfae557dca83434f1d5e0c1a</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2586,12 +2538,12 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>26.96</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -2601,7 +2553,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Racing Santander -0.5</t>
+          <t>Deportivo Alaves -0.5</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2611,27 +2563,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xb811d0e9d1802cd3762a57ca8fc3a5399392dd37dec4f8d9fd37f0170ece0f50</t>
+          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2656,17 +2608,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786621975</t>
+          <t>1786640450</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>146.95082</t>
+          <t>65.957187</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2683,31 +2635,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x8dda40aa7d3c4140b3e5ab6ab62f3db4f5a3730a15ebff80f0bda9807c704ca2</t>
+          <t>0xe750c1fb5c3ef7edfc166b18659be46b00e3cc96d5ae299b162166175d07245f</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>27.87224</t>
+          <t>20.06</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5325</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -2715,27 +2675,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Celta de Vigo vs Osasuna</t>
+          <t>Racing Santander vs Villarreal</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x0f075dae0a586d46b2073e126cbc52393dc2ff99a26953308f94b3b2751764b7</t>
+          <t>0x0a08c3d7f08812839b48fc67d5842cc07f2a5e67ce2a26c46d0210680fda2f99</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19370496</t>
+          <t>L19370490</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2760,17 +2720,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786619056</t>
+          <t>1786639065</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786908600</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>52.342235</t>
+          <t>36.891954</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2787,12 +2747,12 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x4565877a70aabfac9d4d4a2afcda9ace6e304d9bd921ce69a2149c76528e271a</t>
+          <t>0xdc16a40eba6eeb7462531fd3b01240a8f58f0ea20568efbaba25b17131094f2e</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0xb363112BA7ed93A221Efb405496e4Fa3BE119D81</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -2802,12 +2762,12 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.4213</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2817,32 +2777,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>Sevilla vs Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>Rayo Vallecano</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>La Liga</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>Sevilla vs Rayo Vallecano</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Rayo Vallecano</t>
-        </is>
-      </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x2b9c4f75049808a8d2b353d1c6e902da151d2fea092e70f08cdd4ac2ffbfd8a6</t>
+          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2872,7 +2832,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786614389</t>
+          <t>1786633518</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2882,7 +2842,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>175.438596</t>
+          <t>11.869436</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2899,12 +2859,12 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x562837a4689bf537ab0502cfe5d722bafc1833bc972e329ba5399cd7649a219c</t>
+          <t>0x1b67e861f8e383798d979684797f608bfad6122cc87844f2a37a8cf06e019030</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -2914,22 +2874,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>53.83</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2939,27 +2899,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xda132f38d7cbcb404e0db6126292d55c3614e3311c2670ac15890a14a94cdaea</t>
+          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2984,17 +2944,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786586644</t>
+          <t>1786633487</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>7.769231</t>
+          <t>128.166667</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -3011,28 +2971,28 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x27be56be09649bd460766fe27df249788cf4d7ad87d19f5f9a8bfba225e519b9</t>
+          <t>0x909a230aebd5eb00de6012a0eb69301784b515acf69e93ee497d243bd3ce212f</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0xbcD65d7e2D58b95Cf434eB65a82b9FD5b682D144</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>1.52676</t>
+          <t>72.15999</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.7512</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -3058,55 +3018,1975 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
+          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>1786632901</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>120.26665</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>0x081a76991e0701cf3dbcaa6ccbdd7d9dd69242e812c8b7e977517fe836423751</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>7.91</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>1.1038</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Espanyol vs Levante</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>0xd36fc2a623f22222f73350186e7d08c0d31b2d895ac24a68dc8408d4e98bf55a</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>L19370489</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R26" t="inlineStr">
+        <is>
+          <t>1786631513</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>1786899600</t>
+        </is>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>76.240964</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>0x6f1c770a5b9534dbfff85f398a28d171effe0e02699c6558a37a881468f3090e</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>7.91</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>1.1013</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Sevilla vs Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>L19370582</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr">
+        <is>
+          <t>1786631323</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>1786822200</t>
+        </is>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>78.123457</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>0xffde28cdfe7ae2b6324278e8117e605bc5c2ecb236877e683d06b5cbe620b2b1</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>1.165</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr">
+        <is>
+          <t>1786631207</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>67.333333</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>0x1542e94d97dca7a28f2bf2b946f64e1fefc9fc04f50a7622a8a2791d01c58796</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>11.85998</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>1.7113</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr">
+        <is>
+          <t>1786630102</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>16.67484</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>0x9ff18d48c5ac1507ef9b6a3dfaf34f20966e85ee30cbd99e0df47a940abf1d32</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>1.4412</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>0x776caca6c8b9cb32d9a7b2ec2b4f40bbb630001b4db7c24175062af09044b7dd</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr">
+        <is>
+          <t>1786626342</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>11.331445</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>0x50f0b3572b92fd4a3268a217b75ca6b4a52b72077d0276df9d0d123d8b3ebc60</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>16.18903</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>1.4412</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>0x776caca6c8b9cb32d9a7b2ec2b4f40bbb630001b4db7c24175062af09044b7dd</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr">
+        <is>
+          <t>1786626327</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>36.68902</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>0x2d1550913dec85439afda8d85c6033895212998f22943ab968dee5cbd7d7e7a2</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>35.45869</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>1.2537</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>0x0596e7ef887839f51f014583ff32fca0dbfab0916b17c3d05d740985b59eabc3</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>1786624561</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>139.73868</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>0x6f809dd95ba0a7f41584a66e0979cb2c04ebaeefb6e5d949b0bfd9c53278c063</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>1.7163</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>1786623012</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>6.980803</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>0xddff1b4ca7359c6045ede1bd2995e1e57620811dc33cc7338113c5449dccd695</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>28.91904</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>1.6038</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>0xf684bc2655869d0024c7de5a1f2b51fb35813185b075bf3cc8d5f2fe8ce176b5</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R34" t="inlineStr">
+        <is>
+          <t>1786622982</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>47.899031</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>0xb02e365f47ba9eaba62de63e4b14c94bf1b59d60c56188857359df36e7b10ef0</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>30.81465</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>1.7113</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R35" t="inlineStr">
+        <is>
+          <t>1786622982</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>43.32464</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>0xb7f333fbe5a18daf831395020096fbb62febd43977f5f81366c99339b63d902d</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>63.86</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>1.4187</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>Racing Santander vs Villarreal</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>0x1518c9a8caca0376f881601c848e03d81cd65f5d32c2b63a51625351cc193e86</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>L19370490</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R36" t="inlineStr">
+        <is>
+          <t>1786621976</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>1786892400</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>152.501493</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>0x79454b5fc310a342a5ad62ccf677e7ea1c42b0e701cd313d0019ee8ec1faf7a2</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>97.87</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>1.305</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>Racing Santander vs Villarreal</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>0xf9063ec13eee8f96a20b89bd687d0a5f1a3197a4408eb58240f63d72be7c644f</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>L19370490</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R37" t="inlineStr">
+        <is>
+          <t>1786621975</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>1786892400</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>320.885246</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>0x6df789a868c08b6d011dc9dc3fe38cf8be42973ee6e2b3513f1ae98f3a70e174</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>82.86999</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>1.7363</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Racing Santander +1</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>Racing Santander vs Villarreal</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>0xeffd773f9a996fcdab4f40cb833c6db488621204b6af7959d07794c43de040c4</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>L19370490</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R38" t="inlineStr">
+        <is>
+          <t>1786621975</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>1786892400</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>112.556862</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>0x4061873586e14d63aeb0e4cdf23afafe5cd7b3c74fe59157daf06c85b8fd8796</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>44.82</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>1.305</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Racing Santander -0.5</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>Racing Santander vs Villarreal</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>0xb811d0e9d1802cd3762a57ca8fc3a5399392dd37dec4f8d9fd37f0170ece0f50</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>L19370490</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R39" t="inlineStr">
+        <is>
+          <t>1786621975</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>1786892400</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>146.95082</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>0x8dda40aa7d3c4140b3e5ab6ab62f3db4f5a3730a15ebff80f0bda9807c704ca2</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>27.87224</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>1.5325</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>Celta de Vigo vs Osasuna</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Celta de Vigo</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>0x0f075dae0a586d46b2073e126cbc52393dc2ff99a26953308f94b3b2751764b7</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>L19370496</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R40" t="inlineStr">
+        <is>
+          <t>1786619056</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>1786908600</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>52.342235</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>0x4565877a70aabfac9d4d4a2afcda9ace6e304d9bd921ce69a2149c76528e271a</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>0xb363112BA7ed93A221Efb405496e4Fa3BE119D81</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>1.285</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>Sevilla vs Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>0x2b9c4f75049808a8d2b353d1c6e902da151d2fea092e70f08cdd4ac2ffbfd8a6</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>L19370582</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R41" t="inlineStr">
+        <is>
+          <t>1786614389</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>1786822200</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>175.438596</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>0x562837a4689bf537ab0502cfe5d722bafc1833bc972e329ba5399cd7649a219c</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>0xda132f38d7cbcb404e0db6126292d55c3614e3311c2670ac15890a14a94cdaea</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R42" t="inlineStr">
+        <is>
+          <t>1786586644</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>7.769231</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>0x27be56be09649bd460766fe27df249788cf4d7ad87d19f5f9a8bfba225e519b9</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>1.52676</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>1.7512</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
           <t>0x32766ed977cae312bdb45c44b07e70207b356db986ef0293796496f193e13d1e</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>L19370598</t>
         </is>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" t="inlineStr">
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
         <is>
           <t>1786578252</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr">
+      <c r="S43" t="inlineStr">
         <is>
           <t>1786815000</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr">
+      <c r="T43" t="inlineStr">
         <is>
           <t>2.032293</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr">
+      <c r="U43" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V25" t="inlineStr">
+      <c r="V43" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/La Liga/trades.xlsx
+++ b/data/sxbet/ligas/La Liga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V43"/>
+  <dimension ref="A1:V46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x11476693f9b725995aedcf0e75acf05d19a0f1647da3059f334da311f0f1e922</t>
+          <t>0xec715718ce1e06f5bfd1790eedf07c987dbe7e219a72c5facd15377495db5263</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.19253</t>
+          <t>122.1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5713</t>
+          <t>1.165</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x10c92f089fb69109ac5beea7c82a0e1cd2f23257cd842348710e2598be68bc48</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786664168</t>
+          <t>1786676253</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2.08758</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,23 +635,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x046492cfcbf4e5a3ced4caa85326fa8b44dbff1fb248a61a7fa6c8a8d2d9c1f8</t>
+          <t>0x0e7729ad6b4a9824864f6ac006c58fb19124ac050b08faef247ac7a176fd96ee</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xB66Aa9923E7a8920151375e186E6718064dd4f08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>245.05482</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5962</t>
+          <t>1.755</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xfcdcf41a0510583d5bb65df7215b5101ff435808043952db2a0364f1424743db</t>
+          <t>0x32766ed977cae312bdb45c44b07e70207b356db986ef0293796496f193e13d1e</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786663762</t>
+          <t>1786669488</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -722,7 +722,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>8.385744</t>
+          <t>324.575921</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,28 +739,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0xe376b22b83ba1a0d5c58e6763337d61f4445c85bfdc77949472d41c7c47e42b6</t>
+          <t>0x8d79a50b7331e59ea36d27efa5d99d53e26dfd1be15401e254a4cc43e280ff2f</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
+          <t>0x9737E0E3E8EE2DD6B8A7E19D1507EcB3221b5483</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>4.89999</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.5863</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -771,27 +771,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Celta de Vigo vs Osasuna</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19370496</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -816,17 +816,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786657450</t>
+          <t>1786667446</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786908600</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>8.358192</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,27 +843,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x4e949c2076e8faf4dcc272acfa8d69c62442324aca8ceeb5820b8348c74f13f6</t>
+          <t>0x11476693f9b725995aedcf0e75acf05d19a0f1647da3059f334da311f0f1e922</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>1.19253</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.5713</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -871,11 +867,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -883,27 +875,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Celta de Vigo vs Osasuna</t>
+          <t>Racing Santander vs Villarreal</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
+          <t>0x10c92f089fb69109ac5beea7c82a0e1cd2f23257cd842348710e2598be68bc48</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19370496</t>
+          <t>L19370490</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -928,17 +920,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786657449</t>
+          <t>1786664168</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786908600</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>52.967742</t>
+          <t>2.08758</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,7 +947,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0xd54151c9cd066d8a5e7714f77ebc5e24ee2aac3e2c8a52a50b3a6becd0bac875</t>
+          <t>0x046492cfcbf4e5a3ced4caa85326fa8b44dbff1fb248a61a7fa6c8a8d2d9c1f8</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -966,12 +958,12 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>112.94</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.6625</t>
+          <t>1.5962</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1002,7 +994,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x78a4cf6b02d047f006e2c80b80d1bba724ebd9a508d0cce70fc13d1dcc698bd3</t>
+          <t>0xfcdcf41a0510583d5bb65df7215b5101ff435808043952db2a0364f1424743db</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1032,7 +1024,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786656774</t>
+          <t>1786663762</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1042,7 +1034,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>170.475472</t>
+          <t>8.385744</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,28 +1051,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x835c08ffc86c9c616d8c107e844ff9658b10b62372398122a4f7ded5bb28a516</t>
+          <t>0xe376b22b83ba1a0d5c58e6763337d61f4445c85bfdc77949472d41c7c47e42b6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0x8e9bE2B8b636Cc98b01957cE9D4E3B62cF579080</t>
+          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1091,27 +1083,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Celta de Vigo vs Osasuna</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370496</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1136,17 +1128,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786651844</t>
+          <t>1786657450</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786908600</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>8.492552</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,31 +1155,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x45cc84f2dd4c1b45226a895eead76c109d5af22eac83562ab8aa23758f8a6b5e</t>
+          <t>0x4e949c2076e8faf4dcc272acfa8d69c62442324aca8ceeb5820b8348c74f13f6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xa3786b93377213A42Bf1d3261d373cE67Cf2AA67</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -1195,27 +1195,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Celta de Vigo vs Osasuna</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370496</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1240,17 +1240,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786651814</t>
+          <t>1786657449</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786908600</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>42.735043</t>
+          <t>52.967742</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,23 +1267,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x213398a7cadc42743f3aee31a89c45cc1f9c78136646bd816983864c34b13f79</t>
+          <t>0xd54151c9cd066d8a5e7714f77ebc5e24ee2aac3e2c8a52a50b3a6becd0bac875</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x4feB57379592eb94c51c014553de6EEbD4d42577</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>112.94</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.6625</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1299,27 +1299,27 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Celta de Vigo vs Osasuna</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
+          <t>0x78a4cf6b02d047f006e2c80b80d1bba724ebd9a508d0cce70fc13d1dcc698bd3</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>L19370496</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786651743</t>
+          <t>1786656774</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>1786908600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>170.475472</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1371,12 +1371,12 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x0adf7a0f94fb74bebb4e5acb49582e1f91e3ae462b204becaedfbe0f50714ede</t>
+          <t>0x835c08ffc86c9c616d8c107e844ff9658b10b62372398122a4f7ded5bb28a516</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x06a603b688E676702ec63D735CAe4A57ff71B3e1</t>
+          <t>0x8e9bE2B8b636Cc98b01957cE9D4E3B62cF579080</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786651718</t>
+          <t>1786651844</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>8.546991</t>
+          <t>8.492552</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1475,18 +1475,18 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0xc33e951dfa8d84c01759f86fe63dfc68ddc2b547988e3a32445d72b681f7f7a5</t>
+          <t>0x45cc84f2dd4c1b45226a895eead76c109d5af22eac83562ab8aa23758f8a6b5e</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
+          <t>0xa3786b93377213A42Bf1d3261d373cE67Cf2AA67</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786651637</t>
+          <t>1786651814</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -1562,7 +1562,7 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>8.546991</t>
+          <t>42.735043</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1579,28 +1579,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x948b3c3ece530e62252af65b92bdd73725833fe7355d5496ab1d4f6d84e43cc4</t>
+          <t>0x213398a7cadc42743f3aee31a89c45cc1f9c78136646bd816983864c34b13f79</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
+          <t>0x4feB57379592eb94c51c014553de6EEbD4d42577</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1611,27 +1611,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Celta de Vigo vs Osasuna</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370496</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1656,17 +1656,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786651588</t>
+          <t>1786651743</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786908600</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>1.709402</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1683,18 +1683,18 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x7578c65431424d3ae35de659ad6d246a7814cbb553d85319bf0968700f7bca4a</t>
+          <t>0x0adf7a0f94fb74bebb4e5acb49582e1f91e3ae462b204becaedfbe0f50714ede</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+          <t>0x06a603b688E676702ec63D735CAe4A57ff71B3e1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786651585</t>
+          <t>1786651718</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>17.094</t>
+          <t>8.546991</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1787,18 +1787,18 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x28bc2779df67c8165804579669b7a40ef9e3a34f89e4d9d4c81a44f6c49d8be2</t>
+          <t>0xc33e951dfa8d84c01759f86fe63dfc68ddc2b547988e3a32445d72b681f7f7a5</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x2F9aCBd9B89C6eF3bc3Dc2B0F0cCD0E0936BF912</t>
+          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1864,7 +1864,7 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786651567</t>
+          <t>1786651637</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>17.094</t>
+          <t>8.546991</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1891,18 +1891,18 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x0eaa76f318c30c9b01a36fedfdc1b48daafadd063ed5c90a74fd0908bdecfce3</t>
+          <t>0x948b3c3ece530e62252af65b92bdd73725833fe7355d5496ab1d4f6d84e43cc4</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x6203b6338991Ec84C8A8f5ef06bC17ceB1395Ddb</t>
+          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1968,7 +1968,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786651567</t>
+          <t>1786651588</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>11.965812</t>
+          <t>1.709402</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1995,18 +1995,18 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xcc54eb94d459bc0b9a34beb78c07fafbc7c1f3e7c6d43846f17fb20856c43d24</t>
+          <t>0x7578c65431424d3ae35de659ad6d246a7814cbb553d85319bf0968700f7bca4a</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786651559</t>
+          <t>1786651585</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2082,7 +2082,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>42.735043</t>
+          <t>17.094</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2099,12 +2099,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x1b14ab3ce842bb0ded035add24fcdd28a77380141c189ae36b1f623e70dff465</t>
+          <t>0x28bc2779df67c8165804579669b7a40ef9e3a34f89e4d9d4c81a44f6c49d8be2</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+          <t>0x2F9aCBd9B89C6eF3bc3Dc2B0F0cCD0E0936BF912</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786651559</t>
+          <t>1786651567</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2203,18 +2203,18 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x31a8e64cfb4307b5b608318a4e037810f68fe9bef13258aa7d3c45dd664c0ad3</t>
+          <t>0x0eaa76f318c30c9b01a36fedfdc1b48daafadd063ed5c90a74fd0908bdecfce3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x03d4fFC791EE4A80194C9d9782E7D56407b242Ed</t>
+          <t>0x6203b6338991Ec84C8A8f5ef06bC17ceB1395Ddb</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2280,7 +2280,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786651558</t>
+          <t>1786651567</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2290,7 +2290,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>25.641026</t>
+          <t>11.965812</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2307,18 +2307,18 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x1c244dc1d052ae42a83bf5640bcba1b28bb9c28853e7f42713fa4fddcb66b677</t>
+          <t>0xcc54eb94d459bc0b9a34beb78c07fafbc7c1f3e7c6d43846f17fb20856c43d24</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2384,7 +2384,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786651550</t>
+          <t>1786651559</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>8.546991</t>
+          <t>42.735043</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2411,39 +2411,31 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x20fcd5dbfafe538f08c15c6b35af5d546fa35aa588ef9811c9696ac39843c736</t>
+          <t>0x1b14ab3ce842bb0ded035add24fcdd28a77380141c189ae36b1f623e70dff465</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>Deportivo Alaves -0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -2451,27 +2443,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2496,17 +2488,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786640471</t>
+          <t>1786651559</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>12.195122</t>
+          <t>17.094</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2523,39 +2515,31 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x48d06bf1eb103be3b93f605ad7b9ed301f228fa4dfae557dca83434f1d5e0c1a</t>
+          <t>0x31a8e64cfb4307b5b608318a4e037810f68fe9bef13258aa7d3c45dd664c0ad3</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x03d4fFC791EE4A80194C9d9782E7D56407b242Ed</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>26.96</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Deportivo Alaves -0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -2563,27 +2547,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2608,17 +2592,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786640450</t>
+          <t>1786651558</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>65.957187</t>
+          <t>25.641026</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2635,27 +2619,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0xe750c1fb5c3ef7edfc166b18659be46b00e3cc96d5ae299b162166175d07245f</t>
+          <t>0x1c244dc1d052ae42a83bf5640bcba1b28bb9c28853e7f42713fa4fddcb66b677</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2663,11 +2643,7 @@
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -2675,27 +2651,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x0a08c3d7f08812839b48fc67d5842cc07f2a5e67ce2a26c46d0210680fda2f99</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2720,17 +2696,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786639065</t>
+          <t>1786651550</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>36.891954</t>
+          <t>8.546991</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2747,7 +2723,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xdc16a40eba6eeb7462531fd3b01240a8f58f0ea20568efbaba25b17131094f2e</t>
+          <t>0x20fcd5dbfafe538f08c15c6b35af5d546fa35aa588ef9811c9696ac39843c736</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2767,17 +2743,17 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.4213</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves -0.5</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2787,27 +2763,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
+          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2832,17 +2808,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786633518</t>
+          <t>1786640471</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>11.869436</t>
+          <t>12.195122</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2859,7 +2835,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x1b67e861f8e383798d979684797f608bfad6122cc87844f2a37a8cf06e019030</t>
+          <t>0x48d06bf1eb103be3b93f605ad7b9ed301f228fa4dfae557dca83434f1d5e0c1a</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2874,22 +2850,22 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>53.83</t>
+          <t>26.96</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves -0.5</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2899,27 +2875,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
+          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2944,17 +2920,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786633487</t>
+          <t>1786640450</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>128.166667</t>
+          <t>65.957187</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2971,31 +2947,39 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x909a230aebd5eb00de6012a0eb69301784b515acf69e93ee497d243bd3ce212f</t>
+          <t>0xe750c1fb5c3ef7edfc166b18659be46b00e3cc96d5ae299b162166175d07245f</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xbcD65d7e2D58b95Cf434eB65a82b9FD5b682D144</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>72.15999</t>
+          <t>20.06</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -3003,27 +2987,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Racing Santander vs Villarreal</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
+          <t>0x0a08c3d7f08812839b48fc67d5842cc07f2a5e67ce2a26c46d0210680fda2f99</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370490</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3048,17 +3032,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786632901</t>
+          <t>1786639065</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>120.26665</t>
+          <t>36.891954</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3075,31 +3059,39 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x081a76991e0701cf3dbcaa6ccbdd7d9dd69242e812c8b7e977517fe836423751</t>
+          <t>0xdc16a40eba6eeb7462531fd3b01240a8f58f0ea20568efbaba25b17131094f2e</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.1038</t>
+          <t>1.4213</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -3107,27 +3099,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Espanyol vs Levante</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xd36fc2a623f22222f73350186e7d08c0d31b2d895ac24a68dc8408d4e98bf55a</t>
+          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19370489</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3152,17 +3144,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786631513</t>
+          <t>1786633518</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>76.240964</t>
+          <t>11.869436</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3179,31 +3171,39 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x6f1c770a5b9534dbfff85f398a28d171effe0e02699c6558a37a881468f3090e</t>
+          <t>0x1b67e861f8e383798d979684797f608bfad6122cc87844f2a37a8cf06e019030</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>53.83</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.1013</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
+          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786631323</t>
+          <t>1786633487</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3266,7 +3266,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>78.123457</t>
+          <t>128.166667</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3283,28 +3283,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xffde28cdfe7ae2b6324278e8117e605bc5c2ecb236877e683d06b5cbe620b2b1</t>
+          <t>0x909a230aebd5eb00de6012a0eb69301784b515acf69e93ee497d243bd3ce212f</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xbcD65d7e2D58b95Cf434eB65a82b9FD5b682D144</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>72.15999</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3330,7 +3330,7 @@
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
+          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -3360,7 +3360,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786631207</t>
+          <t>1786632901</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>67.333333</t>
+          <t>120.26665</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3387,7 +3387,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x1542e94d97dca7a28f2bf2b946f64e1fefc9fc04f50a7622a8a2791d01c58796</t>
+          <t>0x081a76991e0701cf3dbcaa6ccbdd7d9dd69242e812c8b7e977517fe836423751</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3398,17 +3398,17 @@
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>11.85998</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.7113</t>
+          <t>1.1038</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3419,27 +3419,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Espanyol vs Levante</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
+          <t>0xd36fc2a623f22222f73350186e7d08c0d31b2d895ac24a68dc8408d4e98bf55a</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370489</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3464,17 +3464,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786630102</t>
+          <t>1786631513</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>16.67484</t>
+          <t>76.240964</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3491,28 +3491,28 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x9ff18d48c5ac1507ef9b6a3dfaf34f20966e85ee30cbd99e0df47a940abf1d32</t>
+          <t>0x6f1c770a5b9534dbfff85f398a28d171effe0e02699c6558a37a881468f3090e</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.4412</t>
+          <t>1.1013</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3523,27 +3523,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x776caca6c8b9cb32d9a7b2ec2b4f40bbb630001b4db7c24175062af09044b7dd</t>
+          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3568,17 +3568,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786626342</t>
+          <t>1786631323</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>11.331445</t>
+          <t>78.123457</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3595,28 +3595,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x50f0b3572b92fd4a3268a217b75ca6b4a52b72077d0276df9d0d123d8b3ebc60</t>
+          <t>0xffde28cdfe7ae2b6324278e8117e605bc5c2ecb236877e683d06b5cbe620b2b1</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>16.18903</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.4412</t>
+          <t>1.165</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3642,7 +3642,7 @@
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x776caca6c8b9cb32d9a7b2ec2b4f40bbb630001b4db7c24175062af09044b7dd</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -3672,7 +3672,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786626327</t>
+          <t>1786631207</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3682,7 +3682,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>36.68902</t>
+          <t>67.333333</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3699,28 +3699,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x2d1550913dec85439afda8d85c6033895212998f22943ab968dee5cbd7d7e7a2</t>
+          <t>0x1542e94d97dca7a28f2bf2b946f64e1fefc9fc04f50a7622a8a2791d01c58796</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>35.45869</t>
+          <t>11.85998</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.2537</t>
+          <t>1.7113</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3746,7 +3746,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x0596e7ef887839f51f014583ff32fca0dbfab0916b17c3d05d740985b59eabc3</t>
+          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786624561</t>
+          <t>1786630102</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>139.73868</t>
+          <t>16.67484</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3803,7 +3803,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x6f809dd95ba0a7f41584a66e0979cb2c04ebaeefb6e5d949b0bfd9c53278c063</t>
+          <t>0x9ff18d48c5ac1507ef9b6a3dfaf34f20966e85ee30cbd99e0df47a940abf1d32</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3819,12 +3819,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.7163</t>
+          <t>1.4412</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -3850,7 +3850,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
+          <t>0x776caca6c8b9cb32d9a7b2ec2b4f40bbb630001b4db7c24175062af09044b7dd</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3880,7 +3880,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786623012</t>
+          <t>1786626342</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3890,7 +3890,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>6.980803</t>
+          <t>11.331445</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3907,7 +3907,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0xddff1b4ca7359c6045ede1bd2995e1e57620811dc33cc7338113c5449dccd695</t>
+          <t>0x50f0b3572b92fd4a3268a217b75ca6b4a52b72077d0276df9d0d123d8b3ebc60</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3918,17 +3918,17 @@
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>28.91904</t>
+          <t>16.18903</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.4412</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3954,7 +3954,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xf684bc2655869d0024c7de5a1f2b51fb35813185b075bf3cc8d5f2fe8ce176b5</t>
+          <t>0x776caca6c8b9cb32d9a7b2ec2b4f40bbb630001b4db7c24175062af09044b7dd</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786622982</t>
+          <t>1786626327</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>47.899031</t>
+          <t>36.68902</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4011,7 +4011,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0xb02e365f47ba9eaba62de63e4b14c94bf1b59d60c56188857359df36e7b10ef0</t>
+          <t>0x2d1550913dec85439afda8d85c6033895212998f22943ab968dee5cbd7d7e7a2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4022,17 +4022,17 @@
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>30.81465</t>
+          <t>35.45869</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.7113</t>
+          <t>1.2537</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
+          <t>0x0596e7ef887839f51f014583ff32fca0dbfab0916b17c3d05d740985b59eabc3</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4088,7 +4088,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786622982</t>
+          <t>1786624561</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>43.32464</t>
+          <t>139.73868</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4115,67 +4115,59 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xb7f333fbe5a18daf831395020096fbb62febd43977f5f81366c99339b63d902d</t>
+          <t>0x6f809dd95ba0a7f41584a66e0979cb2c04ebaeefb6e5d949b0bfd9c53278c063</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>63.86</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.7163</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr">
+        <is>
           <t>La Liga</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Racing Santander</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>La Liga</t>
-        </is>
-      </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x1518c9a8caca0376f881601c848e03d81cd65f5d32c2b63a51625351cc193e86</t>
+          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4200,17 +4192,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786621976</t>
+          <t>1786623012</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>152.501493</t>
+          <t>6.980803</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4227,7 +4219,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x79454b5fc310a342a5ad62ccf677e7ea1c42b0e701cd313d0019ee8ec1faf7a2</t>
+          <t>0xddff1b4ca7359c6045ede1bd2995e1e57620811dc33cc7338113c5449dccd695</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4235,31 +4227,23 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>97.87</t>
+          <t>28.91904</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Racing Santander</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -4267,27 +4251,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xf9063ec13eee8f96a20b89bd687d0a5f1a3197a4408eb58240f63d72be7c644f</t>
+          <t>0xf684bc2655869d0024c7de5a1f2b51fb35813185b075bf3cc8d5f2fe8ce176b5</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4312,17 +4296,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786621975</t>
+          <t>1786622982</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>320.885246</t>
+          <t>47.899031</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4339,7 +4323,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x6df789a868c08b6d011dc9dc3fe38cf8be42973ee6e2b3513f1ae98f3a70e174</t>
+          <t>0xb02e365f47ba9eaba62de63e4b14c94bf1b59d60c56188857359df36e7b10ef0</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4347,31 +4331,23 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>82.86999</t>
+          <t>30.81465</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.7113</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Racing Santander +1</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -4379,27 +4355,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xeffd773f9a996fcdab4f40cb833c6db488621204b6af7959d07794c43de040c4</t>
+          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4424,17 +4400,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786621975</t>
+          <t>1786622982</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>112.556862</t>
+          <t>43.32464</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4451,7 +4427,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x4061873586e14d63aeb0e4cdf23afafe5cd7b3c74fe59157daf06c85b8fd8796</t>
+          <t>0xb7f333fbe5a18daf831395020096fbb62febd43977f5f81366c99339b63d902d</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4466,22 +4442,22 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>63.86</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>1.4187</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>La Liga</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Racing Santander -0.5</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -4506,7 +4482,7 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xb811d0e9d1802cd3762a57ca8fc3a5399392dd37dec4f8d9fd37f0170ece0f50</t>
+          <t>0x1518c9a8caca0376f881601c848e03d81cd65f5d32c2b63a51625351cc193e86</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -4536,7 +4512,7 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786621975</t>
+          <t>1786621976</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
@@ -4546,7 +4522,7 @@
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>146.95082</t>
+          <t>152.501493</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4563,7 +4539,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x8dda40aa7d3c4140b3e5ab6ab62f3db4f5a3730a15ebff80f0bda9807c704ca2</t>
+          <t>0x79454b5fc310a342a5ad62ccf677e7ea1c42b0e701cd313d0019ee8ec1faf7a2</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4571,15 +4547,19 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr"/>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>27.87224</t>
+          <t>97.87</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.5325</t>
+          <t>1.305</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4587,7 +4567,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -4595,27 +4579,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Celta de Vigo vs Osasuna</t>
+          <t>Racing Santander vs Villarreal</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x0f075dae0a586d46b2073e126cbc52393dc2ff99a26953308f94b3b2751764b7</t>
+          <t>0xf9063ec13eee8f96a20b89bd687d0a5f1a3197a4408eb58240f63d72be7c644f</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19370496</t>
+          <t>L19370490</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4640,17 +4624,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786619056</t>
+          <t>1786621975</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1786908600</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>52.342235</t>
+          <t>320.885246</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4667,12 +4651,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x4565877a70aabfac9d4d4a2afcda9ace6e304d9bd921ce69a2149c76528e271a</t>
+          <t>0x6df789a868c08b6d011dc9dc3fe38cf8be42973ee6e2b3513f1ae98f3a70e174</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0xb363112BA7ed93A221Efb405496e4Fa3BE119D81</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -4682,22 +4666,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>82.86999</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (1)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Racing Santander +1</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4707,27 +4691,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Racing Santander vs Villarreal</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x2b9c4f75049808a8d2b353d1c6e902da151d2fea092e70f08cdd4ac2ffbfd8a6</t>
+          <t>0xeffd773f9a996fcdab4f40cb833c6db488621204b6af7959d07794c43de040c4</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370490</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4752,17 +4736,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786614389</t>
+          <t>1786621975</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>175.438596</t>
+          <t>112.556862</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4779,12 +4763,12 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x562837a4689bf537ab0502cfe5d722bafc1833bc972e329ba5399cd7649a219c</t>
+          <t>0x4061873586e14d63aeb0e4cdf23afafe5cd7b3c74fe59157daf06c85b8fd8796</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -4794,22 +4778,22 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>44.82</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.305</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Racing Santander -0.5</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4819,27 +4803,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Racing Santander vs Villarreal</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0xda132f38d7cbcb404e0db6126292d55c3614e3311c2670ac15890a14a94cdaea</t>
+          <t>0xb811d0e9d1802cd3762a57ca8fc3a5399392dd37dec4f8d9fd37f0170ece0f50</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370490</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4864,17 +4848,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786586644</t>
+          <t>1786621975</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>7.769231</t>
+          <t>146.95082</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4891,23 +4875,23 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x27be56be09649bd460766fe27df249788cf4d7ad87d19f5f9a8bfba225e519b9</t>
+          <t>0x8dda40aa7d3c4140b3e5ab6ab62f3db4f5a3730a15ebff80f0bda9807c704ca2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>1.52676</t>
+          <t>27.87224</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.7512</t>
+          <t>1.5325</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4923,70 +4907,398 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
+          <t>Celta de Vigo vs Osasuna</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Celta de Vigo</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>0x0f075dae0a586d46b2073e126cbc52393dc2ff99a26953308f94b3b2751764b7</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>L19370496</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R43" t="inlineStr">
+        <is>
+          <t>1786619056</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>1786908600</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>52.342235</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>0x4565877a70aabfac9d4d4a2afcda9ace6e304d9bd921ce69a2149c76528e271a</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>0xb363112BA7ed93A221Efb405496e4Fa3BE119D81</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>1.285</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>Sevilla vs Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>0x2b9c4f75049808a8d2b353d1c6e902da151d2fea092e70f08cdd4ac2ffbfd8a6</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>L19370582</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R44" t="inlineStr">
+        <is>
+          <t>1786614389</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>1786822200</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>175.438596</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>0x562837a4689bf537ab0502cfe5d722bafc1833bc972e329ba5399cd7649a219c</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
           <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr">
+      <c r="J45" t="inlineStr">
         <is>
           <t>Deportivo Alaves</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="K45" t="inlineStr">
         <is>
           <t>Getafe</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>0xda132f38d7cbcb404e0db6126292d55c3614e3311c2670ac15890a14a94cdaea</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>1786586644</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>7.769231</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>0x27be56be09649bd460766fe27df249788cf4d7ad87d19f5f9a8bfba225e519b9</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1.52676</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.7512</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
         <is>
           <t>0x32766ed977cae312bdb45c44b07e70207b356db986ef0293796496f193e13d1e</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>L19370598</t>
         </is>
       </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R43" t="inlineStr">
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
         <is>
           <t>1786578252</t>
         </is>
       </c>
-      <c r="S43" t="inlineStr">
+      <c r="S46" t="inlineStr">
         <is>
           <t>1786815000</t>
         </is>
       </c>
-      <c r="T43" t="inlineStr">
+      <c r="T46" t="inlineStr">
         <is>
           <t>2.032293</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr">
+      <c r="U46" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V43" t="inlineStr">
+      <c r="V46" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/La Liga/trades.xlsx
+++ b/data/sxbet/ligas/La Liga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V46"/>
+  <dimension ref="A1:V52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,28 +531,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xec715718ce1e06f5bfd1790eedf07c987dbe7e219a72c5facd15377495db5263</t>
+          <t>0xbf1a151f615bf3f9a9e616e3c50bbe9cfcae4e7a99f9ce723f49c93c83cdc9d0</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
+          <t>0x30E3f83573EbFc7274EeAfD586D930F7392F5650</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>122.1</t>
+          <t>1.16999</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>1.5875</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -563,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786676253</t>
+          <t>1786687820</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>1.991472</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,23 +635,27 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x0e7729ad6b4a9824864f6ac006c58fb19124ac050b08faef247ac7a176fd96ee</t>
+          <t>0x11994251df996a13dca305742c6cfa502ae27aa5f4bd0111f29dc7341166926a</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xB66Aa9923E7a8920151375e186E6718064dd4f08</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>0xdFC5342F5d4bF9F317c0CBf71121AC6FA92d8fbf</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>245.05482</t>
+          <t>45.715</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.755</t>
+          <t>1.2788</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -659,7 +663,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -667,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Celta de Vigo vs Osasuna</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x32766ed977cae312bdb45c44b07e70207b356db986ef0293796496f193e13d1e</t>
+          <t>0x9993d963f79cc9f688d38136ed8af60ad8c5e128ae668d0af49645c4ec2e0c25</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370496</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -712,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786669488</t>
+          <t>1786684730</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786908600</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>324.575921</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -739,28 +747,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x8d79a50b7331e59ea36d27efa5d99d53e26dfd1be15401e254a4cc43e280ff2f</t>
+          <t>0x03eaa48ad5cba7703834b4eb4188b2512fc59fc66ce1a132f347fb208e62190e</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0x9737E0E3E8EE2DD6B8A7E19D1507EcB3221b5483</t>
+          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>4.89999</t>
+          <t>29.16362</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.5863</t>
+          <t>1.1075</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -786,7 +794,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -816,7 +824,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786667446</t>
+          <t>1786684614</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -826,7 +834,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>8.358192</t>
+          <t>271.289488</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -843,28 +851,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x11476693f9b725995aedcf0e75acf05d19a0f1647da3059f334da311f0f1e922</t>
+          <t>0xf7320171cfa1d2a4388cf7700c275208ec77d1f0986bae7466346769cb38d5b4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.19253</t>
+          <t>1.05797</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.5713</t>
+          <t>1.1075</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -875,27 +883,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x10c92f089fb69109ac5beea7c82a0e1cd2f23257cd842348710e2598be68bc48</t>
+          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -920,17 +928,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786664168</t>
+          <t>1786684161</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>2.08758</t>
+          <t>9.841581</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -947,28 +955,28 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x046492cfcbf4e5a3ced4caa85326fa8b44dbff1fb248a61a7fa6c8a8d2d9c1f8</t>
+          <t>0x2c667f7cd0a5ee4597a318320db656e61b2fe595b68044cdbb02a35a2c508f11</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>122.1</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5962</t>
+          <t>1.165</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr"/>
@@ -994,7 +1002,7 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xfcdcf41a0510583d5bb65df7215b5101ff435808043952db2a0364f1424743db</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -1024,7 +1032,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786663762</t>
+          <t>1786679771</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1034,7 +1042,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>8.385744</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1051,28 +1059,28 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xe376b22b83ba1a0d5c58e6763337d61f4445c85bfdc77949472d41c7c47e42b6</t>
+          <t>0xef898b845c993efce01f949a5b4165e91083d76283cd50b5ccb38113072d39a3</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
+          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>122.1</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.165</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G7" t="inlineStr"/>
@@ -1083,27 +1091,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Celta de Vigo vs Osasuna</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19370496</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1128,17 +1136,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786657450</t>
+          <t>1786677944</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786908600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1155,39 +1163,31 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x4e949c2076e8faf4dcc272acfa8d69c62442324aca8ceeb5820b8348c74f13f6</t>
+          <t>0xec715718ce1e06f5bfd1790eedf07c987dbe7e219a72c5facd15377495db5263</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>122.1</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.165</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -1195,27 +1195,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Celta de Vigo vs Osasuna</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19370496</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1240,17 +1240,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786657449</t>
+          <t>1786676253</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786908600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>52.967742</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,23 +1267,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0xd54151c9cd066d8a5e7714f77ebc5e24ee2aac3e2c8a52a50b3a6becd0bac875</t>
+          <t>0x0e7729ad6b4a9824864f6ac006c58fb19124ac050b08faef247ac7a176fd96ee</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xB66Aa9923E7a8920151375e186E6718064dd4f08</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>112.94</t>
+          <t>245.05482</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.6625</t>
+          <t>1.755</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x78a4cf6b02d047f006e2c80b80d1bba724ebd9a508d0cce70fc13d1dcc698bd3</t>
+          <t>0x32766ed977cae312bdb45c44b07e70207b356db986ef0293796496f193e13d1e</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786656774</t>
+          <t>1786669488</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>170.475472</t>
+          <t>324.575921</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1371,23 +1371,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x835c08ffc86c9c616d8c107e844ff9658b10b62372398122a4f7ded5bb28a516</t>
+          <t>0x8d79a50b7331e59ea36d27efa5d99d53e26dfd1be15401e254a4cc43e280ff2f</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x8e9bE2B8b636Cc98b01957cE9D4E3B62cF579080</t>
+          <t>0x9737E0E3E8EE2DD6B8A7E19D1507EcB3221b5483</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>4.89999</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.5863</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1448,7 +1448,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786651844</t>
+          <t>1786667446</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>8.492552</t>
+          <t>8.358192</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1475,28 +1475,28 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x45cc84f2dd4c1b45226a895eead76c109d5af22eac83562ab8aa23758f8a6b5e</t>
+          <t>0x11476693f9b725995aedcf0e75acf05d19a0f1647da3059f334da311f0f1e922</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xa3786b93377213A42Bf1d3261d373cE67Cf2AA67</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1.19253</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.5713</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -1507,27 +1507,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Racing Santander vs Villarreal</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0x10c92f089fb69109ac5beea7c82a0e1cd2f23257cd842348710e2598be68bc48</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370490</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1552,17 +1552,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786651814</t>
+          <t>1786664168</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>42.735043</t>
+          <t>2.08758</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1579,23 +1579,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x213398a7cadc42743f3aee31a89c45cc1f9c78136646bd816983864c34b13f79</t>
+          <t>0x046492cfcbf4e5a3ced4caa85326fa8b44dbff1fb248a61a7fa6c8a8d2d9c1f8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x4feB57379592eb94c51c014553de6EEbD4d42577</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.5962</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1611,27 +1611,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Celta de Vigo vs Osasuna</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
+          <t>0xfcdcf41a0510583d5bb65df7215b5101ff435808043952db2a0364f1424743db</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19370496</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1656,17 +1656,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786651743</t>
+          <t>1786663762</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786908600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>8.385744</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1683,28 +1683,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0x0adf7a0f94fb74bebb4e5acb49582e1f91e3ae462b204becaedfbe0f50714ede</t>
+          <t>0xe376b22b83ba1a0d5c58e6763337d61f4445c85bfdc77949472d41c7c47e42b6</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x06a603b688E676702ec63D735CAe4A57ff71B3e1</t>
+          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1715,27 +1715,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Celta de Vigo vs Osasuna</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370496</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1760,17 +1760,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786651718</t>
+          <t>1786657450</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786908600</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>8.546991</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1787,31 +1787,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0xc33e951dfa8d84c01759f86fe63dfc68ddc2b547988e3a32445d72b681f7f7a5</t>
+          <t>0x4e949c2076e8faf4dcc272acfa8d69c62442324aca8ceeb5820b8348c74f13f6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -1819,27 +1827,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Celta de Vigo vs Osasuna</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370496</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1864,17 +1872,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786651637</t>
+          <t>1786657449</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786908600</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>8.546991</t>
+          <t>52.967742</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1891,28 +1899,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x948b3c3ece530e62252af65b92bdd73725833fe7355d5496ab1d4f6d84e43cc4</t>
+          <t>0xd54151c9cd066d8a5e7714f77ebc5e24ee2aac3e2c8a52a50b3a6becd0bac875</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>112.94</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.6625</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1923,27 +1931,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0x78a4cf6b02d047f006e2c80b80d1bba724ebd9a508d0cce70fc13d1dcc698bd3</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1968,17 +1976,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786651588</t>
+          <t>1786656774</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>1.709402</t>
+          <t>170.475472</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -1995,23 +2003,23 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x7578c65431424d3ae35de659ad6d246a7814cbb553d85319bf0968700f7bca4a</t>
+          <t>0x835c08ffc86c9c616d8c107e844ff9658b10b62372398122a4f7ded5bb28a516</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+          <t>0x8e9bE2B8b636Cc98b01957cE9D4E3B62cF579080</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2072,7 +2080,7 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786651585</t>
+          <t>1786651844</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
@@ -2082,7 +2090,7 @@
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>17.094</t>
+          <t>8.492552</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2099,18 +2107,18 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x28bc2779df67c8165804579669b7a40ef9e3a34f89e4d9d4c81a44f6c49d8be2</t>
+          <t>0x45cc84f2dd4c1b45226a895eead76c109d5af22eac83562ab8aa23758f8a6b5e</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0x2F9aCBd9B89C6eF3bc3Dc2B0F0cCD0E0936BF912</t>
+          <t>0xa3786b93377213A42Bf1d3261d373cE67Cf2AA67</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2176,7 +2184,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786651567</t>
+          <t>1786651814</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2186,7 +2194,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>17.094</t>
+          <t>42.735043</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2203,28 +2211,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x0eaa76f318c30c9b01a36fedfdc1b48daafadd063ed5c90a74fd0908bdecfce3</t>
+          <t>0x213398a7cadc42743f3aee31a89c45cc1f9c78136646bd816983864c34b13f79</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x6203b6338991Ec84C8A8f5ef06bC17ceB1395Ddb</t>
+          <t>0x4feB57379592eb94c51c014553de6EEbD4d42577</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2235,27 +2243,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Celta de Vigo vs Osasuna</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370496</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2280,17 +2288,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786651567</t>
+          <t>1786651743</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786908600</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>11.965812</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2307,18 +2315,18 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xcc54eb94d459bc0b9a34beb78c07fafbc7c1f3e7c6d43846f17fb20856c43d24</t>
+          <t>0x0adf7a0f94fb74bebb4e5acb49582e1f91e3ae462b204becaedfbe0f50714ede</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+          <t>0x06a603b688E676702ec63D735CAe4A57ff71B3e1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2384,7 +2392,7 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786651559</t>
+          <t>1786651718</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
@@ -2394,7 +2402,7 @@
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>42.735043</t>
+          <t>8.546991</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2411,18 +2419,18 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x1b14ab3ce842bb0ded035add24fcdd28a77380141c189ae36b1f623e70dff465</t>
+          <t>0xc33e951dfa8d84c01759f86fe63dfc68ddc2b547988e3a32445d72b681f7f7a5</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2488,7 +2496,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786651559</t>
+          <t>1786651637</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2498,7 +2506,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>17.094</t>
+          <t>8.546991</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2515,18 +2523,18 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x31a8e64cfb4307b5b608318a4e037810f68fe9bef13258aa7d3c45dd664c0ad3</t>
+          <t>0x948b3c3ece530e62252af65b92bdd73725833fe7355d5496ab1d4f6d84e43cc4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x03d4fFC791EE4A80194C9d9782E7D56407b242Ed</t>
+          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2592,7 +2600,7 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786651558</t>
+          <t>1786651588</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
@@ -2602,7 +2610,7 @@
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>25.641026</t>
+          <t>1.709402</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2619,18 +2627,18 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x1c244dc1d052ae42a83bf5640bcba1b28bb9c28853e7f42713fa4fddcb66b677</t>
+          <t>0x7578c65431424d3ae35de659ad6d246a7814cbb553d85319bf0968700f7bca4a</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2696,7 +2704,7 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786651550</t>
+          <t>1786651585</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
@@ -2706,7 +2714,7 @@
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>8.546991</t>
+          <t>17.094</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2723,39 +2731,31 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x20fcd5dbfafe538f08c15c6b35af5d546fa35aa588ef9811c9696ac39843c736</t>
+          <t>0x28bc2779df67c8165804579669b7a40ef9e3a34f89e4d9d4c81a44f6c49d8be2</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x2F9aCBd9B89C6eF3bc3Dc2B0F0cCD0E0936BF912</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Deportivo Alaves -0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
       <c r="H23" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -2763,27 +2763,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2808,17 +2808,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786640471</t>
+          <t>1786651567</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>12.195122</t>
+          <t>17.094</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2835,39 +2835,31 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x48d06bf1eb103be3b93f605ad7b9ed301f228fa4dfae557dca83434f1d5e0c1a</t>
+          <t>0x0eaa76f318c30c9b01a36fedfdc1b48daafadd063ed5c90a74fd0908bdecfce3</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x6203b6338991Ec84C8A8f5ef06bC17ceB1395Ddb</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>26.96</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Deportivo Alaves -0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
       <c r="H24" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -2875,27 +2867,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2920,17 +2912,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786640450</t>
+          <t>1786651567</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>65.957187</t>
+          <t>11.965812</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2947,27 +2939,23 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xe750c1fb5c3ef7edfc166b18659be46b00e3cc96d5ae299b162166175d07245f</t>
+          <t>0xcc54eb94d459bc0b9a34beb78c07fafbc7c1f3e7c6d43846f17fb20856c43d24</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -2975,11 +2963,7 @@
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -2987,27 +2971,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0x0a08c3d7f08812839b48fc67d5842cc07f2a5e67ce2a26c46d0210680fda2f99</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3032,17 +3016,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786639065</t>
+          <t>1786651559</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>36.891954</t>
+          <t>42.735043</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3059,54 +3043,46 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xdc16a40eba6eeb7462531fd3b01240a8f58f0ea20568efbaba25b17131094f2e</t>
+          <t>0x1b14ab3ce842bb0ded035add24fcdd28a77380141c189ae36b1f623e70dff465</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.4213</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>Sevilla vs Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
         <is>
           <t>Sevilla</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>La Liga</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Sevilla vs Rayo Vallecano</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr">
         <is>
           <t>Rayo Vallecano</t>
@@ -3114,7 +3090,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -3144,7 +3120,7 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786633518</t>
+          <t>1786651559</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
@@ -3154,7 +3130,7 @@
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>11.869436</t>
+          <t>17.094</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3171,54 +3147,46 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x1b67e861f8e383798d979684797f608bfad6122cc87844f2a37a8cf06e019030</t>
+          <t>0x31a8e64cfb4307b5b608318a4e037810f68fe9bef13258aa7d3c45dd664c0ad3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x03d4fFC791EE4A80194C9d9782E7D56407b242Ed</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>53.83</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>Sevilla vs Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
         <is>
           <t>Sevilla</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>La Liga</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Sevilla vs Rayo Vallecano</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
       <c r="K27" t="inlineStr">
         <is>
           <t>Rayo Vallecano</t>
@@ -3226,7 +3194,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3256,7 +3224,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786633487</t>
+          <t>1786651558</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3266,7 +3234,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>128.166667</t>
+          <t>25.641026</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3283,28 +3251,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x909a230aebd5eb00de6012a0eb69301784b515acf69e93ee497d243bd3ce212f</t>
+          <t>0x1c244dc1d052ae42a83bf5640bcba1b28bb9c28853e7f42713fa4fddcb66b677</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xbcD65d7e2D58b95Cf434eB65a82b9FD5b682D144</t>
+          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>72.15999</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3315,27 +3283,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3360,17 +3328,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786632901</t>
+          <t>1786651550</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>120.26665</t>
+          <t>8.546991</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3387,31 +3355,39 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x081a76991e0701cf3dbcaa6ccbdd7d9dd69242e812c8b7e977517fe836423751</t>
+          <t>0x20fcd5dbfafe538f08c15c6b35af5d546fa35aa588ef9811c9696ac39843c736</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.1038</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves -0.5</t>
+        </is>
+      </c>
       <c r="H29" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -3419,27 +3395,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Espanyol vs Levante</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xd36fc2a623f22222f73350186e7d08c0d31b2d895ac24a68dc8408d4e98bf55a</t>
+          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19370489</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3464,17 +3440,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786631513</t>
+          <t>1786640471</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>76.240964</t>
+          <t>12.195122</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3491,31 +3467,39 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x6f1c770a5b9534dbfff85f398a28d171effe0e02699c6558a37a881468f3090e</t>
+          <t>0x48d06bf1eb103be3b93f605ad7b9ed301f228fa4dfae557dca83434f1d5e0c1a</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>26.96</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.1013</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves -0.5</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -3523,27 +3507,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
+          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3568,17 +3552,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786631323</t>
+          <t>1786640450</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>78.123457</t>
+          <t>65.957187</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3595,7 +3579,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xffde28cdfe7ae2b6324278e8117e605bc5c2ecb236877e683d06b5cbe620b2b1</t>
+          <t>0xe750c1fb5c3ef7edfc166b18659be46b00e3cc96d5ae299b162166175d07245f</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3603,23 +3587,31 @@
           <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>20.06</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H31" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -3627,27 +3619,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Racing Santander vs Villarreal</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
+          <t>0x0a08c3d7f08812839b48fc67d5842cc07f2a5e67ce2a26c46d0210680fda2f99</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370490</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3672,17 +3664,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786631207</t>
+          <t>1786639065</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>67.333333</t>
+          <t>36.891954</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3699,31 +3691,39 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x1542e94d97dca7a28f2bf2b946f64e1fefc9fc04f50a7622a8a2791d01c58796</t>
+          <t>0xdc16a40eba6eeb7462531fd3b01240a8f58f0ea20568efbaba25b17131094f2e</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>11.85998</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.7113</t>
+          <t>1.4213</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
       <c r="H32" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -3731,27 +3731,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
+          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3776,17 +3776,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786630102</t>
+          <t>1786633518</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>16.67484</t>
+          <t>11.869436</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3803,31 +3803,39 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x9ff18d48c5ac1507ef9b6a3dfaf34f20966e85ee30cbd99e0df47a940abf1d32</t>
+          <t>0x1b67e861f8e383798d979684797f608bfad6122cc87844f2a37a8cf06e019030</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>53.83</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.4412</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
       <c r="H33" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -3835,27 +3843,27 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0x776caca6c8b9cb32d9a7b2ec2b4f40bbb630001b4db7c24175062af09044b7dd</t>
+          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -3880,17 +3888,17 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786626342</t>
+          <t>1786633487</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>11.331445</t>
+          <t>128.166667</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3907,28 +3915,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x50f0b3572b92fd4a3268a217b75ca6b4a52b72077d0276df9d0d123d8b3ebc60</t>
+          <t>0x909a230aebd5eb00de6012a0eb69301784b515acf69e93ee497d243bd3ce212f</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xbcD65d7e2D58b95Cf434eB65a82b9FD5b682D144</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>16.18903</t>
+          <t>72.15999</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.4412</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3954,7 +3962,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x776caca6c8b9cb32d9a7b2ec2b4f40bbb630001b4db7c24175062af09044b7dd</t>
+          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3984,7 +3992,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786626327</t>
+          <t>1786632901</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -3994,7 +4002,7 @@
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>36.68902</t>
+          <t>120.26665</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4011,28 +4019,28 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x2d1550913dec85439afda8d85c6033895212998f22943ab968dee5cbd7d7e7a2</t>
+          <t>0x081a76991e0701cf3dbcaa6ccbdd7d9dd69242e812c8b7e977517fe836423751</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>35.45869</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.2537</t>
+          <t>1.1038</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -4043,27 +4051,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Espanyol vs Levante</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0x0596e7ef887839f51f014583ff32fca0dbfab0916b17c3d05d740985b59eabc3</t>
+          <t>0xd36fc2a623f22222f73350186e7d08c0d31b2d895ac24a68dc8408d4e98bf55a</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370489</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4088,17 +4096,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786624561</t>
+          <t>1786631513</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>139.73868</t>
+          <t>76.240964</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4115,28 +4123,28 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x6f809dd95ba0a7f41584a66e0979cb2c04ebaeefb6e5d949b0bfd9c53278c063</t>
+          <t>0x6f1c770a5b9534dbfff85f398a28d171effe0e02699c6558a37a881468f3090e</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.7163</t>
+          <t>1.1013</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -4147,27 +4155,27 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
+          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -4192,17 +4200,17 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786623012</t>
+          <t>1786631323</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>6.980803</t>
+          <t>78.123457</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4219,28 +4227,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xddff1b4ca7359c6045ede1bd2995e1e57620811dc33cc7338113c5449dccd695</t>
+          <t>0xffde28cdfe7ae2b6324278e8117e605bc5c2ecb236877e683d06b5cbe620b2b1</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>28.91904</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.165</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4266,7 +4274,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xf684bc2655869d0024c7de5a1f2b51fb35813185b075bf3cc8d5f2fe8ce176b5</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4296,7 +4304,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786622982</t>
+          <t>1786631207</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4306,7 +4314,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>47.899031</t>
+          <t>67.333333</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4323,18 +4331,18 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0xb02e365f47ba9eaba62de63e4b14c94bf1b59d60c56188857359df36e7b10ef0</t>
+          <t>0x1542e94d97dca7a28f2bf2b946f64e1fefc9fc04f50a7622a8a2791d01c58796</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>30.81465</t>
+          <t>11.85998</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -4400,7 +4408,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786622982</t>
+          <t>1786630102</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4410,7 +4418,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>43.32464</t>
+          <t>16.67484</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4427,67 +4435,59 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xb7f333fbe5a18daf831395020096fbb62febd43977f5f81366c99339b63d902d</t>
+          <t>0x9ff18d48c5ac1507ef9b6a3dfaf34f20966e85ee30cbd99e0df47a940abf1d32</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>63.86</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.4412</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr">
+        <is>
           <t>La Liga</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Racing Santander</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>La Liga</t>
-        </is>
-      </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x1518c9a8caca0376f881601c848e03d81cd65f5d32c2b63a51625351cc193e86</t>
+          <t>0x776caca6c8b9cb32d9a7b2ec2b4f40bbb630001b4db7c24175062af09044b7dd</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4512,17 +4512,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786621976</t>
+          <t>1786626342</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>152.501493</t>
+          <t>11.331445</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4539,7 +4539,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x79454b5fc310a342a5ad62ccf677e7ea1c42b0e701cd313d0019ee8ec1faf7a2</t>
+          <t>0x50f0b3572b92fd4a3268a217b75ca6b4a52b72077d0276df9d0d123d8b3ebc60</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4547,31 +4547,23 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>97.87</t>
+          <t>16.18903</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>1.4412</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Racing Santander</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -4579,27 +4571,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xf9063ec13eee8f96a20b89bd687d0a5f1a3197a4408eb58240f63d72be7c644f</t>
+          <t>0x776caca6c8b9cb32d9a7b2ec2b4f40bbb630001b4db7c24175062af09044b7dd</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4624,17 +4616,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786621975</t>
+          <t>1786626327</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>320.885246</t>
+          <t>36.68902</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4651,7 +4643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x6df789a868c08b6d011dc9dc3fe38cf8be42973ee6e2b3513f1ae98f3a70e174</t>
+          <t>0x2d1550913dec85439afda8d85c6033895212998f22943ab968dee5cbd7d7e7a2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4659,31 +4651,23 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>82.86999</t>
+          <t>35.45869</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.2537</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Racing Santander +1</t>
-        </is>
-      </c>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -4691,27 +4675,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xeffd773f9a996fcdab4f40cb833c6db488621204b6af7959d07794c43de040c4</t>
+          <t>0x0596e7ef887839f51f014583ff32fca0dbfab0916b17c3d05d740985b59eabc3</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4736,17 +4720,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786621975</t>
+          <t>1786624561</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>112.556862</t>
+          <t>139.73868</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4763,39 +4747,31 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x4061873586e14d63aeb0e4cdf23afafe5cd7b3c74fe59157daf06c85b8fd8796</t>
+          <t>0x6f809dd95ba0a7f41584a66e0979cb2c04ebaeefb6e5d949b0bfd9c53278c063</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>1.7163</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Racing Santander -0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -4803,27 +4779,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0xb811d0e9d1802cd3762a57ca8fc3a5399392dd37dec4f8d9fd37f0170ece0f50</t>
+          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4848,17 +4824,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786621975</t>
+          <t>1786623012</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>146.95082</t>
+          <t>6.980803</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4875,7 +4851,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x8dda40aa7d3c4140b3e5ab6ab62f3db4f5a3730a15ebff80f0bda9807c704ca2</t>
+          <t>0xddff1b4ca7359c6045ede1bd2995e1e57620811dc33cc7338113c5449dccd695</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4886,17 +4862,17 @@
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>27.87224</t>
+          <t>28.91904</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.5325</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -4907,27 +4883,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Celta de Vigo vs Osasuna</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0x0f075dae0a586d46b2073e126cbc52393dc2ff99a26953308f94b3b2751764b7</t>
+          <t>0xf684bc2655869d0024c7de5a1f2b51fb35813185b075bf3cc8d5f2fe8ce176b5</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19370496</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4952,17 +4928,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786619056</t>
+          <t>1786622982</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786908600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>52.342235</t>
+          <t>47.899031</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -4979,39 +4955,31 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x4565877a70aabfac9d4d4a2afcda9ace6e304d9bd921ce69a2149c76528e271a</t>
+          <t>0xb02e365f47ba9eaba62de63e4b14c94bf1b59d60c56188857359df36e7b10ef0</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0xb363112BA7ed93A221Efb405496e4Fa3BE119D81</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30.81465</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.7113</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Rayo Vallecano</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -5019,27 +4987,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x2b9c4f75049808a8d2b353d1c6e902da151d2fea092e70f08cdd4ac2ffbfd8a6</t>
+          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5064,17 +5032,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786614389</t>
+          <t>1786622982</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>175.438596</t>
+          <t>43.32464</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5091,12 +5059,12 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x562837a4689bf537ab0502cfe5d722bafc1833bc972e329ba5399cd7649a219c</t>
+          <t>0xb7f333fbe5a18daf831395020096fbb62febd43977f5f81366c99339b63d902d</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5106,22 +5074,22 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>63.86</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.4187</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>La Liga</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5131,27 +5099,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Racing Santander vs Villarreal</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xda132f38d7cbcb404e0db6126292d55c3614e3311c2670ac15890a14a94cdaea</t>
+          <t>0x1518c9a8caca0376f881601c848e03d81cd65f5d32c2b63a51625351cc193e86</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370490</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5176,17 +5144,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786586644</t>
+          <t>1786621976</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>7.769231</t>
+          <t>152.501493</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5203,102 +5171,766 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>0x79454b5fc310a342a5ad62ccf677e7ea1c42b0e701cd313d0019ee8ec1faf7a2</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>97.87</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>1.305</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>Racing Santander vs Villarreal</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>0xf9063ec13eee8f96a20b89bd687d0a5f1a3197a4408eb58240f63d72be7c644f</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>L19370490</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>1786621975</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>1786892400</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>320.885246</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>0x6df789a868c08b6d011dc9dc3fe38cf8be42973ee6e2b3513f1ae98f3a70e174</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>82.86999</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>1.7363</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Racing Santander +1</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>Racing Santander vs Villarreal</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0xeffd773f9a996fcdab4f40cb833c6db488621204b6af7959d07794c43de040c4</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>L19370490</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>1786621975</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>1786892400</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>112.556862</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>0x4061873586e14d63aeb0e4cdf23afafe5cd7b3c74fe59157daf06c85b8fd8796</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>44.82</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>1.305</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Racing Santander -0.5</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>Racing Santander vs Villarreal</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0xb811d0e9d1802cd3762a57ca8fc3a5399392dd37dec4f8d9fd37f0170ece0f50</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>L19370490</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>1786621975</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>1786892400</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>146.95082</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>0x8dda40aa7d3c4140b3e5ab6ab62f3db4f5a3730a15ebff80f0bda9807c704ca2</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>27.87224</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>1.5325</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Celta de Vigo vs Osasuna</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Celta de Vigo</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0x0f075dae0a586d46b2073e126cbc52393dc2ff99a26953308f94b3b2751764b7</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>L19370496</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>1786619056</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>1786908600</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>52.342235</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>0x4565877a70aabfac9d4d4a2afcda9ace6e304d9bd921ce69a2149c76528e271a</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>0xb363112BA7ed93A221Efb405496e4Fa3BE119D81</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>1.285</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Sevilla vs Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0x2b9c4f75049808a8d2b353d1c6e902da151d2fea092e70f08cdd4ac2ffbfd8a6</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>L19370582</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>1786614389</t>
+        </is>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>1786822200</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>175.438596</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>0x562837a4689bf537ab0502cfe5d722bafc1833bc972e329ba5399cd7649a219c</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0xda132f38d7cbcb404e0db6126292d55c3614e3311c2670ac15890a14a94cdaea</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>1786586644</t>
+        </is>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>7.769231</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
           <t>0x27be56be09649bd460766fe27df249788cf4d7ad87d19f5f9a8bfba225e519b9</t>
         </is>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B52" t="inlineStr">
         <is>
           <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr">
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
         <is>
           <t>1.52676</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>1.7512</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr">
         <is>
           <t>La Liga</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr">
+      <c r="I52" t="inlineStr">
         <is>
           <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr">
+      <c r="J52" t="inlineStr">
         <is>
           <t>Deportivo Alaves</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>Getafe</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>0x32766ed977cae312bdb45c44b07e70207b356db986ef0293796496f193e13d1e</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>L19370598</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R46" t="inlineStr">
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
         <is>
           <t>1786578252</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr">
+      <c r="S52" t="inlineStr">
         <is>
           <t>1786815000</t>
         </is>
       </c>
-      <c r="T46" t="inlineStr">
+      <c r="T52" t="inlineStr">
         <is>
           <t>2.032293</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr">
+      <c r="U52" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V46" t="inlineStr">
+      <c r="V52" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/La Liga/trades.xlsx
+++ b/data/sxbet/ligas/La Liga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V52"/>
+  <dimension ref="A1:V60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,23 +531,27 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xbf1a151f615bf3f9a9e616e3c50bbe9cfcae4e7a99f9ce723f49c93c83cdc9d0</t>
+          <t>0xd1b390848190c00232506eacbdf3de0c4fb3341dfed7509ed5d82ce98fefb68f</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x30E3f83573EbFc7274EeAfD586D930F7392F5650</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.16999</t>
+          <t>32.12</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.5875</t>
+          <t>1.4275</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -555,7 +559,11 @@
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H2" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -563,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Espanyol vs Levante</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0x3b15a29eb768ad2d602f53ab34fccc5aa069fa3f722408b8d6710612a74fb3b6</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370489</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -608,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786687820</t>
+          <t>1786708635</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>1.991472</t>
+          <t>75.134503</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -635,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x11994251df996a13dca305742c6cfa502ae27aa5f4bd0111f29dc7341166926a</t>
+          <t>0x7f0e441004fffd1fe881714dcaf8f0dc3d32bf046fffc69dff440d1672c7714f</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xdFC5342F5d4bF9F317c0CBf71121AC6FA92d8fbf</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -650,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>45.715</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.2788</t>
+          <t>1.5787</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Over 2.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -675,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Celta de Vigo vs Osasuna</t>
+          <t>Espanyol vs Levante</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x9993d963f79cc9f688d38136ed8af60ad8c5e128ae668d0af49645c4ec2e0c25</t>
+          <t>0x49dabceb14c4027b90dc4d8270cdfd514fe4070867c271757ed62270904d3f7a</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19370496</t>
+          <t>L19370489</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -720,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786684730</t>
+          <t>1786708635</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786908600</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>101.563715</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -747,7 +755,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x03eaa48ad5cba7703834b4eb4188b2512fc59fc66ce1a132f347fb208e62190e</t>
+          <t>0x0215ba1f4a546ce50b568125670efe2f3cb594679153dfd16e003add1ff1670b</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -758,12 +766,12 @@
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>29.16362</t>
+          <t>35.07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.1075</t>
+          <t>1.1062</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -824,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786684614</t>
+          <t>1786707052</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -834,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>271.289488</t>
+          <t>330.070588</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -851,28 +859,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xf7320171cfa1d2a4388cf7700c275208ec77d1f0986bae7466346769cb38d5b4</t>
+          <t>0x0ae19247ab2948e516f5ce1b5b97bbb5e71f6c997858511110a66b7335904c07</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.05797</t>
+          <t>108.84</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.1075</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -883,27 +891,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
+          <t>0x78a4cf6b02d047f006e2c80b80d1bba724ebd9a508d0cce70fc13d1dcc698bd3</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -928,17 +936,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786684161</t>
+          <t>1786706935</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>9.841581</t>
+          <t>164.909091</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -955,7 +963,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x2c667f7cd0a5ee4597a318320db656e61b2fe595b68044cdbb02a35a2c508f11</t>
+          <t>0x6ccfb889ade998fdea5a13e6f95b82afc8d38ea46dc3cdb05777d19b61d38489</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -966,12 +974,12 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>122.1</t>
+          <t>38.96365</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>1.1675</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -1032,7 +1040,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786679771</t>
+          <t>1786706838</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1042,7 +1050,7 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>232.618806</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1059,23 +1067,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xef898b845c993efce01f949a5b4165e91083d76283cd50b5ccb38113072d39a3</t>
+          <t>0xece691e2f3fa898d49c7d3c991735f87e5c4d9d84718f8019f8459dd0608d12b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
+          <t>0xa1B345AC7dAd7aA730fe22f3a6379de06a7f6B61</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>122.1</t>
+          <t>123</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>1.1663</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1136,7 +1144,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786677944</t>
+          <t>1786704868</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1146,7 +1154,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>739.849624</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1163,28 +1171,28 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0xec715718ce1e06f5bfd1790eedf07c987dbe7e219a72c5facd15377495db5263</t>
+          <t>0x233e63e043940ed7a303b95c191bb2fe090edd21f5a29da25bf50df5b3a936de</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>122.1</t>
+          <t>136.87</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>1.545</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1195,27 +1203,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Espanyol vs Levante</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
+          <t>0x0b6a22493b6514fc21dd836e8493df5b744432e27aa48ef80289f94befb19490</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370489</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1240,17 +1248,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786676253</t>
+          <t>1786696941</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>251.137615</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1267,28 +1275,28 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x0e7729ad6b4a9824864f6ac006c58fb19124ac050b08faef247ac7a176fd96ee</t>
+          <t>0x465f902491d3a3e6b99a234c6b14c18b007ae7c4d5a71ccdd550d024861bb7b6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xB66Aa9923E7a8920151375e186E6718064dd4f08</t>
+          <t>0xFBd63A3Adf898EfFf1e5A017f98756dC760eBfb8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>245.05482</t>
+          <t>61.46</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.755</t>
+          <t>1.1663</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -1314,7 +1322,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0x32766ed977cae312bdb45c44b07e70207b356db986ef0293796496f193e13d1e</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -1344,7 +1352,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786669488</t>
+          <t>1786692208</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1354,7 +1362,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>324.575921</t>
+          <t>369.684211</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1371,23 +1379,23 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0x8d79a50b7331e59ea36d27efa5d99d53e26dfd1be15401e254a4cc43e280ff2f</t>
+          <t>0xbf1a151f615bf3f9a9e616e3c50bbe9cfcae4e7a99f9ce723f49c93c83cdc9d0</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x9737E0E3E8EE2DD6B8A7E19D1507EcB3221b5483</t>
+          <t>0x30E3f83573EbFc7274EeAfD586D930F7392F5650</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>4.89999</t>
+          <t>1.16999</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5863</t>
+          <t>1.5875</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1448,7 +1456,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786667446</t>
+          <t>1786687820</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1458,7 +1466,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>8.358192</t>
+          <t>1.991472</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1475,23 +1483,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x11476693f9b725995aedcf0e75acf05d19a0f1647da3059f334da311f0f1e922</t>
+          <t>0x11994251df996a13dca305742c6cfa502ae27aa5f4bd0111f29dc7341166926a</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>0xdFC5342F5d4bF9F317c0CBf71121AC6FA92d8fbf</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.19253</t>
+          <t>45.715</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.5713</t>
+          <t>1.2788</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1499,7 +1511,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -1507,27 +1523,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Celta de Vigo vs Osasuna</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x10c92f089fb69109ac5beea7c82a0e1cd2f23257cd842348710e2598be68bc48</t>
+          <t>0x9993d963f79cc9f688d38136ed8af60ad8c5e128ae668d0af49645c4ec2e0c25</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370496</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1552,17 +1568,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786664168</t>
+          <t>1786684730</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786908600</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>2.08758</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1579,28 +1595,28 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x046492cfcbf4e5a3ced4caa85326fa8b44dbff1fb248a61a7fa6c8a8d2d9c1f8</t>
+          <t>0x03eaa48ad5cba7703834b4eb4188b2512fc59fc66ce1a132f347fb208e62190e</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>29.16362</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.5962</t>
+          <t>1.1075</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -1611,27 +1627,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0xfcdcf41a0510583d5bb65df7215b5101ff435808043952db2a0364f1424743db</t>
+          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1656,17 +1672,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786663762</t>
+          <t>1786684614</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>8.385744</t>
+          <t>271.289488</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1683,28 +1699,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xe376b22b83ba1a0d5c58e6763337d61f4445c85bfdc77949472d41c7c47e42b6</t>
+          <t>0xf7320171cfa1d2a4388cf7700c275208ec77d1f0986bae7466346769cb38d5b4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
+          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>1.05797</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.1075</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1715,27 +1731,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Celta de Vigo vs Osasuna</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
+          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19370496</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1760,17 +1776,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786657450</t>
+          <t>1786684161</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786908600</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>9.841581</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1787,39 +1803,31 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x4e949c2076e8faf4dcc272acfa8d69c62442324aca8ceeb5820b8348c74f13f6</t>
+          <t>0x2c667f7cd0a5ee4597a318320db656e61b2fe595b68044cdbb02a35a2c508f11</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>122.1</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.165</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -1827,27 +1835,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Celta de Vigo vs Osasuna</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19370496</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1872,17 +1880,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786657449</t>
+          <t>1786679771</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786908600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>52.967742</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1899,28 +1907,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xd54151c9cd066d8a5e7714f77ebc5e24ee2aac3e2c8a52a50b3a6becd0bac875</t>
+          <t>0xef898b845c993efce01f949a5b4165e91083d76283cd50b5ccb38113072d39a3</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>112.94</t>
+          <t>122.1</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.6625</t>
+          <t>1.165</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G15" t="inlineStr"/>
@@ -1946,7 +1954,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x78a4cf6b02d047f006e2c80b80d1bba724ebd9a508d0cce70fc13d1dcc698bd3</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1976,7 +1984,7 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786656774</t>
+          <t>1786677944</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
@@ -1986,7 +1994,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>170.475472</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2003,28 +2011,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0x835c08ffc86c9c616d8c107e844ff9658b10b62372398122a4f7ded5bb28a516</t>
+          <t>0xec715718ce1e06f5bfd1790eedf07c987dbe7e219a72c5facd15377495db5263</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0x8e9bE2B8b636Cc98b01957cE9D4E3B62cF579080</t>
+          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>122.1</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.165</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2035,27 +2043,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2080,17 +2088,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786651844</t>
+          <t>1786676253</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>8.492552</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2107,28 +2115,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x45cc84f2dd4c1b45226a895eead76c109d5af22eac83562ab8aa23758f8a6b5e</t>
+          <t>0x0e7729ad6b4a9824864f6ac006c58fb19124ac050b08faef247ac7a176fd96ee</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xa3786b93377213A42Bf1d3261d373cE67Cf2AA67</t>
+          <t>0xB66Aa9923E7a8920151375e186E6718064dd4f08</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>245.05482</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.755</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2139,27 +2147,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0x32766ed977cae312bdb45c44b07e70207b356db986ef0293796496f193e13d1e</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2184,17 +2192,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786651814</t>
+          <t>1786669488</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>42.735043</t>
+          <t>324.575921</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2211,28 +2219,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x213398a7cadc42743f3aee31a89c45cc1f9c78136646bd816983864c34b13f79</t>
+          <t>0x8d79a50b7331e59ea36d27efa5d99d53e26dfd1be15401e254a4cc43e280ff2f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x4feB57379592eb94c51c014553de6EEbD4d42577</t>
+          <t>0x9737E0E3E8EE2DD6B8A7E19D1507EcB3221b5483</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>4.89999</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.5863</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2243,27 +2251,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Celta de Vigo vs Osasuna</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19370496</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2288,17 +2296,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786651743</t>
+          <t>1786667446</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786908600</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>8.358192</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2315,28 +2323,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x0adf7a0f94fb74bebb4e5acb49582e1f91e3ae462b204becaedfbe0f50714ede</t>
+          <t>0x11476693f9b725995aedcf0e75acf05d19a0f1647da3059f334da311f0f1e922</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x06a603b688E676702ec63D735CAe4A57ff71B3e1</t>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>1.19253</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.5713</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2347,27 +2355,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Racing Santander vs Villarreal</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0x10c92f089fb69109ac5beea7c82a0e1cd2f23257cd842348710e2598be68bc48</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370490</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2392,17 +2400,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786651718</t>
+          <t>1786664168</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>8.546991</t>
+          <t>2.08758</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2419,28 +2427,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0xc33e951dfa8d84c01759f86fe63dfc68ddc2b547988e3a32445d72b681f7f7a5</t>
+          <t>0x046492cfcbf4e5a3ced4caa85326fa8b44dbff1fb248a61a7fa6c8a8d2d9c1f8</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.5962</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2451,27 +2459,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0xfcdcf41a0510583d5bb65df7215b5101ff435808043952db2a0364f1424743db</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2496,17 +2504,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786651637</t>
+          <t>1786663762</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>8.546991</t>
+          <t>8.385744</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2523,28 +2531,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x948b3c3ece530e62252af65b92bdd73725833fe7355d5496ab1d4f6d84e43cc4</t>
+          <t>0xe376b22b83ba1a0d5c58e6763337d61f4445c85bfdc77949472d41c7c47e42b6</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
+          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2555,27 +2563,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Celta de Vigo vs Osasuna</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370496</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2600,17 +2608,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786651588</t>
+          <t>1786657450</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786908600</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>1.709402</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2627,31 +2635,39 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x7578c65431424d3ae35de659ad6d246a7814cbb553d85319bf0968700f7bca4a</t>
+          <t>0x4e949c2076e8faf4dcc272acfa8d69c62442324aca8ceeb5820b8348c74f13f6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -2659,27 +2675,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Celta de Vigo vs Osasuna</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370496</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2704,17 +2720,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786651585</t>
+          <t>1786657449</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786908600</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>17.094</t>
+          <t>52.967742</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2731,28 +2747,28 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x28bc2779df67c8165804579669b7a40ef9e3a34f89e4d9d4c81a44f6c49d8be2</t>
+          <t>0xd54151c9cd066d8a5e7714f77ebc5e24ee2aac3e2c8a52a50b3a6becd0bac875</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x2F9aCBd9B89C6eF3bc3Dc2B0F0cCD0E0936BF912</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>112.94</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.6625</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2763,27 +2779,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0x78a4cf6b02d047f006e2c80b80d1bba724ebd9a508d0cce70fc13d1dcc698bd3</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2808,17 +2824,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786651567</t>
+          <t>1786656774</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>17.094</t>
+          <t>170.475472</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2835,23 +2851,23 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x0eaa76f318c30c9b01a36fedfdc1b48daafadd063ed5c90a74fd0908bdecfce3</t>
+          <t>0x835c08ffc86c9c616d8c107e844ff9658b10b62372398122a4f7ded5bb28a516</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x6203b6338991Ec84C8A8f5ef06bC17ceB1395Ddb</t>
+          <t>0x8e9bE2B8b636Cc98b01957cE9D4E3B62cF579080</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -2912,7 +2928,7 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786651567</t>
+          <t>1786651844</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
@@ -2922,7 +2938,7 @@
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>11.965812</t>
+          <t>8.492552</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2939,12 +2955,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0xcc54eb94d459bc0b9a34beb78c07fafbc7c1f3e7c6d43846f17fb20856c43d24</t>
+          <t>0x45cc84f2dd4c1b45226a895eead76c109d5af22eac83562ab8aa23758f8a6b5e</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+          <t>0xa3786b93377213A42Bf1d3261d373cE67Cf2AA67</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -3016,7 +3032,7 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786651559</t>
+          <t>1786651814</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -3043,28 +3059,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x1b14ab3ce842bb0ded035add24fcdd28a77380141c189ae36b1f623e70dff465</t>
+          <t>0x213398a7cadc42743f3aee31a89c45cc1f9c78136646bd816983864c34b13f79</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+          <t>0x4feB57379592eb94c51c014553de6EEbD4d42577</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G26" t="inlineStr"/>
@@ -3075,27 +3091,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Celta de Vigo vs Osasuna</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370496</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3120,17 +3136,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786651559</t>
+          <t>1786651743</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786908600</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>17.094</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3147,18 +3163,18 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x31a8e64cfb4307b5b608318a4e037810f68fe9bef13258aa7d3c45dd664c0ad3</t>
+          <t>0x0adf7a0f94fb74bebb4e5acb49582e1f91e3ae462b204becaedfbe0f50714ede</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x03d4fFC791EE4A80194C9d9782E7D56407b242Ed</t>
+          <t>0x06a603b688E676702ec63D735CAe4A57ff71B3e1</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -3224,7 +3240,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786651558</t>
+          <t>1786651718</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3234,7 +3250,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>25.641026</t>
+          <t>8.546991</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3251,12 +3267,12 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x1c244dc1d052ae42a83bf5640bcba1b28bb9c28853e7f42713fa4fddcb66b677</t>
+          <t>0xc33e951dfa8d84c01759f86fe63dfc68ddc2b547988e3a32445d72b681f7f7a5</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -3328,7 +3344,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786651550</t>
+          <t>1786651637</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3355,39 +3371,31 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x20fcd5dbfafe538f08c15c6b35af5d546fa35aa588ef9811c9696ac39843c736</t>
+          <t>0x948b3c3ece530e62252af65b92bdd73725833fe7355d5496ab1d4f6d84e43cc4</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Deportivo Alaves -0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -3395,27 +3403,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3440,17 +3448,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786640471</t>
+          <t>1786651588</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>12.195122</t>
+          <t>1.709402</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3467,39 +3475,31 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x48d06bf1eb103be3b93f605ad7b9ed301f228fa4dfae557dca83434f1d5e0c1a</t>
+          <t>0x7578c65431424d3ae35de659ad6d246a7814cbb553d85319bf0968700f7bca4a</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>26.96</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Deportivo Alaves -0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
       <c r="H30" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -3507,27 +3507,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3552,17 +3552,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786640450</t>
+          <t>1786651585</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>65.957187</t>
+          <t>17.094</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3579,27 +3579,23 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xe750c1fb5c3ef7edfc166b18659be46b00e3cc96d5ae299b162166175d07245f</t>
+          <t>0x28bc2779df67c8165804579669b7a40ef9e3a34f89e4d9d4c81a44f6c49d8be2</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x2F9aCBd9B89C6eF3bc3Dc2B0F0cCD0E0936BF912</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -3607,11 +3603,7 @@
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -3619,27 +3611,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0x0a08c3d7f08812839b48fc67d5842cc07f2a5e67ce2a26c46d0210680fda2f99</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3664,17 +3656,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786639065</t>
+          <t>1786651567</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>36.891954</t>
+          <t>17.094</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3691,54 +3683,46 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0xdc16a40eba6eeb7462531fd3b01240a8f58f0ea20568efbaba25b17131094f2e</t>
+          <t>0x0eaa76f318c30c9b01a36fedfdc1b48daafadd063ed5c90a74fd0908bdecfce3</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x6203b6338991Ec84C8A8f5ef06bC17ceB1395Ddb</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.4213</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>Sevilla vs Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
         <is>
           <t>Sevilla</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>La Liga</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Sevilla vs Rayo Vallecano</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
       <c r="K32" t="inlineStr">
         <is>
           <t>Rayo Vallecano</t>
@@ -3746,7 +3730,7 @@
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -3776,7 +3760,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786633518</t>
+          <t>1786651567</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3786,7 +3770,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>11.869436</t>
+          <t>11.965812</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3803,54 +3787,46 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x1b67e861f8e383798d979684797f608bfad6122cc87844f2a37a8cf06e019030</t>
+          <t>0xcc54eb94d459bc0b9a34beb78c07fafbc7c1f3e7c6d43846f17fb20856c43d24</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>53.83</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>Sevilla vs Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
         <is>
           <t>Sevilla</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>La Liga</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Sevilla vs Rayo Vallecano</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr">
         <is>
           <t>Rayo Vallecano</t>
@@ -3858,7 +3834,7 @@
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -3888,7 +3864,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786633487</t>
+          <t>1786651559</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3898,7 +3874,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>128.166667</t>
+          <t>42.735043</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3915,28 +3891,28 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x909a230aebd5eb00de6012a0eb69301784b515acf69e93ee497d243bd3ce212f</t>
+          <t>0x1b14ab3ce842bb0ded035add24fcdd28a77380141c189ae36b1f623e70dff465</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0xbcD65d7e2D58b95Cf434eB65a82b9FD5b682D144</t>
+          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr">
         <is>
-          <t>72.15999</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr"/>
@@ -3947,27 +3923,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3992,17 +3968,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786632901</t>
+          <t>1786651559</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>120.26665</t>
+          <t>17.094</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4019,28 +3995,28 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x081a76991e0701cf3dbcaa6ccbdd7d9dd69242e812c8b7e977517fe836423751</t>
+          <t>0x31a8e64cfb4307b5b608318a4e037810f68fe9bef13258aa7d3c45dd664c0ad3</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x03d4fFC791EE4A80194C9d9782E7D56407b242Ed</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.1038</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -4051,27 +4027,27 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Espanyol vs Levante</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xd36fc2a623f22222f73350186e7d08c0d31b2d895ac24a68dc8408d4e98bf55a</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>L19370489</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
@@ -4096,17 +4072,17 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786631513</t>
+          <t>1786651558</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>76.240964</t>
+          <t>25.641026</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4123,28 +4099,28 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x6f1c770a5b9534dbfff85f398a28d171effe0e02699c6558a37a881468f3090e</t>
+          <t>0x1c244dc1d052ae42a83bf5640bcba1b28bb9c28853e7f42713fa4fddcb66b677</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.1013</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -4170,7 +4146,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4200,7 +4176,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786631323</t>
+          <t>1786651550</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4210,7 +4186,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>78.123457</t>
+          <t>8.546991</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4227,31 +4203,39 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0xffde28cdfe7ae2b6324278e8117e605bc5c2ecb236877e683d06b5cbe620b2b1</t>
+          <t>0x20fcd5dbfafe538f08c15c6b35af5d546fa35aa588ef9811c9696ac39843c736</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves -0.5</t>
+        </is>
+      </c>
       <c r="H37" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -4274,7 +4258,7 @@
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
+          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
@@ -4304,7 +4288,7 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786631207</t>
+          <t>1786640471</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
@@ -4314,7 +4298,7 @@
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>67.333333</t>
+          <t>12.195122</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4331,31 +4315,39 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x1542e94d97dca7a28f2bf2b946f64e1fefc9fc04f50a7622a8a2791d01c58796</t>
+          <t>0x48d06bf1eb103be3b93f605ad7b9ed301f228fa4dfae557dca83434f1d5e0c1a</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>11.85998</t>
+          <t>26.96</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.7113</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves -0.5</t>
+        </is>
+      </c>
       <c r="H38" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -4378,7 +4370,7 @@
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
+          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
@@ -4408,7 +4400,7 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786630102</t>
+          <t>1786640450</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
@@ -4418,7 +4410,7 @@
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>16.67484</t>
+          <t>65.957187</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4435,31 +4427,39 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x9ff18d48c5ac1507ef9b6a3dfaf34f20966e85ee30cbd99e0df47a940abf1d32</t>
+          <t>0xe750c1fb5c3ef7edfc166b18659be46b00e3cc96d5ae299b162166175d07245f</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>20.06</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.4412</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H39" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -4467,27 +4467,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Racing Santander vs Villarreal</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x776caca6c8b9cb32d9a7b2ec2b4f40bbb630001b4db7c24175062af09044b7dd</t>
+          <t>0x0a08c3d7f08812839b48fc67d5842cc07f2a5e67ce2a26c46d0210680fda2f99</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370490</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4512,17 +4512,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786626342</t>
+          <t>1786639065</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>11.331445</t>
+          <t>36.891954</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4539,31 +4539,39 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x50f0b3572b92fd4a3268a217b75ca6b4a52b72077d0276df9d0d123d8b3ebc60</t>
+          <t>0xdc16a40eba6eeb7462531fd3b01240a8f58f0ea20568efbaba25b17131094f2e</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>16.18903</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.4412</t>
+          <t>1.4213</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
       <c r="H40" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -4571,27 +4579,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x776caca6c8b9cb32d9a7b2ec2b4f40bbb630001b4db7c24175062af09044b7dd</t>
+          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4616,17 +4624,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786626327</t>
+          <t>1786633518</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>36.68902</t>
+          <t>11.869436</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4643,7 +4651,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x2d1550913dec85439afda8d85c6033895212998f22943ab968dee5cbd7d7e7a2</t>
+          <t>0x1b67e861f8e383798d979684797f608bfad6122cc87844f2a37a8cf06e019030</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4651,23 +4659,31 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr"/>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>35.45869</t>
+          <t>53.83</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.2537</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
       <c r="H41" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -4675,27 +4691,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x0596e7ef887839f51f014583ff32fca0dbfab0916b17c3d05d740985b59eabc3</t>
+          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4720,17 +4736,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786624561</t>
+          <t>1786633487</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>139.73868</t>
+          <t>128.166667</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4747,28 +4763,28 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x6f809dd95ba0a7f41584a66e0979cb2c04ebaeefb6e5d949b0bfd9c53278c063</t>
+          <t>0x909a230aebd5eb00de6012a0eb69301784b515acf69e93ee497d243bd3ce212f</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xbcD65d7e2D58b95Cf434eB65a82b9FD5b682D144</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>72.15999</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.7163</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G42" t="inlineStr"/>
@@ -4794,7 +4810,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
+          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4824,7 +4840,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786623012</t>
+          <t>1786632901</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4834,7 +4850,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>6.980803</t>
+          <t>120.26665</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4851,28 +4867,28 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xddff1b4ca7359c6045ede1bd2995e1e57620811dc33cc7338113c5449dccd695</t>
+          <t>0x081a76991e0701cf3dbcaa6ccbdd7d9dd69242e812c8b7e977517fe836423751</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
-          <t>28.91904</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.1038</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G43" t="inlineStr"/>
@@ -4883,27 +4899,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Espanyol vs Levante</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xf684bc2655869d0024c7de5a1f2b51fb35813185b075bf3cc8d5f2fe8ce176b5</t>
+          <t>0xd36fc2a623f22222f73350186e7d08c0d31b2d895ac24a68dc8408d4e98bf55a</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370489</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4928,17 +4944,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786622982</t>
+          <t>1786631513</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>47.899031</t>
+          <t>76.240964</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -4955,28 +4971,28 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0xb02e365f47ba9eaba62de63e4b14c94bf1b59d60c56188857359df36e7b10ef0</t>
+          <t>0x6f1c770a5b9534dbfff85f398a28d171effe0e02699c6558a37a881468f3090e</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>30.81465</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.7113</t>
+          <t>1.1013</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -4987,27 +5003,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
+          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5032,17 +5048,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786622982</t>
+          <t>1786631323</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>43.32464</t>
+          <t>78.123457</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5059,67 +5075,59 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xb7f333fbe5a18daf831395020096fbb62febd43977f5f81366c99339b63d902d</t>
+          <t>0xffde28cdfe7ae2b6324278e8117e605bc5c2ecb236877e683d06b5cbe620b2b1</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>63.86</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.165</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr">
+        <is>
           <t>La Liga</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Racing Santander</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>La Liga</t>
-        </is>
-      </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x1518c9a8caca0376f881601c848e03d81cd65f5d32c2b63a51625351cc193e86</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5144,17 +5152,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786621976</t>
+          <t>1786631207</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>152.501493</t>
+          <t>67.333333</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5171,39 +5179,31 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x79454b5fc310a342a5ad62ccf677e7ea1c42b0e701cd313d0019ee8ec1faf7a2</t>
+          <t>0x1542e94d97dca7a28f2bf2b946f64e1fefc9fc04f50a7622a8a2791d01c58796</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>97.87</t>
+          <t>11.85998</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>1.7113</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Racing Santander</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -5211,27 +5211,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xf9063ec13eee8f96a20b89bd687d0a5f1a3197a4408eb58240f63d72be7c644f</t>
+          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5256,17 +5256,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786621975</t>
+          <t>1786630102</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>320.885246</t>
+          <t>16.67484</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5283,39 +5283,31 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x6df789a868c08b6d011dc9dc3fe38cf8be42973ee6e2b3513f1ae98f3a70e174</t>
+          <t>0x9ff18d48c5ac1507ef9b6a3dfaf34f20966e85ee30cbd99e0df47a940abf1d32</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>82.86999</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.4412</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Racing Santander +1</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -5323,27 +5315,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0xeffd773f9a996fcdab4f40cb833c6db488621204b6af7959d07794c43de040c4</t>
+          <t>0x776caca6c8b9cb32d9a7b2ec2b4f40bbb630001b4db7c24175062af09044b7dd</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5368,17 +5360,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786621975</t>
+          <t>1786626342</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>112.556862</t>
+          <t>11.331445</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5395,7 +5387,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x4061873586e14d63aeb0e4cdf23afafe5cd7b3c74fe59157daf06c85b8fd8796</t>
+          <t>0x50f0b3572b92fd4a3268a217b75ca6b4a52b72077d0276df9d0d123d8b3ebc60</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5403,31 +5395,23 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>16.18903</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>1.4412</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Racing Santander -0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -5435,27 +5419,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xb811d0e9d1802cd3762a57ca8fc3a5399392dd37dec4f8d9fd37f0170ece0f50</t>
+          <t>0x776caca6c8b9cb32d9a7b2ec2b4f40bbb630001b4db7c24175062af09044b7dd</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5480,17 +5464,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786621975</t>
+          <t>1786626327</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>146.95082</t>
+          <t>36.68902</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5507,7 +5491,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x8dda40aa7d3c4140b3e5ab6ab62f3db4f5a3730a15ebff80f0bda9807c704ca2</t>
+          <t>0x2d1550913dec85439afda8d85c6033895212998f22943ab968dee5cbd7d7e7a2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5518,17 +5502,17 @@
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>27.87224</t>
+          <t>35.45869</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.5325</t>
+          <t>1.2537</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -5539,27 +5523,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Celta de Vigo vs Osasuna</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x0f075dae0a586d46b2073e126cbc52393dc2ff99a26953308f94b3b2751764b7</t>
+          <t>0x0596e7ef887839f51f014583ff32fca0dbfab0916b17c3d05d740985b59eabc3</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19370496</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5584,17 +5568,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786619056</t>
+          <t>1786624561</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1786908600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>52.342235</t>
+          <t>139.73868</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5611,39 +5595,31 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x4565877a70aabfac9d4d4a2afcda9ace6e304d9bd921ce69a2149c76528e271a</t>
+          <t>0x6f809dd95ba0a7f41584a66e0979cb2c04ebaeefb6e5d949b0bfd9c53278c063</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0xb363112BA7ed93A221Efb405496e4Fa3BE119D81</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.7163</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Rayo Vallecano</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
       <c r="H50" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -5651,27 +5627,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x2b9c4f75049808a8d2b353d1c6e902da151d2fea092e70f08cdd4ac2ffbfd8a6</t>
+          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5696,17 +5672,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786614389</t>
+          <t>1786623012</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>175.438596</t>
+          <t>6.980803</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5723,39 +5699,31 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x562837a4689bf537ab0502cfe5d722bafc1833bc972e329ba5399cd7649a219c</t>
+          <t>0xddff1b4ca7359c6045ede1bd2995e1e57620811dc33cc7338113c5449dccd695</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>28.91904</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Over 3.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -5778,7 +5746,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xda132f38d7cbcb404e0db6126292d55c3614e3311c2670ac15890a14a94cdaea</t>
+          <t>0xf684bc2655869d0024c7de5a1f2b51fb35813185b075bf3cc8d5f2fe8ce176b5</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5808,7 +5776,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786586644</t>
+          <t>1786622982</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5818,7 +5786,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>7.769231</t>
+          <t>47.899031</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5835,28 +5803,28 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x27be56be09649bd460766fe27df249788cf4d7ad87d19f5f9a8bfba225e519b9</t>
+          <t>0xb02e365f47ba9eaba62de63e4b14c94bf1b59d60c56188857359df36e7b10ef0</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>1.52676</t>
+          <t>30.81465</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.7512</t>
+          <t>1.7113</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5882,55 +5850,935 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
+          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>1786622982</t>
+        </is>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>43.32464</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>0xb7f333fbe5a18daf831395020096fbb62febd43977f5f81366c99339b63d902d</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>63.86</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1.4187</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Racing Santander vs Villarreal</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>0x1518c9a8caca0376f881601c848e03d81cd65f5d32c2b63a51625351cc193e86</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>L19370490</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>1786621976</t>
+        </is>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>1786892400</t>
+        </is>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>152.501493</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>0x79454b5fc310a342a5ad62ccf677e7ea1c42b0e701cd313d0019ee8ec1faf7a2</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>97.87</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>1.305</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Racing Santander vs Villarreal</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>0xf9063ec13eee8f96a20b89bd687d0a5f1a3197a4408eb58240f63d72be7c644f</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>L19370490</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>1786621975</t>
+        </is>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>1786892400</t>
+        </is>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>320.885246</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>0x6df789a868c08b6d011dc9dc3fe38cf8be42973ee6e2b3513f1ae98f3a70e174</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>82.86999</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>1.7363</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Racing Santander +1</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Racing Santander vs Villarreal</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>0xeffd773f9a996fcdab4f40cb833c6db488621204b6af7959d07794c43de040c4</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>L19370490</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>1786621975</t>
+        </is>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>1786892400</t>
+        </is>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>112.556862</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>0x4061873586e14d63aeb0e4cdf23afafe5cd7b3c74fe59157daf06c85b8fd8796</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>44.82</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>1.305</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Racing Santander -0.5</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Racing Santander vs Villarreal</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>0xb811d0e9d1802cd3762a57ca8fc3a5399392dd37dec4f8d9fd37f0170ece0f50</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>L19370490</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>1786621975</t>
+        </is>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>1786892400</t>
+        </is>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>146.95082</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>0x8dda40aa7d3c4140b3e5ab6ab62f3db4f5a3730a15ebff80f0bda9807c704ca2</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>27.87224</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>1.5325</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Celta de Vigo vs Osasuna</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>Celta de Vigo</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>0x0f075dae0a586d46b2073e126cbc52393dc2ff99a26953308f94b3b2751764b7</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>L19370496</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>1786619056</t>
+        </is>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>1786908600</t>
+        </is>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>52.342235</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>0x4565877a70aabfac9d4d4a2afcda9ace6e304d9bd921ce69a2149c76528e271a</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>0xb363112BA7ed93A221Efb405496e4Fa3BE119D81</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>1.285</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Sevilla vs Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>0x2b9c4f75049808a8d2b353d1c6e902da151d2fea092e70f08cdd4ac2ffbfd8a6</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>L19370582</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>1786614389</t>
+        </is>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>1786822200</t>
+        </is>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>175.438596</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>0x562837a4689bf537ab0502cfe5d722bafc1833bc972e329ba5399cd7649a219c</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>0xda132f38d7cbcb404e0db6126292d55c3614e3311c2670ac15890a14a94cdaea</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>1786586644</t>
+        </is>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>7.769231</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>0x27be56be09649bd460766fe27df249788cf4d7ad87d19f5f9a8bfba225e519b9</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>1.52676</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>1.7512</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr"/>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
           <t>0x32766ed977cae312bdb45c44b07e70207b356db986ef0293796496f193e13d1e</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="M60" t="inlineStr">
         <is>
           <t>L19370598</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P52" t="inlineStr">
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R52" t="inlineStr">
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
         <is>
           <t>1786578252</t>
         </is>
       </c>
-      <c r="S52" t="inlineStr">
+      <c r="S60" t="inlineStr">
         <is>
           <t>1786815000</t>
         </is>
       </c>
-      <c r="T52" t="inlineStr">
+      <c r="T60" t="inlineStr">
         <is>
           <t>2.032293</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr">
+      <c r="U60" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V52" t="inlineStr">
+      <c r="V60" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/La Liga/trades.xlsx
+++ b/data/sxbet/ligas/La Liga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V60"/>
+  <dimension ref="A1:V63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,12 +531,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xd1b390848190c00232506eacbdf3de0c4fb3341dfed7509ed5d82ce98fefb68f</t>
+          <t>0x1120510e2af332af623aaf2def0c6f3242599093c43023de2de2d4d05ab3cf2a</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xF77AceaD3B354FCD16E60e4a6AbEdB7796b7094E</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -546,22 +546,22 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>32.12</t>
+          <t>377.95875</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4275</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Over 2.5</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -571,27 +571,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Espanyol vs Levante</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0x3b15a29eb768ad2d602f53ab34fccc5aa069fa3f722408b8d6710612a74fb3b6</t>
+          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19370489</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +616,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786708635</t>
+          <t>1786711945</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>75.134503</t>
+          <t>905.290419</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +643,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x7f0e441004fffd1fe881714dcaf8f0dc3d32bf046fffc69dff440d1672c7714f</t>
+          <t>0x30eb86e1b4397e3d4423a777fb6ed5785a789a492af35964b27097d9ff0e0f0c</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0xF77AceaD3B354FCD16E60e4a6AbEdB7796b7094E</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,22 +658,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>283.53</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.5787</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Sevilla -0.5</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -683,27 +683,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Espanyol vs Levante</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0x49dabceb14c4027b90dc4d8270cdfd514fe4070867c271757ed62270904d3f7a</t>
+          <t>0xe6296471d7ae7834d2fe168f940eb41253ef7ab571b7c4a8e391bbd18f47f2c0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19370489</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786708635</t>
+          <t>1786711930</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>101.563715</t>
+          <t>679.113772</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,23 +755,23 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x0215ba1f4a546ce50b568125670efe2f3cb594679153dfd16e003add1ff1670b</t>
+          <t>0x91aab92dfd48273588feb93e3faba11fc9f8c1f944d65a4451e2337d0b6be50e</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
+          <t>0xa1B345AC7dAd7aA730fe22f3a6379de06a7f6B61</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>35.07</t>
+          <t>21.77517</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.1062</t>
+          <t>1.1075</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -832,7 +832,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786707052</t>
+          <t>1786710306</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>330.070588</t>
+          <t>202.559721</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,31 +859,39 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0x0ae19247ab2948e516f5ce1b5b97bbb5e71f6c997858511110a66b7335904c07</t>
+          <t>0xd1b390848190c00232506eacbdf3de0c4fb3341dfed7509ed5d82ce98fefb68f</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>108.84</t>
+          <t>32.12</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.4275</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H5" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -891,27 +899,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Espanyol vs Levante</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x78a4cf6b02d047f006e2c80b80d1bba724ebd9a508d0cce70fc13d1dcc698bd3</t>
+          <t>0x3b15a29eb768ad2d602f53ab34fccc5aa069fa3f722408b8d6710612a74fb3b6</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370489</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -936,17 +944,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786706935</t>
+          <t>1786708635</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>164.909091</t>
+          <t>75.134503</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -963,31 +971,39 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x6ccfb889ade998fdea5a13e6f95b82afc8d38ea46dc3cdb05777d19b61d38489</t>
+          <t>0x7f0e441004fffd1fe881714dcaf8f0dc3d32bf046fffc69dff440d1672c7714f</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>38.96365</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.1675</t>
+          <t>1.5787</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -995,27 +1011,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Espanyol vs Levante</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
+          <t>0x49dabceb14c4027b90dc4d8270cdfd514fe4070867c271757ed62270904d3f7a</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370489</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1040,17 +1056,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786706838</t>
+          <t>1786708635</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>232.618806</t>
+          <t>101.563715</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1067,23 +1083,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0xece691e2f3fa898d49c7d3c991735f87e5c4d9d84718f8019f8459dd0608d12b</t>
+          <t>0x0215ba1f4a546ce50b568125670efe2f3cb594679153dfd16e003add1ff1670b</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xa1B345AC7dAd7aA730fe22f3a6379de06a7f6B61</t>
+          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>35.07</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.1663</t>
+          <t>1.1062</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1099,27 +1115,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
+          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1144,17 +1160,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786704868</t>
+          <t>1786707052</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>739.849624</t>
+          <t>330.070588</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1171,7 +1187,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x233e63e043940ed7a303b95c191bb2fe090edd21f5a29da25bf50df5b3a936de</t>
+          <t>0x0ae19247ab2948e516f5ce1b5b97bbb5e71f6c997858511110a66b7335904c07</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1182,17 +1198,17 @@
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>136.87</t>
+          <t>108.84</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.545</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1203,27 +1219,27 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Espanyol vs Levante</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x0b6a22493b6514fc21dd836e8493df5b744432e27aa48ef80289f94befb19490</t>
+          <t>0x78a4cf6b02d047f006e2c80b80d1bba724ebd9a508d0cce70fc13d1dcc698bd3</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>L19370489</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1248,17 +1264,17 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786696941</t>
+          <t>1786706935</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>251.137615</t>
+          <t>164.909091</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1275,23 +1291,23 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x465f902491d3a3e6b99a234c6b14c18b007ae7c4d5a71ccdd550d024861bb7b6</t>
+          <t>0x6ccfb889ade998fdea5a13e6f95b82afc8d38ea46dc3cdb05777d19b61d38489</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xFBd63A3Adf898EfFf1e5A017f98756dC760eBfb8</t>
+          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>61.46</t>
+          <t>38.96365</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.1663</t>
+          <t>1.1675</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1352,7 +1368,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786692208</t>
+          <t>1786706838</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1362,7 +1378,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>369.684211</t>
+          <t>232.618806</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1379,28 +1395,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xbf1a151f615bf3f9a9e616e3c50bbe9cfcae4e7a99f9ce723f49c93c83cdc9d0</t>
+          <t>0xece691e2f3fa898d49c7d3c991735f87e5c4d9d84718f8019f8459dd0608d12b</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0x30E3f83573EbFc7274EeAfD586D930F7392F5650</t>
+          <t>0xa1B345AC7dAd7aA730fe22f3a6379de06a7f6B61</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.16999</t>
+          <t>123</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.5875</t>
+          <t>1.1663</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -1411,27 +1427,27 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1456,17 +1472,17 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786687820</t>
+          <t>1786704868</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>1.991472</t>
+          <t>739.849624</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1483,39 +1499,31 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x11994251df996a13dca305742c6cfa502ae27aa5f4bd0111f29dc7341166926a</t>
+          <t>0x233e63e043940ed7a303b95c191bb2fe090edd21f5a29da25bf50df5b3a936de</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0xdFC5342F5d4bF9F317c0CBf71121AC6FA92d8fbf</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>45.715</t>
+          <t>136.87</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.2788</t>
+          <t>1.545</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Osasuna</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -1523,27 +1531,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Celta de Vigo vs Osasuna</t>
+          <t>Espanyol vs Levante</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x9993d963f79cc9f688d38136ed8af60ad8c5e128ae668d0af49645c4ec2e0c25</t>
+          <t>0x0b6a22493b6514fc21dd836e8493df5b744432e27aa48ef80289f94befb19490</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19370496</t>
+          <t>L19370489</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1568,17 +1576,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786684730</t>
+          <t>1786696941</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786908600</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>251.137615</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1595,23 +1603,23 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x03eaa48ad5cba7703834b4eb4188b2512fc59fc66ce1a132f347fb208e62190e</t>
+          <t>0x465f902491d3a3e6b99a234c6b14c18b007ae7c4d5a71ccdd550d024861bb7b6</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
+          <t>0xFBd63A3Adf898EfFf1e5A017f98756dC760eBfb8</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>29.16362</t>
+          <t>61.46</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.1075</t>
+          <t>1.1663</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1627,27 +1635,27 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1672,17 +1680,17 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786684614</t>
+          <t>1786692208</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>271.289488</t>
+          <t>369.684211</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1699,28 +1707,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xf7320171cfa1d2a4388cf7700c275208ec77d1f0986bae7466346769cb38d5b4</t>
+          <t>0xbf1a151f615bf3f9a9e616e3c50bbe9cfcae4e7a99f9ce723f49c93c83cdc9d0</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
+          <t>0x30E3f83573EbFc7274EeAfD586D930F7392F5650</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.05797</t>
+          <t>1.16999</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.1075</t>
+          <t>1.5875</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -1746,7 +1754,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -1776,7 +1784,7 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786684161</t>
+          <t>1786687820</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -1786,7 +1794,7 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>9.841581</t>
+          <t>1.991472</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1803,31 +1811,39 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x2c667f7cd0a5ee4597a318320db656e61b2fe595b68044cdbb02a35a2c508f11</t>
+          <t>0x11994251df996a13dca305742c6cfa502ae27aa5f4bd0111f29dc7341166926a</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
+          <t>0xdFC5342F5d4bF9F317c0CBf71121AC6FA92d8fbf</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>122.1</t>
+          <t>45.715</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>1.2788</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
       <c r="H14" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -1835,27 +1851,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Celta de Vigo vs Osasuna</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
+          <t>0x9993d963f79cc9f688d38136ed8af60ad8c5e128ae668d0af49645c4ec2e0c25</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370496</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1880,17 +1896,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786679771</t>
+          <t>1786684730</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786908600</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1907,7 +1923,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0xef898b845c993efce01f949a5b4165e91083d76283cd50b5ccb38113072d39a3</t>
+          <t>0x03eaa48ad5cba7703834b4eb4188b2512fc59fc66ce1a132f347fb208e62190e</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1918,12 +1934,12 @@
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>122.1</t>
+          <t>29.16362</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>1.1075</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1939,27 +1955,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
+          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1984,17 +2000,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786677944</t>
+          <t>1786684614</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>271.289488</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2011,7 +2027,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xec715718ce1e06f5bfd1790eedf07c987dbe7e219a72c5facd15377495db5263</t>
+          <t>0xf7320171cfa1d2a4388cf7700c275208ec77d1f0986bae7466346769cb38d5b4</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2022,12 +2038,12 @@
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>122.1</t>
+          <t>1.05797</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>1.1075</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -2043,27 +2059,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
+          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2088,17 +2104,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786676253</t>
+          <t>1786684161</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>9.841581</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2115,28 +2131,28 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x0e7729ad6b4a9824864f6ac006c58fb19124ac050b08faef247ac7a176fd96ee</t>
+          <t>0x2c667f7cd0a5ee4597a318320db656e61b2fe595b68044cdbb02a35a2c508f11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xB66Aa9923E7a8920151375e186E6718064dd4f08</t>
+          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>245.05482</t>
+          <t>122.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.755</t>
+          <t>1.165</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -2162,7 +2178,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0x32766ed977cae312bdb45c44b07e70207b356db986ef0293796496f193e13d1e</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -2192,7 +2208,7 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786669488</t>
+          <t>1786679771</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
@@ -2202,7 +2218,7 @@
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>324.575921</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2219,28 +2235,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0x8d79a50b7331e59ea36d27efa5d99d53e26dfd1be15401e254a4cc43e280ff2f</t>
+          <t>0xef898b845c993efce01f949a5b4165e91083d76283cd50b5ccb38113072d39a3</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>0x9737E0E3E8EE2DD6B8A7E19D1507EcB3221b5483</t>
+          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>4.89999</t>
+          <t>122.1</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.5863</t>
+          <t>1.165</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -2251,27 +2267,27 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -2296,17 +2312,17 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786667446</t>
+          <t>1786677944</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>8.358192</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2323,28 +2339,28 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0x11476693f9b725995aedcf0e75acf05d19a0f1647da3059f334da311f0f1e922</t>
+          <t>0xec715718ce1e06f5bfd1790eedf07c987dbe7e219a72c5facd15377495db5263</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.19253</t>
+          <t>122.1</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.5713</t>
+          <t>1.165</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2355,27 +2371,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0x10c92f089fb69109ac5beea7c82a0e1cd2f23257cd842348710e2598be68bc48</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2400,17 +2416,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786664168</t>
+          <t>1786676253</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>2.08758</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2427,23 +2443,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x046492cfcbf4e5a3ced4caa85326fa8b44dbff1fb248a61a7fa6c8a8d2d9c1f8</t>
+          <t>0x0e7729ad6b4a9824864f6ac006c58fb19124ac050b08faef247ac7a176fd96ee</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xB66Aa9923E7a8920151375e186E6718064dd4f08</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>245.05482</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.5962</t>
+          <t>1.755</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -2474,7 +2490,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0xfcdcf41a0510583d5bb65df7215b5101ff435808043952db2a0364f1424743db</t>
+          <t>0x32766ed977cae312bdb45c44b07e70207b356db986ef0293796496f193e13d1e</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -2504,7 +2520,7 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786663762</t>
+          <t>1786669488</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
@@ -2514,7 +2530,7 @@
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>8.385744</t>
+          <t>324.575921</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2531,28 +2547,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0xe376b22b83ba1a0d5c58e6763337d61f4445c85bfdc77949472d41c7c47e42b6</t>
+          <t>0x8d79a50b7331e59ea36d27efa5d99d53e26dfd1be15401e254a4cc43e280ff2f</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
+          <t>0x9737E0E3E8EE2DD6B8A7E19D1507EcB3221b5483</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>4.89999</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.5863</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2563,27 +2579,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Celta de Vigo vs Osasuna</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19370496</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2608,17 +2624,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786657450</t>
+          <t>1786667446</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786908600</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>8.358192</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2635,27 +2651,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x4e949c2076e8faf4dcc272acfa8d69c62442324aca8ceeb5820b8348c74f13f6</t>
+          <t>0x11476693f9b725995aedcf0e75acf05d19a0f1647da3059f334da311f0f1e922</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>1.19253</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.5713</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2663,11 +2675,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Tie</t>
-        </is>
-      </c>
+      <c r="G22" t="inlineStr"/>
       <c r="H22" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -2675,27 +2683,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Celta de Vigo vs Osasuna</t>
+          <t>Racing Santander vs Villarreal</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
+          <t>0x10c92f089fb69109ac5beea7c82a0e1cd2f23257cd842348710e2598be68bc48</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19370496</t>
+          <t>L19370490</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2720,17 +2728,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786657449</t>
+          <t>1786664168</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786908600</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>52.967742</t>
+          <t>2.08758</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2747,7 +2755,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0xd54151c9cd066d8a5e7714f77ebc5e24ee2aac3e2c8a52a50b3a6becd0bac875</t>
+          <t>0x046492cfcbf4e5a3ced4caa85326fa8b44dbff1fb248a61a7fa6c8a8d2d9c1f8</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2758,12 +2766,12 @@
       <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
-          <t>112.94</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.6625</t>
+          <t>1.5962</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -2794,7 +2802,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0x78a4cf6b02d047f006e2c80b80d1bba724ebd9a508d0cce70fc13d1dcc698bd3</t>
+          <t>0xfcdcf41a0510583d5bb65df7215b5101ff435808043952db2a0364f1424743db</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -2824,7 +2832,7 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786656774</t>
+          <t>1786663762</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
@@ -2834,7 +2842,7 @@
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>170.475472</t>
+          <t>8.385744</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2851,28 +2859,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0x835c08ffc86c9c616d8c107e844ff9658b10b62372398122a4f7ded5bb28a516</t>
+          <t>0xe376b22b83ba1a0d5c58e6763337d61f4445c85bfdc77949472d41c7c47e42b6</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0x8e9bE2B8b636Cc98b01957cE9D4E3B62cF579080</t>
+          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2883,27 +2891,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Celta de Vigo vs Osasuna</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370496</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2928,17 +2936,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786651844</t>
+          <t>1786657450</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786908600</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>8.492552</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2955,31 +2963,39 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x45cc84f2dd4c1b45226a895eead76c109d5af22eac83562ab8aa23758f8a6b5e</t>
+          <t>0x4e949c2076e8faf4dcc272acfa8d69c62442324aca8ceeb5820b8348c74f13f6</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xa3786b93377213A42Bf1d3261d373cE67Cf2AA67</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H25" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -2987,27 +3003,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Celta de Vigo vs Osasuna</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370496</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3032,17 +3048,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786651814</t>
+          <t>1786657449</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786908600</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>42.735043</t>
+          <t>52.967742</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3059,23 +3075,23 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0x213398a7cadc42743f3aee31a89c45cc1f9c78136646bd816983864c34b13f79</t>
+          <t>0xd54151c9cd066d8a5e7714f77ebc5e24ee2aac3e2c8a52a50b3a6becd0bac875</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x4feB57379592eb94c51c014553de6EEbD4d42577</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
       <c r="D26" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>112.94</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.6625</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -3091,27 +3107,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Celta de Vigo vs Osasuna</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
+          <t>0x78a4cf6b02d047f006e2c80b80d1bba724ebd9a508d0cce70fc13d1dcc698bd3</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19370496</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3136,17 +3152,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786651743</t>
+          <t>1786656774</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1786908600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>170.475472</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3163,12 +3179,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x0adf7a0f94fb74bebb4e5acb49582e1f91e3ae462b204becaedfbe0f50714ede</t>
+          <t>0x835c08ffc86c9c616d8c107e844ff9658b10b62372398122a4f7ded5bb28a516</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x06a603b688E676702ec63D735CAe4A57ff71B3e1</t>
+          <t>0x8e9bE2B8b636Cc98b01957cE9D4E3B62cF579080</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -3179,7 +3195,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -3240,7 +3256,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786651718</t>
+          <t>1786651844</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3250,7 +3266,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>8.546991</t>
+          <t>8.492552</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3267,18 +3283,18 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0xc33e951dfa8d84c01759f86fe63dfc68ddc2b547988e3a32445d72b681f7f7a5</t>
+          <t>0x45cc84f2dd4c1b45226a895eead76c109d5af22eac83562ab8aa23758f8a6b5e</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
+          <t>0xa3786b93377213A42Bf1d3261d373cE67Cf2AA67</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -3344,7 +3360,7 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786651637</t>
+          <t>1786651814</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
@@ -3354,7 +3370,7 @@
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>8.546991</t>
+          <t>42.735043</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3371,28 +3387,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x948b3c3ece530e62252af65b92bdd73725833fe7355d5496ab1d4f6d84e43cc4</t>
+          <t>0x213398a7cadc42743f3aee31a89c45cc1f9c78136646bd816983864c34b13f79</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
+          <t>0x4feB57379592eb94c51c014553de6EEbD4d42577</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3403,27 +3419,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Celta de Vigo vs Osasuna</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370496</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3448,17 +3464,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786651588</t>
+          <t>1786651743</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786908600</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>1.709402</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3475,18 +3491,18 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x7578c65431424d3ae35de659ad6d246a7814cbb553d85319bf0968700f7bca4a</t>
+          <t>0x0adf7a0f94fb74bebb4e5acb49582e1f91e3ae462b204becaedfbe0f50714ede</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+          <t>0x06a603b688E676702ec63D735CAe4A57ff71B3e1</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -3552,7 +3568,7 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786651585</t>
+          <t>1786651718</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
@@ -3562,7 +3578,7 @@
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>17.094</t>
+          <t>8.546991</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3579,18 +3595,18 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0x28bc2779df67c8165804579669b7a40ef9e3a34f89e4d9d4c81a44f6c49d8be2</t>
+          <t>0xc33e951dfa8d84c01759f86fe63dfc68ddc2b547988e3a32445d72b681f7f7a5</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x2F9aCBd9B89C6eF3bc3Dc2B0F0cCD0E0936BF912</t>
+          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -3656,7 +3672,7 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786651567</t>
+          <t>1786651637</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
@@ -3666,7 +3682,7 @@
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>17.094</t>
+          <t>8.546991</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3683,18 +3699,18 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x0eaa76f318c30c9b01a36fedfdc1b48daafadd063ed5c90a74fd0908bdecfce3</t>
+          <t>0x948b3c3ece530e62252af65b92bdd73725833fe7355d5496ab1d4f6d84e43cc4</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x6203b6338991Ec84C8A8f5ef06bC17ceB1395Ddb</t>
+          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -3760,7 +3776,7 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786651567</t>
+          <t>1786651588</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
@@ -3770,7 +3786,7 @@
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>11.965812</t>
+          <t>1.709402</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3787,18 +3803,18 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0xcc54eb94d459bc0b9a34beb78c07fafbc7c1f3e7c6d43846f17fb20856c43d24</t>
+          <t>0x7578c65431424d3ae35de659ad6d246a7814cbb553d85319bf0968700f7bca4a</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -3864,7 +3880,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786651559</t>
+          <t>1786651585</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3874,7 +3890,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>42.735043</t>
+          <t>17.094</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3891,12 +3907,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x1b14ab3ce842bb0ded035add24fcdd28a77380141c189ae36b1f623e70dff465</t>
+          <t>0x28bc2779df67c8165804579669b7a40ef9e3a34f89e4d9d4c81a44f6c49d8be2</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+          <t>0x2F9aCBd9B89C6eF3bc3Dc2B0F0cCD0E0936BF912</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -3968,7 +3984,7 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786651559</t>
+          <t>1786651567</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
@@ -3995,18 +4011,18 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x31a8e64cfb4307b5b608318a4e037810f68fe9bef13258aa7d3c45dd664c0ad3</t>
+          <t>0x0eaa76f318c30c9b01a36fedfdc1b48daafadd063ed5c90a74fd0908bdecfce3</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x03d4fFC791EE4A80194C9d9782E7D56407b242Ed</t>
+          <t>0x6203b6338991Ec84C8A8f5ef06bC17ceB1395Ddb</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4072,7 +4088,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786651558</t>
+          <t>1786651567</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4082,7 +4098,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>25.641026</t>
+          <t>11.965812</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4099,18 +4115,18 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0x1c244dc1d052ae42a83bf5640bcba1b28bb9c28853e7f42713fa4fddcb66b677</t>
+          <t>0xcc54eb94d459bc0b9a34beb78c07fafbc7c1f3e7c6d43846f17fb20856c43d24</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4176,7 +4192,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786651550</t>
+          <t>1786651559</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4186,7 +4202,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>8.546991</t>
+          <t>42.735043</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4203,39 +4219,31 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x20fcd5dbfafe538f08c15c6b35af5d546fa35aa588ef9811c9696ac39843c736</t>
+          <t>0x1b14ab3ce842bb0ded035add24fcdd28a77380141c189ae36b1f623e70dff465</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Deportivo Alaves -0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
       <c r="H37" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -4243,27 +4251,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4288,17 +4296,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786640471</t>
+          <t>1786651559</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>12.195122</t>
+          <t>17.094</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4315,39 +4323,31 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x48d06bf1eb103be3b93f605ad7b9ed301f228fa4dfae557dca83434f1d5e0c1a</t>
+          <t>0x31a8e64cfb4307b5b608318a4e037810f68fe9bef13258aa7d3c45dd664c0ad3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x03d4fFC791EE4A80194C9d9782E7D56407b242Ed</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>26.96</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Deportivo Alaves -0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -4355,27 +4355,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4400,17 +4400,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786640450</t>
+          <t>1786651558</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>65.957187</t>
+          <t>25.641026</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4427,27 +4427,23 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0xe750c1fb5c3ef7edfc166b18659be46b00e3cc96d5ae299b162166175d07245f</t>
+          <t>0x1c244dc1d052ae42a83bf5640bcba1b28bb9c28853e7f42713fa4fddcb66b677</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4455,11 +4451,7 @@
           <t>Under/Over (2.5)</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+      <c r="G39" t="inlineStr"/>
       <c r="H39" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -4467,27 +4459,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0x0a08c3d7f08812839b48fc67d5842cc07f2a5e67ce2a26c46d0210680fda2f99</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4512,17 +4504,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786639065</t>
+          <t>1786651550</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>36.891954</t>
+          <t>8.546991</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4539,7 +4531,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0xdc16a40eba6eeb7462531fd3b01240a8f58f0ea20568efbaba25b17131094f2e</t>
+          <t>0x20fcd5dbfafe538f08c15c6b35af5d546fa35aa588ef9811c9696ac39843c736</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4559,17 +4551,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.4213</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves -0.5</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4579,27 +4571,27 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
+          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -4624,17 +4616,17 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786633518</t>
+          <t>1786640471</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>11.869436</t>
+          <t>12.195122</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4651,7 +4643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x1b67e861f8e383798d979684797f608bfad6122cc87844f2a37a8cf06e019030</t>
+          <t>0x48d06bf1eb103be3b93f605ad7b9ed301f228fa4dfae557dca83434f1d5e0c1a</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4666,22 +4658,22 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>53.83</t>
+          <t>26.96</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves -0.5</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -4691,27 +4683,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
+          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4736,17 +4728,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786633487</t>
+          <t>1786640450</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>128.166667</t>
+          <t>65.957187</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4763,31 +4755,39 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0x909a230aebd5eb00de6012a0eb69301784b515acf69e93ee497d243bd3ce212f</t>
+          <t>0xe750c1fb5c3ef7edfc166b18659be46b00e3cc96d5ae299b162166175d07245f</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0xbcD65d7e2D58b95Cf434eB65a82b9FD5b682D144</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>72.15999</t>
+          <t>20.06</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Over 2.5</t>
+        </is>
+      </c>
       <c r="H42" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -4795,27 +4795,27 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Racing Santander vs Villarreal</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
+          <t>0x0a08c3d7f08812839b48fc67d5842cc07f2a5e67ce2a26c46d0210680fda2f99</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370490</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -4840,17 +4840,17 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786632901</t>
+          <t>1786639065</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>120.26665</t>
+          <t>36.891954</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4867,31 +4867,39 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0x081a76991e0701cf3dbcaa6ccbdd7d9dd69242e812c8b7e977517fe836423751</t>
+          <t>0xdc16a40eba6eeb7462531fd3b01240a8f58f0ea20568efbaba25b17131094f2e</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.1038</t>
+          <t>1.4213</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
       <c r="H43" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -4899,27 +4907,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Espanyol vs Levante</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xd36fc2a623f22222f73350186e7d08c0d31b2d895ac24a68dc8408d4e98bf55a</t>
+          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19370489</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4944,17 +4952,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786631513</t>
+          <t>1786633518</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>76.240964</t>
+          <t>11.869436</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -4971,31 +4979,39 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x6f1c770a5b9534dbfff85f398a28d171effe0e02699c6558a37a881468f3090e</t>
+          <t>0x1b67e861f8e383798d979684797f608bfad6122cc87844f2a37a8cf06e019030</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>53.83</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.1013</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
       <c r="H44" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -5018,7 +5034,7 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
+          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -5048,7 +5064,7 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786631323</t>
+          <t>1786633487</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
@@ -5058,7 +5074,7 @@
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>78.123457</t>
+          <t>128.166667</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5075,28 +5091,28 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0xffde28cdfe7ae2b6324278e8117e605bc5c2ecb236877e683d06b5cbe620b2b1</t>
+          <t>0x909a230aebd5eb00de6012a0eb69301784b515acf69e93ee497d243bd3ce212f</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xbcD65d7e2D58b95Cf434eB65a82b9FD5b682D144</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
       <c r="D45" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>72.15999</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G45" t="inlineStr"/>
@@ -5122,7 +5138,7 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
+          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
@@ -5152,7 +5168,7 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786631207</t>
+          <t>1786632901</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
@@ -5162,7 +5178,7 @@
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>67.333333</t>
+          <t>120.26665</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5179,7 +5195,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x1542e94d97dca7a28f2bf2b946f64e1fefc9fc04f50a7622a8a2791d01c58796</t>
+          <t>0x081a76991e0701cf3dbcaa6ccbdd7d9dd69242e812c8b7e977517fe836423751</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5190,17 +5206,17 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>11.85998</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.7113</t>
+          <t>1.1038</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -5211,27 +5227,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Espanyol vs Levante</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
+          <t>0xd36fc2a623f22222f73350186e7d08c0d31b2d895ac24a68dc8408d4e98bf55a</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370489</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5256,17 +5272,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786630102</t>
+          <t>1786631513</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>16.67484</t>
+          <t>76.240964</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5283,28 +5299,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x9ff18d48c5ac1507ef9b6a3dfaf34f20966e85ee30cbd99e0df47a940abf1d32</t>
+          <t>0x6f1c770a5b9534dbfff85f398a28d171effe0e02699c6558a37a881468f3090e</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7.91</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.4412</t>
+          <t>1.1013</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -5315,27 +5331,27 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x776caca6c8b9cb32d9a7b2ec2b4f40bbb630001b4db7c24175062af09044b7dd</t>
+          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -5360,17 +5376,17 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786626342</t>
+          <t>1786631323</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>11.331445</t>
+          <t>78.123457</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5387,28 +5403,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0x50f0b3572b92fd4a3268a217b75ca6b4a52b72077d0276df9d0d123d8b3ebc60</t>
+          <t>0xffde28cdfe7ae2b6324278e8117e605bc5c2ecb236877e683d06b5cbe620b2b1</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>16.18903</t>
+          <t>11.11</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.4412</t>
+          <t>1.165</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -5434,7 +5450,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0x776caca6c8b9cb32d9a7b2ec2b4f40bbb630001b4db7c24175062af09044b7dd</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -5464,7 +5480,7 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786626327</t>
+          <t>1786631207</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
@@ -5474,7 +5490,7 @@
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>36.68902</t>
+          <t>67.333333</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5491,28 +5507,28 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x2d1550913dec85439afda8d85c6033895212998f22943ab968dee5cbd7d7e7a2</t>
+          <t>0x1542e94d97dca7a28f2bf2b946f64e1fefc9fc04f50a7622a8a2791d01c58796</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>35.45869</t>
+          <t>11.85998</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.2537</t>
+          <t>1.7113</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -5538,7 +5554,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x0596e7ef887839f51f014583ff32fca0dbfab0916b17c3d05d740985b59eabc3</t>
+          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -5568,7 +5584,7 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786624561</t>
+          <t>1786630102</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
@@ -5578,7 +5594,7 @@
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>139.73868</t>
+          <t>16.67484</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5595,7 +5611,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x6f809dd95ba0a7f41584a66e0979cb2c04ebaeefb6e5d949b0bfd9c53278c063</t>
+          <t>0x9ff18d48c5ac1507ef9b6a3dfaf34f20966e85ee30cbd99e0df47a940abf1d32</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -5611,12 +5627,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.7163</t>
+          <t>1.4412</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -5642,7 +5658,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
+          <t>0x776caca6c8b9cb32d9a7b2ec2b4f40bbb630001b4db7c24175062af09044b7dd</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -5672,7 +5688,7 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786623012</t>
+          <t>1786626342</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
@@ -5682,7 +5698,7 @@
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>6.980803</t>
+          <t>11.331445</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5699,7 +5715,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0xddff1b4ca7359c6045ede1bd2995e1e57620811dc33cc7338113c5449dccd695</t>
+          <t>0x50f0b3572b92fd4a3268a217b75ca6b4a52b72077d0276df9d0d123d8b3ebc60</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -5710,17 +5726,17 @@
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>28.91904</t>
+          <t>16.18903</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.4412</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (1.5)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -5746,7 +5762,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0xf684bc2655869d0024c7de5a1f2b51fb35813185b075bf3cc8d5f2fe8ce176b5</t>
+          <t>0x776caca6c8b9cb32d9a7b2ec2b4f40bbb630001b4db7c24175062af09044b7dd</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -5776,7 +5792,7 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786622982</t>
+          <t>1786626327</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
@@ -5786,7 +5802,7 @@
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>47.899031</t>
+          <t>36.68902</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5803,7 +5819,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0xb02e365f47ba9eaba62de63e4b14c94bf1b59d60c56188857359df36e7b10ef0</t>
+          <t>0x2d1550913dec85439afda8d85c6033895212998f22943ab968dee5cbd7d7e7a2</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -5814,17 +5830,17 @@
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>30.81465</t>
+          <t>35.45869</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.7113</t>
+          <t>1.2537</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (0.5)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5850,7 +5866,7 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
+          <t>0x0596e7ef887839f51f014583ff32fca0dbfab0916b17c3d05d740985b59eabc3</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
@@ -5880,7 +5896,7 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786622982</t>
+          <t>1786624561</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
@@ -5890,7 +5906,7 @@
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>43.32464</t>
+          <t>139.73868</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -5907,67 +5923,59 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0xb7f333fbe5a18daf831395020096fbb62febd43977f5f81366c99339b63d902d</t>
+          <t>0x6f809dd95ba0a7f41584a66e0979cb2c04ebaeefb6e5d949b0bfd9c53278c063</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>63.86</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.7163</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
           <t>La Liga</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Racing Santander</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>La Liga</t>
-        </is>
-      </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x1518c9a8caca0376f881601c848e03d81cd65f5d32c2b63a51625351cc193e86</t>
+          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -5992,17 +6000,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786621976</t>
+          <t>1786623012</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>152.501493</t>
+          <t>6.980803</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6019,7 +6027,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0x79454b5fc310a342a5ad62ccf677e7ea1c42b0e701cd313d0019ee8ec1faf7a2</t>
+          <t>0xddff1b4ca7359c6045ede1bd2995e1e57620811dc33cc7338113c5449dccd695</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6027,31 +6035,23 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>97.87</t>
+          <t>28.91904</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>1.6038</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Racing Santander</t>
-        </is>
-      </c>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -6059,27 +6059,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xf9063ec13eee8f96a20b89bd687d0a5f1a3197a4408eb58240f63d72be7c644f</t>
+          <t>0xf684bc2655869d0024c7de5a1f2b51fb35813185b075bf3cc8d5f2fe8ce176b5</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6104,17 +6104,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786621975</t>
+          <t>1786622982</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>320.885246</t>
+          <t>47.899031</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6131,7 +6131,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0x6df789a868c08b6d011dc9dc3fe38cf8be42973ee6e2b3513f1ae98f3a70e174</t>
+          <t>0xb02e365f47ba9eaba62de63e4b14c94bf1b59d60c56188857359df36e7b10ef0</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6139,31 +6139,23 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>82.86999</t>
+          <t>30.81465</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.7113</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Racing Santander +1</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -6171,27 +6163,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0xeffd773f9a996fcdab4f40cb833c6db488621204b6af7959d07794c43de040c4</t>
+          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6216,17 +6208,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786621975</t>
+          <t>1786622982</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>112.556862</t>
+          <t>43.32464</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6243,7 +6235,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0x4061873586e14d63aeb0e4cdf23afafe5cd7b3c74fe59157daf06c85b8fd8796</t>
+          <t>0xb7f333fbe5a18daf831395020096fbb62febd43977f5f81366c99339b63d902d</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6258,22 +6250,22 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>63.86</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>1.4187</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>La Liga</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Racing Santander -0.5</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6298,7 +6290,7 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0xb811d0e9d1802cd3762a57ca8fc3a5399392dd37dec4f8d9fd37f0170ece0f50</t>
+          <t>0x1518c9a8caca0376f881601c848e03d81cd65f5d32c2b63a51625351cc193e86</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
@@ -6328,7 +6320,7 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786621975</t>
+          <t>1786621976</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
@@ -6338,7 +6330,7 @@
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>146.95082</t>
+          <t>152.501493</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6355,7 +6347,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x8dda40aa7d3c4140b3e5ab6ab62f3db4f5a3730a15ebff80f0bda9807c704ca2</t>
+          <t>0x79454b5fc310a342a5ad62ccf677e7ea1c42b0e701cd313d0019ee8ec1faf7a2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6363,15 +6355,19 @@
           <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>27.87224</t>
+          <t>97.87</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.5325</t>
+          <t>1.305</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -6379,7 +6375,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
       <c r="H57" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -6387,27 +6387,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Celta de Vigo vs Osasuna</t>
+          <t>Racing Santander vs Villarreal</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0x0f075dae0a586d46b2073e126cbc52393dc2ff99a26953308f94b3b2751764b7</t>
+          <t>0xf9063ec13eee8f96a20b89bd687d0a5f1a3197a4408eb58240f63d72be7c644f</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19370496</t>
+          <t>L19370490</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6432,17 +6432,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786619056</t>
+          <t>1786621975</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1786908600</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>52.342235</t>
+          <t>320.885246</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6459,12 +6459,12 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x4565877a70aabfac9d4d4a2afcda9ace6e304d9bd921ce69a2149c76528e271a</t>
+          <t>0x6df789a868c08b6d011dc9dc3fe38cf8be42973ee6e2b3513f1ae98f3a70e174</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0xb363112BA7ed93A221Efb405496e4Fa3BE119D81</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6474,22 +6474,22 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>82.86999</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.7363</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (1)</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Racing Santander +1</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
@@ -6499,27 +6499,27 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Racing Santander vs Villarreal</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0x2b9c4f75049808a8d2b353d1c6e902da151d2fea092e70f08cdd4ac2ffbfd8a6</t>
+          <t>0xeffd773f9a996fcdab4f40cb833c6db488621204b6af7959d07794c43de040c4</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370490</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6544,17 +6544,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786614389</t>
+          <t>1786621975</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>175.438596</t>
+          <t>112.556862</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6571,12 +6571,12 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x562837a4689bf537ab0502cfe5d722bafc1833bc972e329ba5399cd7649a219c</t>
+          <t>0x4061873586e14d63aeb0e4cdf23afafe5cd7b3c74fe59157daf06c85b8fd8796</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6586,22 +6586,22 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>44.82</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.305</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Racing Santander -0.5</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -6611,27 +6611,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Racing Santander vs Villarreal</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0xda132f38d7cbcb404e0db6126292d55c3614e3311c2670ac15890a14a94cdaea</t>
+          <t>0xb811d0e9d1802cd3762a57ca8fc3a5399392dd37dec4f8d9fd37f0170ece0f50</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370490</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6656,17 +6656,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786586644</t>
+          <t>1786621975</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>7.769231</t>
+          <t>146.95082</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6683,23 +6683,23 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x27be56be09649bd460766fe27df249788cf4d7ad87d19f5f9a8bfba225e519b9</t>
+          <t>0x8dda40aa7d3c4140b3e5ab6ab62f3db4f5a3730a15ebff80f0bda9807c704ca2</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr">
         <is>
-          <t>1.52676</t>
+          <t>27.87224</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.7512</t>
+          <t>1.5325</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -6715,70 +6715,398 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
+          <t>Celta de Vigo vs Osasuna</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>Celta de Vigo</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>0x0f075dae0a586d46b2073e126cbc52393dc2ff99a26953308f94b3b2751764b7</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>L19370496</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>1786619056</t>
+        </is>
+      </c>
+      <c r="S60" t="inlineStr">
+        <is>
+          <t>1786908600</t>
+        </is>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>52.342235</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>0x4565877a70aabfac9d4d4a2afcda9ace6e304d9bd921ce69a2149c76528e271a</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>0xb363112BA7ed93A221Efb405496e4Fa3BE119D81</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>1.285</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>Sevilla vs Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>0x2b9c4f75049808a8d2b353d1c6e902da151d2fea092e70f08cdd4ac2ffbfd8a6</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>L19370582</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>1786614389</t>
+        </is>
+      </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>1786822200</t>
+        </is>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>175.438596</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>0x562837a4689bf537ab0502cfe5d722bafc1833bc972e329ba5399cd7649a219c</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
           <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
-      <c r="J60" t="inlineStr">
+      <c r="J62" t="inlineStr">
         <is>
           <t>Deportivo Alaves</t>
         </is>
       </c>
-      <c r="K60" t="inlineStr">
+      <c r="K62" t="inlineStr">
         <is>
           <t>Getafe</t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>0xda132f38d7cbcb404e0db6126292d55c3614e3311c2670ac15890a14a94cdaea</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>1786586644</t>
+        </is>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>7.769231</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>0x27be56be09649bd460766fe27df249788cf4d7ad87d19f5f9a8bfba225e519b9</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>1.52676</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1.7512</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr"/>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
         <is>
           <t>0x32766ed977cae312bdb45c44b07e70207b356db986ef0293796496f193e13d1e</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr">
+      <c r="M63" t="inlineStr">
         <is>
           <t>L19370598</t>
         </is>
       </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O60" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P60" t="inlineStr">
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q60" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R60" t="inlineStr">
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
         <is>
           <t>1786578252</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr">
+      <c r="S63" t="inlineStr">
         <is>
           <t>1786815000</t>
         </is>
       </c>
-      <c r="T60" t="inlineStr">
+      <c r="T63" t="inlineStr">
         <is>
           <t>2.032293</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr">
+      <c r="U63" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V60" t="inlineStr">
+      <c r="V63" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>

--- a/data/sxbet/ligas/La Liga/trades.xlsx
+++ b/data/sxbet/ligas/La Liga/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V63"/>
+  <dimension ref="A1:V83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,39 +531,31 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0x1120510e2af332af623aaf2def0c6f3242599093c43023de2de2d4d05ab3cf2a</t>
+          <t>0xa5a20e9d0f197b591eb18f096fd1a527d293b4cda63bb216876fa338536b2e12</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0xF77AceaD3B354FCD16E60e4a6AbEdB7796b7094E</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x0c0188D085B3Edc4EAcfF25cd747ca4A50882743</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>377.95875</t>
+          <t>17.49</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.1663</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -571,27 +563,27 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -616,17 +608,17 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786711945</t>
+          <t>1786719408</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>905.290419</t>
+          <t>105.203008</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,12 +635,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x30eb86e1b4397e3d4423a777fb6ed5785a789a492af35964b27097d9ff0e0f0c</t>
+          <t>0x6bb6d91a5738b1ff837d58cc7fb6b4141ebb3a593afef1cb6ddacf2385ed6c8b</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0xF77AceaD3B354FCD16E60e4a6AbEdB7796b7094E</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -658,22 +650,22 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>283.53</t>
+          <t>69.56</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.4175</t>
+          <t>1.1538</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sevilla -0.5</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -683,27 +675,27 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0xe6296471d7ae7834d2fe168f940eb41253ef7ab571b7c4a8e391bbd18f47f2c0</t>
+          <t>0xd6819e63d9fdd260d581d5fcd48c78ac9a6f09d840c4ec0307622a0bf1b1c03c</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -728,17 +720,17 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>1786711930</t>
+          <t>1786718381</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>679.113772</t>
+          <t>452.422764</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
@@ -755,31 +747,39 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0x91aab92dfd48273588feb93e3faba11fc9f8c1f944d65a4451e2337d0b6be50e</t>
+          <t>0xd7bea85c0dd610acde78afbf35a899d22ec152af67c61c69d8a5126e75857c74</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0xa1B345AC7dAd7aA730fe22f3a6379de06a7f6B61</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>21.77517</t>
+          <t>19.87</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.1075</t>
+          <t>1.1525</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
+          <t>Under/Over (3)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Over 3.0</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -787,27 +787,27 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
+          <t>0xd6819e63d9fdd260d581d5fcd48c78ac9a6f09d840c4ec0307622a0bf1b1c03c</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>1786710306</t>
+          <t>1786718105</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>202.559721</t>
+          <t>130.295082</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
@@ -859,39 +859,31 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0xd1b390848190c00232506eacbdf3de0c4fb3341dfed7509ed5d82ce98fefb68f</t>
+          <t>0xc6b691603711580a076d0665b098932503b34dbc7edabf2b331beadd4de7ff08</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>32.12</t>
+          <t>24.29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.4275</t>
+          <t>1.5913</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -899,27 +891,27 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Espanyol vs Levante</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0x3b15a29eb768ad2d602f53ab34fccc5aa069fa3f722408b8d6710612a74fb3b6</t>
+          <t>0xe6296471d7ae7834d2fe168f940eb41253ef7ab571b7c4a8e391bbd18f47f2c0</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>L19370489</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -944,17 +936,17 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>1786708635</t>
+          <t>1786716745</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>75.134503</t>
+          <t>41.082452</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
@@ -971,12 +963,12 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0x7f0e441004fffd1fe881714dcaf8f0dc3d32bf046fffc69dff440d1672c7714f</t>
+          <t>0x2ce37a8ca9e9d7b23d5f243f615d8bc8ee8757dfcd06a91a700e496d98ed9008</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -986,22 +978,22 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>58.78</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.5787</t>
+          <t>1.835</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Over 2.0</t>
+          <t>Over 0.5</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1011,27 +1003,27 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Espanyol vs Levante</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0x49dabceb14c4027b90dc4d8270cdfd514fe4070867c271757ed62270904d3f7a</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>L19370489</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -1056,17 +1048,17 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>1786708635</t>
+          <t>1786716720</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>101.563715</t>
+          <t>5.988</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
@@ -1083,23 +1075,27 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0x0215ba1f4a546ce50b568125670efe2f3cb594679153dfd16e003add1ff1670b</t>
+          <t>0x9c7490ef65afd377fd3ae5bb5192242277e8b790a9b69361000f90de4ebed8b7</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>35.07</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.1062</t>
+          <t>1.835</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -1107,7 +1103,11 @@
           <t>Under/Over (0.5)</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -1115,27 +1115,27 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -1160,17 +1160,17 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>1786707052</t>
+          <t>1786716718</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>330.070588</t>
+          <t>5.988</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
@@ -1187,31 +1187,39 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0x0ae19247ab2948e516f5ce1b5b97bbb5e71f6c997858511110a66b7335904c07</t>
+          <t>0xda2f237d060cc4d8152771f4b7bbf1f5be0102f58ff3f929a39915c0970e5a30</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>108.84</t>
+          <t>71.05</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.835</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -1234,7 +1242,7 @@
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0x78a4cf6b02d047f006e2c80b80d1bba724ebd9a508d0cce70fc13d1dcc698bd3</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -1264,7 +1272,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>1786706935</t>
+          <t>1786716714</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -1274,7 +1282,7 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>164.909091</t>
+          <t>85.08982</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
@@ -1291,23 +1299,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0x6ccfb889ade998fdea5a13e6f95b82afc8d38ea46dc3cdb05777d19b61d38489</t>
+          <t>0x5d7a7e1fd24980125bed72adc0d9d81399ee86019f08598816cf60baa292b783</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>38.96365</t>
+          <t>42.76997</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.1675</t>
+          <t>1.835</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -1315,7 +1327,11 @@
           <t>Under/Over (0.5)</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -1368,7 +1384,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>1786706838</t>
+          <t>1786716712</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -1378,7 +1394,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>232.618806</t>
+          <t>51.221521</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
@@ -1395,23 +1411,27 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0xece691e2f3fa898d49c7d3c991735f87e5c4d9d84718f8019f8459dd0608d12b</t>
+          <t>0xcd3616b6efa4615d1ee9272b275ae3d22c6b3116f457a1cf465bde12032b6aee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>0xa1B345AC7dAd7aA730fe22f3a6379de06a7f6B61</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>123</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.1663</t>
+          <t>1.835</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -1419,7 +1439,11 @@
           <t>Under/Over (0.5)</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -1472,7 +1496,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>1786704868</t>
+          <t>1786716507</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -1482,7 +1506,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>739.849624</t>
+          <t>5.988</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
@@ -1499,31 +1523,39 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0x233e63e043940ed7a303b95c191bb2fe090edd21f5a29da25bf50df5b3a936de</t>
+          <t>0xf3e99302e3367adbd86ea1a8a452f489139df83d66538a4264c59b0c10ee9edd</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>136.87</t>
+          <t>4.99998</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.545</t>
+          <t>1.835</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
       <c r="H11" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -1531,27 +1563,27 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Espanyol vs Levante</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>0x0b6a22493b6514fc21dd836e8493df5b744432e27aa48ef80289f94befb19490</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>L19370489</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1576,17 +1608,17 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>1786696941</t>
+          <t>1786716504</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>251.137615</t>
+          <t>5.988</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
@@ -1603,23 +1635,27 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0x465f902491d3a3e6b99a234c6b14c18b007ae7c4d5a71ccdd550d024861bb7b6</t>
+          <t>0x85aceb6eb23a67195e33cc52ed94a7664753ce147dcb7a2b1b006a7efbf0b1f1</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>0xFBd63A3Adf898EfFf1e5A017f98756dC760eBfb8</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>61.46</t>
+          <t>39.60997</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.1663</t>
+          <t>1.835</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1627,7 +1663,11 @@
           <t>Under/Over (0.5)</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
       <c r="H12" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -1680,7 +1720,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>1786692208</t>
+          <t>1786716500</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -1690,7 +1730,7 @@
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>369.684211</t>
+          <t>47.43709</t>
         </is>
       </c>
       <c r="U12" t="inlineStr">
@@ -1707,31 +1747,39 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0xbf1a151f615bf3f9a9e616e3c50bbe9cfcae4e7a99f9ce723f49c93c83cdc9d0</t>
+          <t>0x4674c75cab8b48edb6940948851912e67f6115bf6297bd1c27bc0c9d9e663d18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>0x30E3f83573EbFc7274EeAfD586D930F7392F5650</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.16999</t>
+          <t>54.09996</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>1.5875</t>
+          <t>1.835</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Over 0.5</t>
+        </is>
+      </c>
       <c r="H13" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -1739,27 +1787,27 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1784,17 +1832,17 @@
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>1786687820</t>
+          <t>1786716495</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>1.991472</t>
+          <t>64.790371</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
@@ -1811,12 +1859,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0x11994251df996a13dca305742c6cfa502ae27aa5f4bd0111f29dc7341166926a</t>
+          <t>0xb0cd4c5f96f60ba63fd41950ddb0a7424c0f22863a159a5b34bb118a4ff20753</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>0xdFC5342F5d4bF9F317c0CBf71121AC6FA92d8fbf</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1826,22 +1874,22 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45.715</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>1.2788</t>
+          <t>1.15</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (3)</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Over 3.0</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1851,27 +1899,27 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Celta de Vigo vs Osasuna</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>0x9993d963f79cc9f688d38136ed8af60ad8c5e128ae668d0af49645c4ec2e0c25</t>
+          <t>0xd6819e63d9fdd260d581d5fcd48c78ac9a6f09d840c4ec0307622a0bf1b1c03c</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>L19370496</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -1896,17 +1944,17 @@
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>1786684730</t>
+          <t>1786716348</t>
         </is>
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>1786908600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>164.0</t>
+          <t>92.733333</t>
         </is>
       </c>
       <c r="U14" t="inlineStr">
@@ -1923,23 +1971,23 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0x03eaa48ad5cba7703834b4eb4188b2512fc59fc66ce1a132f347fb208e62190e</t>
+          <t>0x2d63ea2ceae3956bac892c2d2e9f94d4c52d41d94b721fc41a14ea7ab98ea246</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
+          <t>0x0c0188D085B3Edc4EAcfF25cd747ca4A50882743</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>29.16362</t>
+          <t>12.66</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.1075</t>
+          <t>1.1663</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1955,27 +2003,27 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -2000,17 +2048,17 @@
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>1786684614</t>
+          <t>1786715832</t>
         </is>
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>271.289488</t>
+          <t>76.150376</t>
         </is>
       </c>
       <c r="U15" t="inlineStr">
@@ -2027,31 +2075,39 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0xf7320171cfa1d2a4388cf7700c275208ec77d1f0986bae7466346769cb38d5b4</t>
+          <t>0x68eacc7e7e60dfcc0155287942bbf73d19862b8e96aca8cc18a95e31448df523</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>0xb363112BA7ed93A221Efb405496e4Fa3BE119D81</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.05797</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>1.1075</t>
+          <t>1.2525</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
       <c r="H16" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -2059,27 +2115,27 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
+          <t>0x32766ed977cae312bdb45c44b07e70207b356db986ef0293796496f193e13d1e</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -2104,17 +2160,17 @@
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>1786684161</t>
+          <t>1786715486</t>
         </is>
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>9.841581</t>
+          <t>99.009901</t>
         </is>
       </c>
       <c r="U16" t="inlineStr">
@@ -2131,23 +2187,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0x2c667f7cd0a5ee4597a318320db656e61b2fe595b68044cdbb02a35a2c508f11</t>
+          <t>0x2351dac3bd64c3881f00771d26c8ac962507b6574a4e12879a08f1881f104a79</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
+          <t>0x0c0188D085B3Edc4EAcfF25cd747ca4A50882743</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>122.1</t>
+          <t>30.1</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>1.1075</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -2163,27 +2219,27 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
+          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -2208,17 +2264,17 @@
       </c>
       <c r="R17" t="inlineStr">
         <is>
-          <t>1786679771</t>
+          <t>1786715086</t>
         </is>
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T17" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>280.0</t>
         </is>
       </c>
       <c r="U17" t="inlineStr">
@@ -2235,7 +2291,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0xef898b845c993efce01f949a5b4165e91083d76283cd50b5ccb38113072d39a3</t>
+          <t>0x9734b396945ef9baa37f98b5e809c53b9251d92300870d1db0f9ab0bbb53eb57</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2246,12 +2302,12 @@
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>122.1</t>
+          <t>0.98223</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>1.1875</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2312,7 +2368,7 @@
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>1786677944</t>
+          <t>1786714669</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
@@ -2322,7 +2378,7 @@
       </c>
       <c r="T18" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>5.23856</t>
         </is>
       </c>
       <c r="U18" t="inlineStr">
@@ -2339,23 +2395,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0xec715718ce1e06f5bfd1790eedf07c987dbe7e219a72c5facd15377495db5263</t>
+          <t>0x30456ccfad64c160bffacf5a1f4e18e0d0ff33564583ec83193fcb3d91e9aaec</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
+          <t>0x0c0188D085B3Edc4EAcfF25cd747ca4A50882743</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>122.1</t>
+          <t>61.92</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>1.1075</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -2371,27 +2427,27 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
+          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -2416,17 +2472,17 @@
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>1786676253</t>
+          <t>1786714476</t>
         </is>
       </c>
       <c r="S19" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T19" t="inlineStr">
         <is>
-          <t>740.0</t>
+          <t>576.0</t>
         </is>
       </c>
       <c r="U19" t="inlineStr">
@@ -2443,28 +2499,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0x0e7729ad6b4a9824864f6ac006c58fb19124ac050b08faef247ac7a176fd96ee</t>
+          <t>0x0d09c63a4b7a6ef00e74525f3fc2b9f5b2a53b4beb121809b52c820bd0cab95b</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>0xB66Aa9923E7a8920151375e186E6718064dd4f08</t>
+          <t>0x0c0188D085B3Edc4EAcfF25cd747ca4A50882743</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>245.05482</t>
+          <t>14.68</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.755</t>
+          <t>1.1062</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2475,27 +2531,27 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>0x32766ed977cae312bdb45c44b07e70207b356db986ef0293796496f193e13d1e</t>
+          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2520,17 +2576,17 @@
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>1786669488</t>
+          <t>1786714438</t>
         </is>
       </c>
       <c r="S20" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
-          <t>324.575921</t>
+          <t>138.164706</t>
         </is>
       </c>
       <c r="U20" t="inlineStr">
@@ -2547,28 +2603,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0x8d79a50b7331e59ea36d27efa5d99d53e26dfd1be15401e254a4cc43e280ff2f</t>
+          <t>0xfad8a96db5b6d20d7f210ef73054d1327c939838b5e270d4d8d924b1aa086629</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>0x9737E0E3E8EE2DD6B8A7E19D1507EcB3221b5483</t>
+          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>4.89999</t>
+          <t>4.1894</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>1.5863</t>
+          <t>1.165</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2579,27 +2635,27 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2624,17 +2680,17 @@
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>1786667446</t>
+          <t>1786714324</t>
         </is>
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T21" t="inlineStr">
         <is>
-          <t>8.358192</t>
+          <t>25.390303</t>
         </is>
       </c>
       <c r="U21" t="inlineStr">
@@ -2651,23 +2707,27 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0x11476693f9b725995aedcf0e75acf05d19a0f1647da3059f334da311f0f1e922</t>
+          <t>0x1120510e2af332af623aaf2def0c6f3242599093c43023de2de2d4d05ab3cf2a</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>0xF77AceaD3B354FCD16E60e4a6AbEdB7796b7094E</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>1.19253</t>
+          <t>377.95875</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.5713</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -2675,7 +2735,11 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
       <c r="H22" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -2683,27 +2747,27 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0x10c92f089fb69109ac5beea7c82a0e1cd2f23257cd842348710e2598be68bc48</t>
+          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2728,17 +2792,17 @@
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>1786664168</t>
+          <t>1786711945</t>
         </is>
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T22" t="inlineStr">
         <is>
-          <t>2.08758</t>
+          <t>905.290419</t>
         </is>
       </c>
       <c r="U22" t="inlineStr">
@@ -2755,31 +2819,39 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0x046492cfcbf4e5a3ced4caa85326fa8b44dbff1fb248a61a7fa6c8a8d2d9c1f8</t>
+          <t>0x30eb86e1b4397e3d4423a777fb6ed5785a789a492af35964b27097d9ff0e0f0c</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>0xF77AceaD3B354FCD16E60e4a6AbEdB7796b7094E</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>283.53</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>1.5962</t>
+          <t>1.4175</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Sevilla -0.5</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -2787,27 +2859,27 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>0xfcdcf41a0510583d5bb65df7215b5101ff435808043952db2a0364f1424743db</t>
+          <t>0xe6296471d7ae7834d2fe168f940eb41253ef7ab571b7c4a8e391bbd18f47f2c0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -2832,17 +2904,17 @@
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>1786663762</t>
+          <t>1786711930</t>
         </is>
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T23" t="inlineStr">
         <is>
-          <t>8.385744</t>
+          <t>679.113772</t>
         </is>
       </c>
       <c r="U23" t="inlineStr">
@@ -2859,28 +2931,28 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0xe376b22b83ba1a0d5c58e6763337d61f4445c85bfdc77949472d41c7c47e42b6</t>
+          <t>0x91aab92dfd48273588feb93e3faba11fc9f8c1f944d65a4451e2337d0b6be50e</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
+          <t>0xa1B345AC7dAd7aA730fe22f3a6379de06a7f6B61</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>21.77517</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.1075</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2891,27 +2963,27 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Celta de Vigo vs Osasuna</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
+          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>L19370496</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2936,17 +3008,17 @@
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>1786657450</t>
+          <t>1786710306</t>
         </is>
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>1786908600</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T24" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>202.559721</t>
         </is>
       </c>
       <c r="U24" t="inlineStr">
@@ -2963,12 +3035,12 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0x4e949c2076e8faf4dcc272acfa8d69c62442324aca8ceeb5820b8348c74f13f6</t>
+          <t>0xd1b390848190c00232506eacbdf3de0c4fb3341dfed7509ed5d82ce98fefb68f</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -2978,22 +3050,22 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>16.42</t>
+          <t>32.12</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.4275</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tie</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3003,27 +3075,27 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>Celta de Vigo vs Osasuna</t>
+          <t>Espanyol vs Levante</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
+          <t>0x3b15a29eb768ad2d602f53ab34fccc5aa069fa3f722408b8d6710612a74fb3b6</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>L19370496</t>
+          <t>L19370489</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -3048,17 +3120,17 @@
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>1786657449</t>
+          <t>1786708635</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>1786908600</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T25" t="inlineStr">
         <is>
-          <t>52.967742</t>
+          <t>75.134503</t>
         </is>
       </c>
       <c r="U25" t="inlineStr">
@@ -3075,31 +3147,39 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0xd54151c9cd066d8a5e7714f77ebc5e24ee2aac3e2c8a52a50b3a6becd0bac875</t>
+          <t>0x7f0e441004fffd1fe881714dcaf8f0dc3d32bf046fffc69dff440d1672c7714f</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>112.94</t>
+          <t>58.78</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.6625</t>
+          <t>1.5787</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Over 2.0</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -3107,27 +3187,27 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Espanyol vs Levante</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>0x78a4cf6b02d047f006e2c80b80d1bba724ebd9a508d0cce70fc13d1dcc698bd3</t>
+          <t>0x49dabceb14c4027b90dc4d8270cdfd514fe4070867c271757ed62270904d3f7a</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370489</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -3152,17 +3232,17 @@
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>1786656774</t>
+          <t>1786708635</t>
         </is>
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T26" t="inlineStr">
         <is>
-          <t>170.475472</t>
+          <t>101.563715</t>
         </is>
       </c>
       <c r="U26" t="inlineStr">
@@ -3179,28 +3259,28 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0x835c08ffc86c9c616d8c107e844ff9658b10b62372398122a4f7ded5bb28a516</t>
+          <t>0x0215ba1f4a546ce50b568125670efe2f3cb594679153dfd16e003add1ff1670b</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>0x8e9bE2B8b636Cc98b01957cE9D4E3B62cF579080</t>
+          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
       <c r="D27" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>35.07</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.5888</t>
+          <t>1.1062</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -3226,7 +3306,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -3256,7 +3336,7 @@
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>1786651844</t>
+          <t>1786707052</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
@@ -3266,7 +3346,7 @@
       </c>
       <c r="T27" t="inlineStr">
         <is>
-          <t>8.492552</t>
+          <t>330.070588</t>
         </is>
       </c>
       <c r="U27" t="inlineStr">
@@ -3283,28 +3363,28 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0x45cc84f2dd4c1b45226a895eead76c109d5af22eac83562ab8aa23758f8a6b5e</t>
+          <t>0x0ae19247ab2948e516f5ce1b5b97bbb5e71f6c997858511110a66b7335904c07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>0xa3786b93377213A42Bf1d3261d373cE67Cf2AA67</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
       <c r="D28" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>108.84</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3315,27 +3395,27 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0x78a4cf6b02d047f006e2c80b80d1bba724ebd9a508d0cce70fc13d1dcc698bd3</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -3360,17 +3440,17 @@
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>1786651814</t>
+          <t>1786706935</t>
         </is>
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T28" t="inlineStr">
         <is>
-          <t>42.735043</t>
+          <t>164.909091</t>
         </is>
       </c>
       <c r="U28" t="inlineStr">
@@ -3387,28 +3467,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0x213398a7cadc42743f3aee31a89c45cc1f9c78136646bd816983864c34b13f79</t>
+          <t>0x6ccfb889ade998fdea5a13e6f95b82afc8d38ea46dc3cdb05777d19b61d38489</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>0x4feB57379592eb94c51c014553de6EEbD4d42577</t>
+          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
       <c r="D29" t="inlineStr">
         <is>
-          <t>13.7</t>
+          <t>38.96365</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.685</t>
+          <t>1.1675</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -3419,27 +3499,27 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Celta de Vigo vs Osasuna</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>L19370496</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -3464,17 +3544,17 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>1786651743</t>
+          <t>1786706838</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>1786908600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T29" t="inlineStr">
         <is>
-          <t>20.0</t>
+          <t>232.618806</t>
         </is>
       </c>
       <c r="U29" t="inlineStr">
@@ -3491,28 +3571,28 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0x0adf7a0f94fb74bebb4e5acb49582e1f91e3ae462b204becaedfbe0f50714ede</t>
+          <t>0xece691e2f3fa898d49c7d3c991735f87e5c4d9d84718f8019f8459dd0608d12b</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>0x06a603b688E676702ec63D735CAe4A57ff71B3e1</t>
+          <t>0xa1B345AC7dAd7aA730fe22f3a6379de06a7f6B61</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
       <c r="D30" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>123</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.1663</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3523,27 +3603,27 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -3568,17 +3648,17 @@
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>1786651718</t>
+          <t>1786704868</t>
         </is>
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T30" t="inlineStr">
         <is>
-          <t>8.546991</t>
+          <t>739.849624</t>
         </is>
       </c>
       <c r="U30" t="inlineStr">
@@ -3595,28 +3675,28 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0xc33e951dfa8d84c01759f86fe63dfc68ddc2b547988e3a32445d72b681f7f7a5</t>
+          <t>0x233e63e043940ed7a303b95c191bb2fe090edd21f5a29da25bf50df5b3a936de</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>136.87</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.545</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -3627,27 +3707,27 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Espanyol vs Levante</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Espanyol</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0x0b6a22493b6514fc21dd836e8493df5b744432e27aa48ef80289f94befb19490</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370489</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -3672,17 +3752,17 @@
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>1786651637</t>
+          <t>1786696941</t>
         </is>
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786899600</t>
         </is>
       </c>
       <c r="T31" t="inlineStr">
         <is>
-          <t>8.546991</t>
+          <t>251.137615</t>
         </is>
       </c>
       <c r="U31" t="inlineStr">
@@ -3699,28 +3779,28 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0x948b3c3ece530e62252af65b92bdd73725833fe7355d5496ab1d4f6d84e43cc4</t>
+          <t>0x465f902491d3a3e6b99a234c6b14c18b007ae7c4d5a71ccdd550d024861bb7b6</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
+          <t>0xFBd63A3Adf898EfFf1e5A017f98756dC760eBfb8</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>61.46</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.1663</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr"/>
@@ -3731,27 +3811,27 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -3776,17 +3856,17 @@
       </c>
       <c r="R32" t="inlineStr">
         <is>
-          <t>1786651588</t>
+          <t>1786692208</t>
         </is>
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T32" t="inlineStr">
         <is>
-          <t>1.709402</t>
+          <t>369.684211</t>
         </is>
       </c>
       <c r="U32" t="inlineStr">
@@ -3803,23 +3883,23 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0x7578c65431424d3ae35de659ad6d246a7814cbb553d85319bf0968700f7bca4a</t>
+          <t>0xbf1a151f615bf3f9a9e616e3c50bbe9cfcae4e7a99f9ce723f49c93c83cdc9d0</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
+          <t>0x30E3f83573EbFc7274EeAfD586D930F7392F5650</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>1.16999</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.5875</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -3880,7 +3960,7 @@
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>1786651585</t>
+          <t>1786687820</t>
         </is>
       </c>
       <c r="S33" t="inlineStr">
@@ -3890,7 +3970,7 @@
       </c>
       <c r="T33" t="inlineStr">
         <is>
-          <t>17.094</t>
+          <t>1.991472</t>
         </is>
       </c>
       <c r="U33" t="inlineStr">
@@ -3907,31 +3987,39 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0x28bc2779df67c8165804579669b7a40ef9e3a34f89e4d9d4c81a44f6c49d8be2</t>
+          <t>0x11994251df996a13dca305742c6cfa502ae27aa5f4bd0111f29dc7341166926a</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>0x2F9aCBd9B89C6eF3bc3Dc2B0F0cCD0E0936BF912</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>0xdFC5342F5d4bF9F317c0CBf71121AC6FA92d8fbf</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>45.715</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.2788</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
       <c r="H34" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -3939,27 +4027,27 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Celta de Vigo vs Osasuna</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0x9993d963f79cc9f688d38136ed8af60ad8c5e128ae668d0af49645c4ec2e0c25</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370496</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3984,17 +4072,17 @@
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>1786651567</t>
+          <t>1786684730</t>
         </is>
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786908600</t>
         </is>
       </c>
       <c r="T34" t="inlineStr">
         <is>
-          <t>17.094</t>
+          <t>164.0</t>
         </is>
       </c>
       <c r="U34" t="inlineStr">
@@ -4011,28 +4099,28 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0x0eaa76f318c30c9b01a36fedfdc1b48daafadd063ed5c90a74fd0908bdecfce3</t>
+          <t>0x03eaa48ad5cba7703834b4eb4188b2512fc59fc66ce1a132f347fb208e62190e</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>0x6203b6338991Ec84C8A8f5ef06bC17ceB1395Ddb</t>
+          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
       <c r="D35" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>29.16362</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.1075</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -4058,7 +4146,7 @@
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -4088,7 +4176,7 @@
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>1786651567</t>
+          <t>1786684614</t>
         </is>
       </c>
       <c r="S35" t="inlineStr">
@@ -4098,7 +4186,7 @@
       </c>
       <c r="T35" t="inlineStr">
         <is>
-          <t>11.965812</t>
+          <t>271.289488</t>
         </is>
       </c>
       <c r="U35" t="inlineStr">
@@ -4115,28 +4203,28 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0xcc54eb94d459bc0b9a34beb78c07fafbc7c1f3e7c6d43846f17fb20856c43d24</t>
+          <t>0xf7320171cfa1d2a4388cf7700c275208ec77d1f0986bae7466346769cb38d5b4</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>1.05797</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.1075</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -4162,7 +4250,7 @@
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -4192,7 +4280,7 @@
       </c>
       <c r="R36" t="inlineStr">
         <is>
-          <t>1786651559</t>
+          <t>1786684161</t>
         </is>
       </c>
       <c r="S36" t="inlineStr">
@@ -4202,7 +4290,7 @@
       </c>
       <c r="T36" t="inlineStr">
         <is>
-          <t>42.735043</t>
+          <t>9.841581</t>
         </is>
       </c>
       <c r="U36" t="inlineStr">
@@ -4219,28 +4307,28 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0x1b14ab3ce842bb0ded035add24fcdd28a77380141c189ae36b1f623e70dff465</t>
+          <t>0x2c667f7cd0a5ee4597a318320db656e61b2fe595b68044cdbb02a35a2c508f11</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr">
         <is>
-          <t>9.99999</t>
+          <t>122.1</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.165</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4251,27 +4339,27 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -4296,17 +4384,17 @@
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>1786651559</t>
+          <t>1786679771</t>
         </is>
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T37" t="inlineStr">
         <is>
-          <t>17.094</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="U37" t="inlineStr">
@@ -4323,28 +4411,28 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0x31a8e64cfb4307b5b608318a4e037810f68fe9bef13258aa7d3c45dd664c0ad3</t>
+          <t>0xef898b845c993efce01f949a5b4165e91083d76283cd50b5ccb38113072d39a3</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>0x03d4fFC791EE4A80194C9d9782E7D56407b242Ed</t>
+          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>122.1</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.165</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr"/>
@@ -4355,27 +4443,27 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -4400,17 +4488,17 @@
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>1786651558</t>
+          <t>1786677944</t>
         </is>
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T38" t="inlineStr">
         <is>
-          <t>25.641026</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="U38" t="inlineStr">
@@ -4427,28 +4515,28 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0x1c244dc1d052ae42a83bf5640bcba1b28bb9c28853e7f42713fa4fddcb66b677</t>
+          <t>0xec715718ce1e06f5bfd1790eedf07c987dbe7e219a72c5facd15377495db5263</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+          <t>0xf3F25e96ea1eb0FC87b1778eD6C76af72405e9a4</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4.99999</t>
+          <t>122.1</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.585</t>
+          <t>1.165</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>Under/Over (0.5)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr"/>
@@ -4459,27 +4547,27 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -4504,17 +4592,17 @@
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>1786651550</t>
+          <t>1786676253</t>
         </is>
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T39" t="inlineStr">
         <is>
-          <t>8.546991</t>
+          <t>740.0</t>
         </is>
       </c>
       <c r="U39" t="inlineStr">
@@ -4531,39 +4619,31 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0x20fcd5dbfafe538f08c15c6b35af5d546fa35aa588ef9811c9696ac39843c736</t>
+          <t>0x0e7729ad6b4a9824864f6ac006c58fb19124ac050b08faef247ac7a176fd96ee</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xB66Aa9923E7a8920151375e186E6718064dd4f08</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>245.05482</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>1.755</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Deportivo Alaves -0.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -4586,7 +4666,7 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
+          <t>0x32766ed977cae312bdb45c44b07e70207b356db986ef0293796496f193e13d1e</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -4616,7 +4696,7 @@
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>1786640471</t>
+          <t>1786669488</t>
         </is>
       </c>
       <c r="S40" t="inlineStr">
@@ -4626,7 +4706,7 @@
       </c>
       <c r="T40" t="inlineStr">
         <is>
-          <t>12.195122</t>
+          <t>324.575921</t>
         </is>
       </c>
       <c r="U40" t="inlineStr">
@@ -4643,39 +4723,31 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0x48d06bf1eb103be3b93f605ad7b9ed301f228fa4dfae557dca83434f1d5e0c1a</t>
+          <t>0x8d79a50b7331e59ea36d27efa5d99d53e26dfd1be15401e254a4cc43e280ff2f</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9737E0E3E8EE2DD6B8A7E19D1507EcB3221b5483</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr">
         <is>
-          <t>26.96</t>
+          <t>4.89999</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.4087</t>
+          <t>1.5863</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Deportivo Alaves -0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
       <c r="H41" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -4683,27 +4755,27 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -4728,17 +4800,17 @@
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>1786640450</t>
+          <t>1786667446</t>
         </is>
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T41" t="inlineStr">
         <is>
-          <t>65.957187</t>
+          <t>8.358192</t>
         </is>
       </c>
       <c r="U41" t="inlineStr">
@@ -4755,39 +4827,31 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0xe750c1fb5c3ef7edfc166b18659be46b00e3cc96d5ae299b162166175d07245f</t>
+          <t>0x11476693f9b725995aedcf0e75acf05d19a0f1647da3059f334da311f0f1e922</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr">
         <is>
-          <t>20.06</t>
+          <t>1.19253</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>1.5437</t>
+          <t>1.5713</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Over 2.5</t>
-        </is>
-      </c>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -4810,7 +4874,7 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>0x0a08c3d7f08812839b48fc67d5842cc07f2a5e67ce2a26c46d0210680fda2f99</t>
+          <t>0x10c92f089fb69109ac5beea7c82a0e1cd2f23257cd842348710e2598be68bc48</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -4840,7 +4904,7 @@
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>1786639065</t>
+          <t>1786664168</t>
         </is>
       </c>
       <c r="S42" t="inlineStr">
@@ -4850,7 +4914,7 @@
       </c>
       <c r="T42" t="inlineStr">
         <is>
-          <t>36.891954</t>
+          <t>2.08758</t>
         </is>
       </c>
       <c r="U42" t="inlineStr">
@@ -4867,19 +4931,15 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0xdc16a40eba6eeb7462531fd3b01240a8f58f0ea20568efbaba25b17131094f2e</t>
+          <t>0x046492cfcbf4e5a3ced4caa85326fa8b44dbff1fb248a61a7fa6c8a8d2d9c1f8</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
       <c r="D43" t="inlineStr">
         <is>
           <t>5</t>
@@ -4887,7 +4947,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1.4213</t>
+          <t>1.5962</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -4895,11 +4955,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
+      <c r="G43" t="inlineStr"/>
       <c r="H43" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -4907,27 +4963,27 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
+          <t>0xfcdcf41a0510583d5bb65df7215b5101ff435808043952db2a0364f1424743db</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -4952,17 +5008,17 @@
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>1786633518</t>
+          <t>1786663762</t>
         </is>
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T43" t="inlineStr">
         <is>
-          <t>11.869436</t>
+          <t>8.385744</t>
         </is>
       </c>
       <c r="U43" t="inlineStr">
@@ -4979,27 +5035,23 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0x1b67e861f8e383798d979684797f608bfad6122cc87844f2a37a8cf06e019030</t>
+          <t>0xe376b22b83ba1a0d5c58e6763337d61f4445c85bfdc77949472d41c7c47e42b6</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xA31bC6F3C5514Cc3638BE835d196AF34aB1A8A05</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
       <c r="D44" t="inlineStr">
         <is>
-          <t>53.83</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -5007,11 +5059,7 @@
           <t>1X2</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Sevilla</t>
-        </is>
-      </c>
+      <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -5019,27 +5067,27 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Celta de Vigo vs Osasuna</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
+          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370496</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -5064,17 +5112,17 @@
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>1786633487</t>
+          <t>1786657450</t>
         </is>
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786908600</t>
         </is>
       </c>
       <c r="T44" t="inlineStr">
         <is>
-          <t>128.166667</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="U44" t="inlineStr">
@@ -5091,31 +5139,39 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0x909a230aebd5eb00de6012a0eb69301784b515acf69e93ee497d243bd3ce212f</t>
+          <t>0x4e949c2076e8faf4dcc272acfa8d69c62442324aca8ceeb5820b8348c74f13f6</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>0xbcD65d7e2D58b95Cf434eB65a82b9FD5b682D144</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
+          <t>0xE4DD6165bFF7EE73D7932C3b478f7E22431e85E7</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>72.15999</t>
+          <t>16.42</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Tie</t>
+        </is>
+      </c>
       <c r="H45" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -5123,27 +5179,27 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Celta de Vigo vs Osasuna</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
+          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370496</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -5168,17 +5224,17 @@
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>1786632901</t>
+          <t>1786657449</t>
         </is>
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786908600</t>
         </is>
       </c>
       <c r="T45" t="inlineStr">
         <is>
-          <t>120.26665</t>
+          <t>52.967742</t>
         </is>
       </c>
       <c r="U45" t="inlineStr">
@@ -5195,7 +5251,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0x081a76991e0701cf3dbcaa6ccbdd7d9dd69242e812c8b7e977517fe836423751</t>
+          <t>0xd54151c9cd066d8a5e7714f77ebc5e24ee2aac3e2c8a52a50b3a6becd0bac875</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5206,17 +5262,17 @@
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>112.94</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>1.1038</t>
+          <t>1.6625</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G46" t="inlineStr"/>
@@ -5227,27 +5283,27 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>Espanyol vs Levante</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Levante</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>0xd36fc2a623f22222f73350186e7d08c0d31b2d895ac24a68dc8408d4e98bf55a</t>
+          <t>0x78a4cf6b02d047f006e2c80b80d1bba724ebd9a508d0cce70fc13d1dcc698bd3</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>L19370489</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -5272,17 +5328,17 @@
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>1786631513</t>
+          <t>1786656774</t>
         </is>
       </c>
       <c r="S46" t="inlineStr">
         <is>
-          <t>1786899600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T46" t="inlineStr">
         <is>
-          <t>76.240964</t>
+          <t>170.475472</t>
         </is>
       </c>
       <c r="U46" t="inlineStr">
@@ -5299,28 +5355,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0x6f1c770a5b9534dbfff85f398a28d171effe0e02699c6558a37a881468f3090e</t>
+          <t>0x835c08ffc86c9c616d8c107e844ff9658b10b62372398122a4f7ded5bb28a516</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x8e9bE2B8b636Cc98b01957cE9D4E3B62cF579080</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
       <c r="D47" t="inlineStr">
         <is>
-          <t>7.91</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>1.1013</t>
+          <t>1.5888</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G47" t="inlineStr"/>
@@ -5346,7 +5402,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -5376,7 +5432,7 @@
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>1786631323</t>
+          <t>1786651844</t>
         </is>
       </c>
       <c r="S47" t="inlineStr">
@@ -5386,7 +5442,7 @@
       </c>
       <c r="T47" t="inlineStr">
         <is>
-          <t>78.123457</t>
+          <t>8.492552</t>
         </is>
       </c>
       <c r="U47" t="inlineStr">
@@ -5403,28 +5459,28 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0xffde28cdfe7ae2b6324278e8117e605bc5c2ecb236877e683d06b5cbe620b2b1</t>
+          <t>0x45cc84f2dd4c1b45226a895eead76c109d5af22eac83562ab8aa23758f8a6b5e</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0xa3786b93377213A42Bf1d3261d373cE67Cf2AA67</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
-          <t>11.11</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1.165</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Under/Over (0.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G48" t="inlineStr"/>
@@ -5435,27 +5491,27 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -5480,17 +5536,17 @@
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>1786631207</t>
+          <t>1786651814</t>
         </is>
       </c>
       <c r="S48" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T48" t="inlineStr">
         <is>
-          <t>67.333333</t>
+          <t>42.735043</t>
         </is>
       </c>
       <c r="U48" t="inlineStr">
@@ -5507,28 +5563,28 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0x1542e94d97dca7a28f2bf2b946f64e1fefc9fc04f50a7622a8a2791d01c58796</t>
+          <t>0x213398a7cadc42743f3aee31a89c45cc1f9c78136646bd816983864c34b13f79</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+          <t>0x4feB57379592eb94c51c014553de6EEbD4d42577</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
       <c r="D49" t="inlineStr">
         <is>
-          <t>11.85998</t>
+          <t>13.7</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.7113</t>
+          <t>1.685</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Under/Over (2.5)</t>
+          <t>1X2</t>
         </is>
       </c>
       <c r="G49" t="inlineStr"/>
@@ -5539,27 +5595,27 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Celta de Vigo vs Osasuna</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Celta de Vigo</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Osasuna</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
+          <t>0xaf77554314e04318c5e0efc781f967e8d177d3d17ef168bc65dd3721e2dedc30</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370496</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -5584,17 +5640,17 @@
       </c>
       <c r="R49" t="inlineStr">
         <is>
-          <t>1786630102</t>
+          <t>1786651743</t>
         </is>
       </c>
       <c r="S49" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786908600</t>
         </is>
       </c>
       <c r="T49" t="inlineStr">
         <is>
-          <t>16.67484</t>
+          <t>20.0</t>
         </is>
       </c>
       <c r="U49" t="inlineStr">
@@ -5611,28 +5667,28 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0x9ff18d48c5ac1507ef9b6a3dfaf34f20966e85ee30cbd99e0df47a940abf1d32</t>
+          <t>0x0adf7a0f94fb74bebb4e5acb49582e1f91e3ae462b204becaedfbe0f50714ede</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0x06a603b688E676702ec63D735CAe4A57ff71B3e1</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1.4412</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G50" t="inlineStr"/>
@@ -5643,27 +5699,27 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>0x776caca6c8b9cb32d9a7b2ec2b4f40bbb630001b4db7c24175062af09044b7dd</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -5688,17 +5744,17 @@
       </c>
       <c r="R50" t="inlineStr">
         <is>
-          <t>1786626342</t>
+          <t>1786651718</t>
         </is>
       </c>
       <c r="S50" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T50" t="inlineStr">
         <is>
-          <t>11.331445</t>
+          <t>8.546991</t>
         </is>
       </c>
       <c r="U50" t="inlineStr">
@@ -5715,28 +5771,28 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0x50f0b3572b92fd4a3268a217b75ca6b4a52b72077d0276df9d0d123d8b3ebc60</t>
+          <t>0xc33e951dfa8d84c01759f86fe63dfc68ddc2b547988e3a32445d72b681f7f7a5</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x0c68d398894468F84ECb4805726f19c37e2B3415</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
       <c r="D51" t="inlineStr">
         <is>
-          <t>16.18903</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.4412</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Under/Over (1.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G51" t="inlineStr"/>
@@ -5747,27 +5803,27 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>0x776caca6c8b9cb32d9a7b2ec2b4f40bbb630001b4db7c24175062af09044b7dd</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -5792,17 +5848,17 @@
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>1786626327</t>
+          <t>1786651637</t>
         </is>
       </c>
       <c r="S51" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T51" t="inlineStr">
         <is>
-          <t>36.68902</t>
+          <t>8.546991</t>
         </is>
       </c>
       <c r="U51" t="inlineStr">
@@ -5819,28 +5875,28 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0x2d1550913dec85439afda8d85c6033895212998f22943ab968dee5cbd7d7e7a2</t>
+          <t>0x948b3c3ece530e62252af65b92bdd73725833fe7355d5496ab1d4f6d84e43cc4</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x90aaAb8CC5139A43b5B8A6386929790Aa027Ab30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>35.45869</t>
+          <t>1</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>1.2537</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Asian Handicap (0.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G52" t="inlineStr"/>
@@ -5851,27 +5907,27 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>0x0596e7ef887839f51f014583ff32fca0dbfab0916b17c3d05d740985b59eabc3</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -5896,17 +5952,17 @@
       </c>
       <c r="R52" t="inlineStr">
         <is>
-          <t>1786624561</t>
+          <t>1786651588</t>
         </is>
       </c>
       <c r="S52" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T52" t="inlineStr">
         <is>
-          <t>139.73868</t>
+          <t>1.709402</t>
         </is>
       </c>
       <c r="U52" t="inlineStr">
@@ -5923,23 +5979,23 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0x6f809dd95ba0a7f41584a66e0979cb2c04ebaeefb6e5d949b0bfd9c53278c063</t>
+          <t>0x7578c65431424d3ae35de659ad6d246a7814cbb553d85319bf0968700f7bca4a</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+          <t>0xB892ABBd5A3E0A440c0F94149848F2C1DDf05C5B</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
       <c r="D53" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>1.7163</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -5955,27 +6011,27 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -6000,17 +6056,17 @@
       </c>
       <c r="R53" t="inlineStr">
         <is>
-          <t>1786623012</t>
+          <t>1786651585</t>
         </is>
       </c>
       <c r="S53" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T53" t="inlineStr">
         <is>
-          <t>6.980803</t>
+          <t>17.094</t>
         </is>
       </c>
       <c r="U53" t="inlineStr">
@@ -6027,28 +6083,28 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0xddff1b4ca7359c6045ede1bd2995e1e57620811dc33cc7338113c5449dccd695</t>
+          <t>0x28bc2779df67c8165804579669b7a40ef9e3a34f89e4d9d4c81a44f6c49d8be2</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x2F9aCBd9B89C6eF3bc3Dc2B0F0cCD0E0936BF912</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr">
         <is>
-          <t>28.91904</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>1.6038</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Under/Over (2)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G54" t="inlineStr"/>
@@ -6059,27 +6115,27 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>0xf684bc2655869d0024c7de5a1f2b51fb35813185b075bf3cc8d5f2fe8ce176b5</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -6104,17 +6160,17 @@
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>1786622982</t>
+          <t>1786651567</t>
         </is>
       </c>
       <c r="S54" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T54" t="inlineStr">
         <is>
-          <t>47.899031</t>
+          <t>17.094</t>
         </is>
       </c>
       <c r="U54" t="inlineStr">
@@ -6131,23 +6187,23 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0xb02e365f47ba9eaba62de63e4b14c94bf1b59d60c56188857359df36e7b10ef0</t>
+          <t>0x0eaa76f318c30c9b01a36fedfdc1b48daafadd063ed5c90a74fd0908bdecfce3</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+          <t>0x6203b6338991Ec84C8A8f5ef06bC17ceB1395Ddb</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
       <c r="D55" t="inlineStr">
         <is>
-          <t>30.81465</t>
+          <t>7</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>1.7113</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -6163,27 +6219,27 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -6208,17 +6264,17 @@
       </c>
       <c r="R55" t="inlineStr">
         <is>
-          <t>1786622982</t>
+          <t>1786651567</t>
         </is>
       </c>
       <c r="S55" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T55" t="inlineStr">
         <is>
-          <t>43.32464</t>
+          <t>11.965812</t>
         </is>
       </c>
       <c r="U55" t="inlineStr">
@@ -6235,67 +6291,59 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0xb7f333fbe5a18daf831395020096fbb62febd43977f5f81366c99339b63d902d</t>
+          <t>0xcc54eb94d459bc0b9a34beb78c07fafbc7c1f3e7c6d43846f17fb20856c43d24</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x104A90467B551Fee945180a93e5f0f385c538A75</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>63.86</t>
+          <t>25</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>1.4187</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr"/>
+      <c r="H56" t="inlineStr">
+        <is>
           <t>La Liga</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Racing Santander</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>La Liga</t>
-        </is>
-      </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>0x1518c9a8caca0376f881601c848e03d81cd65f5d32c2b63a51625351cc193e86</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -6320,17 +6368,17 @@
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>1786621976</t>
+          <t>1786651559</t>
         </is>
       </c>
       <c r="S56" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T56" t="inlineStr">
         <is>
-          <t>152.501493</t>
+          <t>42.735043</t>
         </is>
       </c>
       <c r="U56" t="inlineStr">
@@ -6347,39 +6395,31 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0x79454b5fc310a342a5ad62ccf677e7ea1c42b0e701cd313d0019ee8ec1faf7a2</t>
+          <t>0x1b14ab3ce842bb0ded035add24fcdd28a77380141c189ae36b1f623e70dff465</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x9CbF4a8A9EC2a8BABcaC7819e205a7B128798fAa</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" t="inlineStr">
         <is>
-          <t>97.87</t>
+          <t>9.99999</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Racing Santander</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -6387,27 +6427,27 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>0xf9063ec13eee8f96a20b89bd687d0a5f1a3197a4408eb58240f63d72be7c644f</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -6432,17 +6472,17 @@
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>1786621975</t>
+          <t>1786651559</t>
         </is>
       </c>
       <c r="S57" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T57" t="inlineStr">
         <is>
-          <t>320.885246</t>
+          <t>17.094</t>
         </is>
       </c>
       <c r="U57" t="inlineStr">
@@ -6459,39 +6499,31 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0x6df789a868c08b6d011dc9dc3fe38cf8be42973ee6e2b3513f1ae98f3a70e174</t>
+          <t>0x31a8e64cfb4307b5b608318a4e037810f68fe9bef13258aa7d3c45dd664c0ad3</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0x03d4fFC791EE4A80194C9d9782E7D56407b242Ed</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr">
         <is>
-          <t>82.86999</t>
+          <t>15</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>1.7363</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Asian Handicap (1)</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Racing Santander +1</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -6499,27 +6531,27 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>0xeffd773f9a996fcdab4f40cb833c6db488621204b6af7959d07794c43de040c4</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -6544,17 +6576,17 @@
       </c>
       <c r="R58" t="inlineStr">
         <is>
-          <t>1786621975</t>
+          <t>1786651558</t>
         </is>
       </c>
       <c r="S58" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T58" t="inlineStr">
         <is>
-          <t>112.556862</t>
+          <t>25.641026</t>
         </is>
       </c>
       <c r="U58" t="inlineStr">
@@ -6571,39 +6603,31 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0x4061873586e14d63aeb0e4cdf23afafe5cd7b3c74fe59157daf06c85b8fd8796</t>
+          <t>0x1c244dc1d052ae42a83bf5640bcba1b28bb9c28853e7f42713fa4fddcb66b677</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>0xD19384284ACEe246037b2f52b50EEF17F1e33B74</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>44.82</t>
+          <t>4.99999</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.305</t>
+          <t>1.585</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Asian Handicap (-0.5)</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Racing Santander -0.5</t>
-        </is>
-      </c>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -6611,27 +6635,27 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Racing Santander vs Villarreal</t>
+          <t>Sevilla vs Rayo Vallecano</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>Racing Santander</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>0xb811d0e9d1802cd3762a57ca8fc3a5399392dd37dec4f8d9fd37f0170ece0f50</t>
+          <t>0xeb4881400081231ce3e5f9992ac7e23e85fe6e1fdfec6a3997b442a83b7307b1</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>L19370490</t>
+          <t>L19370582</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -6656,17 +6680,17 @@
       </c>
       <c r="R59" t="inlineStr">
         <is>
-          <t>1786621975</t>
+          <t>1786651550</t>
         </is>
       </c>
       <c r="S59" t="inlineStr">
         <is>
-          <t>1786892400</t>
+          <t>1786822200</t>
         </is>
       </c>
       <c r="T59" t="inlineStr">
         <is>
-          <t>146.95082</t>
+          <t>8.546991</t>
         </is>
       </c>
       <c r="U59" t="inlineStr">
@@ -6683,31 +6707,39 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0x8dda40aa7d3c4140b3e5ab6ab62f3db4f5a3730a15ebff80f0bda9807c704ca2</t>
+          <t>0x20fcd5dbfafe538f08c15c6b35af5d546fa35aa588ef9811c9696ac39843c736</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>27.87224</t>
+          <t>5</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>1.5325</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>1X2</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr"/>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves -0.5</t>
+        </is>
+      </c>
       <c r="H60" t="inlineStr">
         <is>
           <t>La Liga</t>
@@ -6715,27 +6747,27 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Celta de Vigo vs Osasuna</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>Celta de Vigo</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>Osasuna</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>0x0f075dae0a586d46b2073e126cbc52393dc2ff99a26953308f94b3b2751764b7</t>
+          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>L19370496</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -6760,17 +6792,17 @@
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>1786619056</t>
+          <t>1786640471</t>
         </is>
       </c>
       <c r="S60" t="inlineStr">
         <is>
-          <t>1786908600</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T60" t="inlineStr">
         <is>
-          <t>52.342235</t>
+          <t>12.195122</t>
         </is>
       </c>
       <c r="U60" t="inlineStr">
@@ -6787,12 +6819,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0x4565877a70aabfac9d4d4a2afcda9ace6e304d9bd921ce69a2149c76528e271a</t>
+          <t>0x48d06bf1eb103be3b93f605ad7b9ed301f228fa4dfae557dca83434f1d5e0c1a</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0xb363112BA7ed93A221Efb405496e4Fa3BE119D81</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6802,22 +6834,22 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>26.96</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>1.285</t>
+          <t>1.4087</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1X2</t>
+          <t>Asian Handicap (-0.5)</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Deportivo Alaves -0.5</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -6827,27 +6859,27 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Sevilla vs Rayo Vallecano</t>
+          <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Deportivo Alaves</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>0x2b9c4f75049808a8d2b353d1c6e902da151d2fea092e70f08cdd4ac2ffbfd8a6</t>
+          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>L19370582</t>
+          <t>L19370598</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -6872,17 +6904,17 @@
       </c>
       <c r="R61" t="inlineStr">
         <is>
-          <t>1786614389</t>
+          <t>1786640450</t>
         </is>
       </c>
       <c r="S61" t="inlineStr">
         <is>
-          <t>1786822200</t>
+          <t>1786815000</t>
         </is>
       </c>
       <c r="T61" t="inlineStr">
         <is>
-          <t>175.438596</t>
+          <t>65.957187</t>
         </is>
       </c>
       <c r="U61" t="inlineStr">
@@ -6899,12 +6931,12 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0x562837a4689bf537ab0502cfe5d722bafc1833bc972e329ba5399cd7649a219c</t>
+          <t>0xe750c1fb5c3ef7edfc166b18659be46b00e3cc96d5ae299b162166175d07245f</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6914,22 +6946,22 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>20.06</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>1.5437</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Under/Over (3.5)</t>
+          <t>Under/Over (2.5)</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Over 3.5</t>
+          <t>Over 2.5</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -6939,27 +6971,27 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Deportivo Alaves vs Getafe</t>
+          <t>Racing Santander vs Villarreal</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>Deportivo Alaves</t>
+          <t>Racing Santander</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>0xda132f38d7cbcb404e0db6126292d55c3614e3311c2670ac15890a14a94cdaea</t>
+          <t>0x0a08c3d7f08812839b48fc67d5842cc07f2a5e67ce2a26c46d0210680fda2f99</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>L19370598</t>
+          <t>L19370490</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -6984,17 +7016,17 @@
       </c>
       <c r="R62" t="inlineStr">
         <is>
-          <t>1786586644</t>
+          <t>1786639065</t>
         </is>
       </c>
       <c r="S62" t="inlineStr">
         <is>
-          <t>1786815000</t>
+          <t>1786892400</t>
         </is>
       </c>
       <c r="T62" t="inlineStr">
         <is>
-          <t>7.769231</t>
+          <t>36.891954</t>
         </is>
       </c>
       <c r="U62" t="inlineStr">
@@ -7011,102 +7043,2246 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
+          <t>0xdc16a40eba6eeb7462531fd3b01240a8f58f0ea20568efbaba25b17131094f2e</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>1.4213</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>Sevilla vs Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>L19370582</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>1786633518</t>
+        </is>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>1786822200</t>
+        </is>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>11.869436</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>0x1b67e861f8e383798d979684797f608bfad6122cc87844f2a37a8cf06e019030</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>53.83</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>Sevilla vs Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>0xa5db2f6f922d69f99abed1f24ad7fa38777c90f51d489e3c1aa07c74dddb10e0</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>L19370582</t>
+        </is>
+      </c>
+      <c r="N64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>1786633487</t>
+        </is>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>1786822200</t>
+        </is>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>128.166667</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>0x909a230aebd5eb00de6012a0eb69301784b515acf69e93ee497d243bd3ce212f</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>0xbcD65d7e2D58b95Cf434eB65a82b9FD5b682D144</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>72.15999</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>0x1b8dfbd894484bd763d2600e4505a21a73c3b4cb8a3004a1654ba87980dbc559</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>1786632901</t>
+        </is>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>120.26665</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>0x081a76991e0701cf3dbcaa6ccbdd7d9dd69242e812c8b7e977517fe836423751</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>7.91</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>1.1038</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr"/>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>Espanyol vs Levante</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>0xd36fc2a623f22222f73350186e7d08c0d31b2d895ac24a68dc8408d4e98bf55a</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>L19370489</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>1786631513</t>
+        </is>
+      </c>
+      <c r="S66" t="inlineStr">
+        <is>
+          <t>1786899600</t>
+        </is>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>76.240964</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>0x6f1c770a5b9534dbfff85f398a28d171effe0e02699c6558a37a881468f3090e</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>7.91</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>1.1013</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr"/>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Sevilla vs Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>0x3b99901d045414f7d5a55497712a0a61ef0f6a829783277b6f0583659a40517f</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>L19370582</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>1786631323</t>
+        </is>
+      </c>
+      <c r="S67" t="inlineStr">
+        <is>
+          <t>1786822200</t>
+        </is>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>78.123457</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>0xffde28cdfe7ae2b6324278e8117e605bc5c2ecb236877e683d06b5cbe620b2b1</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr"/>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>11.11</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>1.165</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Under/Over (0.5)</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr"/>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>0xdae71376e09c91d710d729fe77ea2e842f603f91974aa4731f913be7021c5796</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>1786631207</t>
+        </is>
+      </c>
+      <c r="S68" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>67.333333</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>0x1542e94d97dca7a28f2bf2b946f64e1fefc9fc04f50a7622a8a2791d01c58796</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>0x97EC1C9682F70091efB04e97b0B34698cF815EE1</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>11.85998</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>1.7113</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>1786630102</t>
+        </is>
+      </c>
+      <c r="S69" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>16.67484</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>0x9ff18d48c5ac1507ef9b6a3dfaf34f20966e85ee30cbd99e0df47a940abf1d32</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>1.4412</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr"/>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>0x776caca6c8b9cb32d9a7b2ec2b4f40bbb630001b4db7c24175062af09044b7dd</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>1786626342</t>
+        </is>
+      </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>11.331445</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0x50f0b3572b92fd4a3268a217b75ca6b4a52b72077d0276df9d0d123d8b3ebc60</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>16.18903</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1.4412</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Under/Over (1.5)</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr"/>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>0x776caca6c8b9cb32d9a7b2ec2b4f40bbb630001b4db7c24175062af09044b7dd</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>1786626327</t>
+        </is>
+      </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>36.68902</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>0x2d1550913dec85439afda8d85c6033895212998f22943ab968dee5cbd7d7e7a2</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>35.45869</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>1.2537</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr"/>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>0x0596e7ef887839f51f014583ff32fca0dbfab0916b17c3d05d740985b59eabc3</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>1786624561</t>
+        </is>
+      </c>
+      <c r="S72" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>139.73868</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>0x6f809dd95ba0a7f41584a66e0979cb2c04ebaeefb6e5d949b0bfd9c53278c063</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>0x0DeAbC808957aBc9f4778C03b03CC1D2cBBC9D60</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1.7163</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>1786623012</t>
+        </is>
+      </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>6.980803</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>0xddff1b4ca7359c6045ede1bd2995e1e57620811dc33cc7338113c5449dccd695</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>28.91904</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>1.6038</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Under/Over (2)</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>0xf684bc2655869d0024c7de5a1f2b51fb35813185b075bf3cc8d5f2fe8ce176b5</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>1786622982</t>
+        </is>
+      </c>
+      <c r="S74" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>47.899031</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>0xb02e365f47ba9eaba62de63e4b14c94bf1b59d60c56188857359df36e7b10ef0</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>30.81465</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>1.7113</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Under/Over (2.5)</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>0x8791bf3272cd82404ef50845fa5ccbf5ded7fb2a083138dbf01a1443c1054c54</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>1786622982</t>
+        </is>
+      </c>
+      <c r="S75" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>43.32464</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>0xb7f333fbe5a18daf831395020096fbb62febd43977f5f81366c99339b63d902d</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>63.86</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>1.4187</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>Racing Santander vs Villarreal</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>0x1518c9a8caca0376f881601c848e03d81cd65f5d32c2b63a51625351cc193e86</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>L19370490</t>
+        </is>
+      </c>
+      <c r="N76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>1786621976</t>
+        </is>
+      </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>1786892400</t>
+        </is>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>152.501493</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>0x79454b5fc310a342a5ad62ccf677e7ea1c42b0e701cd313d0019ee8ec1faf7a2</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>97.87</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>1.305</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>Racing Santander vs Villarreal</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>0xf9063ec13eee8f96a20b89bd687d0a5f1a3197a4408eb58240f63d72be7c644f</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>L19370490</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q77" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R77" t="inlineStr">
+        <is>
+          <t>1786621975</t>
+        </is>
+      </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>1786892400</t>
+        </is>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>320.885246</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>0x6df789a868c08b6d011dc9dc3fe38cf8be42973ee6e2b3513f1ae98f3a70e174</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>82.86999</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>1.7363</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Asian Handicap (1)</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Racing Santander +1</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>Racing Santander vs Villarreal</t>
+        </is>
+      </c>
+      <c r="J78" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="K78" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>0xeffd773f9a996fcdab4f40cb833c6db488621204b6af7959d07794c43de040c4</t>
+        </is>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>L19370490</t>
+        </is>
+      </c>
+      <c r="N78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q78" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>1786621975</t>
+        </is>
+      </c>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>1786892400</t>
+        </is>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>112.556862</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>0x4061873586e14d63aeb0e4cdf23afafe5cd7b3c74fe59157daf06c85b8fd8796</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>44.82</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>1.305</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-0.5)</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Racing Santander -0.5</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>Racing Santander vs Villarreal</t>
+        </is>
+      </c>
+      <c r="J79" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="L79" t="inlineStr">
+        <is>
+          <t>0xb811d0e9d1802cd3762a57ca8fc3a5399392dd37dec4f8d9fd37f0170ece0f50</t>
+        </is>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>L19370490</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R79" t="inlineStr">
+        <is>
+          <t>1786621975</t>
+        </is>
+      </c>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>1786892400</t>
+        </is>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>146.95082</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>0x8dda40aa7d3c4140b3e5ab6ab62f3db4f5a3730a15ebff80f0bda9807c704ca2</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>27.87224</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>1.5325</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>Celta de Vigo vs Osasuna</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>Celta de Vigo</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr">
+        <is>
+          <t>0x0f075dae0a586d46b2073e126cbc52393dc2ff99a26953308f94b3b2751764b7</t>
+        </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>L19370496</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q80" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R80" t="inlineStr">
+        <is>
+          <t>1786619056</t>
+        </is>
+      </c>
+      <c r="S80" t="inlineStr">
+        <is>
+          <t>1786908600</t>
+        </is>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>52.342235</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>0x4565877a70aabfac9d4d4a2afcda9ace6e304d9bd921ce69a2149c76528e271a</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>0xb363112BA7ed93A221Efb405496e4Fa3BE119D81</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>1.285</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>Sevilla vs Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr">
+        <is>
+          <t>0x2b9c4f75049808a8d2b353d1c6e902da151d2fea092e70f08cdd4ac2ffbfd8a6</t>
+        </is>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>L19370582</t>
+        </is>
+      </c>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q81" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>1786614389</t>
+        </is>
+      </c>
+      <c r="S81" t="inlineStr">
+        <is>
+          <t>1786822200</t>
+        </is>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>175.438596</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>0x562837a4689bf537ab0502cfe5d722bafc1833bc972e329ba5399cd7649a219c</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>0x740d5718a79A8559fEeE8B00922F8Cd773A81D84</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>1.01</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>1.13</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Under/Over (3.5)</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Over 3.5</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>La Liga</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves vs Getafe</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>Deportivo Alaves</t>
+        </is>
+      </c>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="L82" t="inlineStr">
+        <is>
+          <t>0xda132f38d7cbcb404e0db6126292d55c3614e3311c2670ac15890a14a94cdaea</t>
+        </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>L19370598</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q82" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R82" t="inlineStr">
+        <is>
+          <t>1786586644</t>
+        </is>
+      </c>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>1786815000</t>
+        </is>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>7.769231</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
           <t>0x27be56be09649bd460766fe27df249788cf4d7ad87d19f5f9a8bfba225e519b9</t>
         </is>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B83" t="inlineStr">
         <is>
           <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" t="inlineStr">
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" t="inlineStr">
         <is>
           <t>1.52676</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E83" t="inlineStr">
         <is>
           <t>1.7512</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F83" t="inlineStr">
         <is>
           <t>1X2</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr">
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr">
         <is>
           <t>La Liga</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I83" t="inlineStr">
         <is>
           <t>Deportivo Alaves vs Getafe</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr">
+      <c r="J83" t="inlineStr">
         <is>
           <t>Deportivo Alaves</t>
         </is>
       </c>
-      <c r="K63" t="inlineStr">
+      <c r="K83" t="inlineStr">
         <is>
           <t>Getafe</t>
         </is>
       </c>
-      <c r="L63" t="inlineStr">
+      <c r="L83" t="inlineStr">
         <is>
           <t>0x32766ed977cae312bdb45c44b07e70207b356db986ef0293796496f193e13d1e</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr">
+      <c r="M83" t="inlineStr">
         <is>
           <t>L19370598</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
+      <c r="N83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
         <is>
           <t>SUCCESS</t>
         </is>
       </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
+      <c r="Q83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R83" t="inlineStr">
         <is>
           <t>1786578252</t>
         </is>
       </c>
-      <c r="S63" t="inlineStr">
+      <c r="S83" t="inlineStr">
         <is>
           <t>1786815000</t>
         </is>
       </c>
-      <c r="T63" t="inlineStr">
+      <c r="T83" t="inlineStr">
         <is>
           <t>2.032293</t>
         </is>
       </c>
-      <c r="U63" t="inlineStr">
+      <c r="U83" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V63" t="inlineStr">
+      <c r="V83" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>
